--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.72</v>
+        <v>73.81</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|7</t>
+          <t>2|6|8|44|47|49|23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1650,7 +1650,7 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.72</v>
+        <v>47.81</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1696,22 +1696,22 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="N14" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1741,23 +1741,23 @@
         <v>0.5</v>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>45.72</v>
+        <v>42.81</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2|8|29|33|44|49|19</t>
+          <t>2|17|23|27|40|44|32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="N15" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1823,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1835,23 +1835,23 @@
         <v>0.5</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.72</v>
+        <v>40.31</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2|8|17|20|33|49|28</t>
+          <t>4|8|29|33|35|44|13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
         <v>29</v>
@@ -1893,13 +1893,13 @@
         <v>33</v>
       </c>
       <c r="L16" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
         <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1917,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>40.22</v>
+        <v>38.81</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>2|7|29|33|40|46|13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
@@ -1972,16 +1972,16 @@
         </is>
       </c>
       <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
         <v>33</v>
@@ -1990,10 +1990,10 @@
         <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2011,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>38.72</v>
+        <v>37.81</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>4|8|27|33|40|43|20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -2069,34 +2069,34 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L18" t="n">
+        <v>40</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18</v>
+      </c>
+      <c r="N18" t="n">
+        <v>149</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>41</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>153</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>33</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.00571428571428</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11|14|20|23|41|44|1</t>
+          <t>1|16|17|33|40|42|18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
         <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.47</v>
+        <v>36.56</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11|20|27|30|31|44|7</t>
+          <t>1|8|27|32|42|45|10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -2260,22 +2260,22 @@
         <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N20" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.05333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|23|26|32|37|41|11</t>
+          <t>8|17|19|30|42|49|24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M21" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.72</v>
+        <v>35.81</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|11|14|30|31|33|49</t>
+          <t>2|3|24|43|44|47|10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -2448,10 +2448,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
         <v>30</v>
@@ -2460,10 +2460,10 @@
         <v>32</v>
       </c>
       <c r="M22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.44727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1|9|27|30|32|46|18</t>
+          <t>1|13|14|30|32|47|21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.86</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,32 +2629,32 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.86</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.86</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
+        <v>21</v>
+      </c>
+      <c r="L26" t="n">
         <v>25</v>
-      </c>
-      <c r="L26" t="n">
-        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.36</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2911,11 +2911,11 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O27" t="n">
         <v>2</v>
@@ -2924,7 +2924,7 @@
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.86</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|6|10|25|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L28" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.86</v>
+        <v>37.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="n">
-        <v>14</v>
-      </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.14571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,32 +3169,32 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.61</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3262,20 +3262,20 @@
         <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.19333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.86</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|10|11|21|25</t>
+          <t>4|14|17|25|35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3442,29 +3442,29 @@
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>35</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.58727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|6|13|25|35</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
         <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N35" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3686,16 +3686,16 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>5|19|22|26|38|45|30</t>
+          <t>17|19|20|31|38|44|15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
         <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="N36" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3784,16 +3784,16 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>6|16|24|31|41|45|12</t>
+          <t>5|13|24|30|41|48|47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3928,22 +3928,22 @@
         <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="N38" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3980,16 +3980,16 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|19|24|26|45|46|17</t>
+          <t>9|11|14|40|44|45|37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -4023,22 +4023,22 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L39" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M39" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N39" t="n">
         <v>163</v>
@@ -4078,16 +4078,16 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|13|24|32|41|48|18</t>
+          <t>2|9|24|40|43|45|34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M40" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="N40" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4176,16 +4176,16 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>3|9|14|26|40|41|24</t>
+          <t>2|9|24|31|41|44|33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M41" t="n">
         <v>48</v>
       </c>
       <c r="N41" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4274,16 +4274,16 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|47|48</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N42" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4372,16 +4372,16 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>1|5|9|30|38|44|27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -4415,34 +4415,34 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
+        <v>11</v>
+      </c>
+      <c r="J43" t="n">
         <v>13</v>
-      </c>
-      <c r="J43" t="n">
-        <v>20</v>
       </c>
       <c r="K43" t="n">
         <v>26</v>
       </c>
       <c r="L43" t="n">
+        <v>39</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>131</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>38</v>
-      </c>
-      <c r="M43" t="n">
-        <v>35</v>
-      </c>
-      <c r="N43" t="n">
-        <v>143</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>36</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4470,16 +4470,16 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|13|20|26|38|41|35</t>
+          <t>2|11|13|26|39|40|7</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L44" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N44" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4568,16 +4568,16 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|8|24|30|39|41|16</t>
+          <t>2|16|24|29|31|43|18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -4715,19 +4715,19 @@
         <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
+        <v>33</v>
+      </c>
+      <c r="L46" t="n">
         <v>42</v>
       </c>
-      <c r="L46" t="n">
-        <v>45</v>
-      </c>
       <c r="M46" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N46" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4760,16 +4760,16 @@
         <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>39.1667</v>
+        <v>38.80955714285714</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|10</t>
+          <t>1|2|24|33|42|49|23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
         <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M47" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N47" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0.5</v>
       </c>
       <c r="X47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>38.80955714285714</v>
+        <v>36.1667</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>1|3|6|38|48|49|15</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
         <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="N48" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4953,19 +4953,19 @@
         <v>0.5</v>
       </c>
       <c r="X48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>38.6667</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>1|9|20|38|42|49|8</t>
+          <t>6|11|20|39|44|49|40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5000,28 +5000,28 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L49" t="n">
         <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N49" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5051,23 +5051,23 @@
         <v>0.5</v>
       </c>
       <c r="X49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>38.33336666666666</v>
+        <v>35.6667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1|2|24|29|38|49|7</t>
+          <t>3|5|24|37|38|44|19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
@@ -5098,28 +5098,28 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
+        <v>29</v>
+      </c>
+      <c r="L50" t="n">
         <v>38</v>
       </c>
-      <c r="L50" t="n">
-        <v>48</v>
-      </c>
       <c r="M50" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="N50" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5137,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.0625</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5152,16 +5152,16 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.97439230769231</v>
+        <v>35.5417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|5|24|38|48|49|44</t>
+          <t>8|14|23|29|38|49|36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5196,28 +5196,28 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M51" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N51" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0.0625</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.5417</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|33</t>
+          <t>3|6|24|31|34|43|10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -5294,38 +5294,38 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L52" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M52" t="n">
+        <v>26</v>
+      </c>
+      <c r="N52" t="n">
+        <v>139</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>42</v>
       </c>
-      <c r="N52" t="n">
-        <v>159</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>47</v>
-      </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.43140588235294</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>2|3|24|33|48|49|42</t>
+          <t>3|4|24|29|34|45|26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -5398,31 +5398,31 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
+        <v>32</v>
+      </c>
+      <c r="M53" t="n">
+        <v>46</v>
+      </c>
+      <c r="N53" t="n">
+        <v>133</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="n">
         <v>42</v>
-      </c>
-      <c r="M53" t="n">
-        <v>18</v>
-      </c>
-      <c r="N53" t="n">
-        <v>155</v>
-      </c>
-      <c r="O53" t="n">
-        <v>3</v>
-      </c>
-      <c r="P53" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5450,16 +5450,16 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>3|4|20|29|32|45|46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -5493,34 +5493,34 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J54" t="n">
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M54" t="n">
+        <v>34</v>
+      </c>
+      <c r="N54" t="n">
+        <v>157</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+      <c r="P54" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q54" t="n">
         <v>47</v>
-      </c>
-      <c r="N54" t="n">
-        <v>155</v>
-      </c>
-      <c r="O54" t="n">
-        <v>3</v>
-      </c>
-      <c r="P54" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|12|20|33|38|49|47</t>
+          <t>2|13|20|29|44|49|34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5594,10 +5594,10 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
         <v>38</v>
@@ -5606,10 +5606,10 @@
         <v>42</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N55" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|4|5|38|42|49|6</t>
+          <t>3|8|15|38|42|49|17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.94</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
@@ -2641,20 +2641,20 @@
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.94</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
+        <v>21</v>
+      </c>
+      <c r="L25" t="n">
         <v>25</v>
-      </c>
-      <c r="L25" t="n">
-        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.84</v>
+        <v>42.94</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.34</v>
+        <v>40.44</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,32 +2899,32 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="P27" t="n">
-        <v>3</v>
-      </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.84</v>
+        <v>38.94</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>5|8|14|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.84</v>
+        <v>37.94</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
         <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.12571428571429</v>
+        <v>37.22571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
-      </c>
-      <c r="J30" t="n">
-        <v>14</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.59</v>
+        <v>36.69</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.17333333333333</v>
+        <v>36.27333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3352,20 +3352,20 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
         <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.84</v>
+        <v>35.94</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3448,14 +3448,14 @@
         <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O33" t="n">
         <v>2</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>35.66727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6667</v>
+        <v>48.4375</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|15</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6667</v>
+        <v>43.4375</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|47</t>
+          <t>9|16|22|31|44|45|7</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -3827,34 +3827,34 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
+        <v>26</v>
+      </c>
+      <c r="L37" t="n">
+        <v>38</v>
+      </c>
+      <c r="M37" t="n">
+        <v>35</v>
+      </c>
+      <c r="N37" t="n">
+        <v>141</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
         <v>31</v>
-      </c>
-      <c r="L37" t="n">
-        <v>40</v>
-      </c>
-      <c r="M37" t="n">
-        <v>30</v>
-      </c>
-      <c r="N37" t="n">
-        <v>157</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3</v>
-      </c>
-      <c r="P37" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>43</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1667</v>
+        <v>40.9375</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|19|20|31|40|45|30</t>
+          <t>9|11|17|26|38|40|35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -3925,34 +3925,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
+        <v>38</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>141</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>44</v>
-      </c>
-      <c r="M38" t="n">
-        <v>37</v>
-      </c>
-      <c r="N38" t="n">
-        <v>163</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>36</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,16 +3976,16 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6667</v>
+        <v>39.4375</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|11|14|40|44|45|37</t>
+          <t>1|7|24|26|38|45|5</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4023,22 +4023,22 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L39" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M39" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
         <v>163</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6667</v>
+        <v>38.4375</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|34</t>
+          <t>6|16|24|33|41|43|2</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
@@ -4124,22 +4124,22 @@
         <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L40" t="n">
         <v>41</v>
       </c>
       <c r="M40" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.95241428571428</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|33</t>
+          <t>2|19|24|39|41|42|7</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M41" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N41" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4167</v>
+        <v>37.1875</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>1|19|24|38|40|45|42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M42" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="N42" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.00003333333333</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|5|9|30|38|44|27</t>
+          <t>5|9|14|40|48|49|13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L43" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6667</v>
+        <v>36.4375</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>5|9|22|30|40|45|1</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M44" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N44" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.39397272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|16|24|29|31|43|18</t>
+          <t>6|18|19|31|39|44|48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,25 +4706,25 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M46" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N46" t="n">
         <v>151</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,23 +4757,23 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.80955714285714</v>
+        <v>35.9375</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|2|24|33|42|49|23</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
+        <v>25</v>
+      </c>
+      <c r="L47" t="n">
         <v>38</v>
       </c>
-      <c r="L47" t="n">
-        <v>44</v>
-      </c>
       <c r="M47" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.1667</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|4|12|25|38|39|15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
+        <v>13</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J48" t="n">
         <v>12</v>
       </c>
-      <c r="H48" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>11</v>
-      </c>
-      <c r="J48" t="n">
-        <v>20</v>
-      </c>
       <c r="K48" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N48" t="n">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.97439230769231</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|40</t>
+          <t>3|9|12|25|38|44|49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M49" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N49" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6667</v>
+        <v>35.4375</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|19</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
         <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="N50" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5417</v>
+        <v>35.3125</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>8|14|23|29|38|49|36</t>
+          <t>3|4|20|29|42|45|18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5199,7 +5199,7 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
         <v>6</v>
@@ -5208,16 +5208,16 @@
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L51" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N51" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.43140588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|10</t>
+          <t>5|6|24|34|39|45|13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L52" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M52" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.33336666666666</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|26</t>
+          <t>9|17|20|31|42|46|10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L53" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M53" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="N53" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.24564736842105</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|4|20|29|32|45|46</t>
+          <t>3|6|24|31|34|43|11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M54" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N54" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,16 +5544,16 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1667</v>
+        <v>34.9375</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>2|13|20|29|44|49|34</t>
+          <t>3|6|15|40|42|49|46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
+        <v>34</v>
+      </c>
+      <c r="L55" t="n">
         <v>38</v>
       </c>
-      <c r="L55" t="n">
-        <v>42</v>
-      </c>
       <c r="M55" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|17</t>
+          <t>3|5|20|34|38|39|4</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.94</v>
+        <v>73.72</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,23 +2629,23 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
+        <v>21</v>
+      </c>
+      <c r="L24" t="n">
         <v>25</v>
-      </c>
-      <c r="L24" t="n">
-        <v>33</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.94</v>
+        <v>47.72</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,13 +2719,13 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
         <v>21</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.94</v>
+        <v>42.72</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>6|10|13|21|25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.44</v>
+        <v>40.22</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,13 +2899,13 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.94</v>
+        <v>38.72</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5|8|14|25|27</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,32 +2989,32 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.94</v>
+        <v>37.72</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
         <v>6</v>
       </c>
-      <c r="I29" t="n">
-        <v>10</v>
-      </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
         <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.22571428571428</v>
+        <v>37.00571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,32 +3169,32 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
+        <v>21</v>
+      </c>
+      <c r="L30" t="n">
         <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.69</v>
+        <v>36.47</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.27333333333333</v>
+        <v>36.05333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|10|11|25|33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L32" t="n">
         <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.94</v>
+        <v>35.72</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>7|10|12|23|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,32 +3439,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.66727272727273</v>
+        <v>35.44727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>5|6|9|22|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N35" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.4375</v>
+        <v>48.625</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>2|19|24|31|40|47|10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="n">
         <v>9</v>
       </c>
-      <c r="I36" t="n">
-        <v>16</v>
-      </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
         <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N36" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.4375</v>
+        <v>43.625</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9|16|22|31|44|45|7</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
         <v>26</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M37" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="N37" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>40.9375</v>
+        <v>41.125</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9|11|17|26|38|40|35</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,34 +3925,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
+        <v>16</v>
+      </c>
+      <c r="J38" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" t="n">
+        <v>37</v>
+      </c>
+      <c r="L38" t="n">
+        <v>41</v>
+      </c>
+      <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" t="n">
-        <v>24</v>
-      </c>
-      <c r="K38" t="n">
-        <v>26</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
+        <v>163</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>38</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>141</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>44</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.4375</v>
+        <v>39.625</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>1|7|24|26|38|45|5</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -4023,10 +4023,10 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
@@ -4035,13 +4035,13 @@
         <v>33</v>
       </c>
       <c r="L39" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.4375</v>
+        <v>38.625</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|16|24|33|41|43|2</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -4124,22 +4124,22 @@
         <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
         <v>41</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N40" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.72321428571428</v>
+        <v>37.91071428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|19|24|39|41|42|7</t>
+          <t>2|9|24|31|41|44|32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -4219,7 +4219,7 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
@@ -4228,16 +4228,16 @@
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M41" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N41" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.1875</v>
+        <v>37.375</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1|19|24|38|40|45|42</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J42" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
+        <v>32</v>
+      </c>
+      <c r="M42" t="n">
         <v>48</v>
       </c>
-      <c r="M42" t="n">
-        <v>13</v>
-      </c>
       <c r="N42" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.77083333333333</v>
+        <v>36.95833333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>5|9|14|40|48|49|13</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="N43" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.4375</v>
+        <v>36.625</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|9|22|30|40|45|1</t>
+          <t>17|19|24|27|38|40|33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L44" t="n">
         <v>39</v>
       </c>
       <c r="M44" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="N44" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.16477272727273</v>
+        <v>36.35227272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>6|18|19|31|39|44|48</t>
+          <t>17|20|24|29|39|40|7</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L46" t="n">
+        <v>42</v>
+      </c>
+      <c r="M46" t="n">
         <v>38</v>
       </c>
-      <c r="M46" t="n">
-        <v>20</v>
-      </c>
       <c r="N46" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>35.9375</v>
+        <v>36.125</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>9|11|20|26|42|49|38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M47" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.74519230769231</v>
+        <v>35.93269230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|4|12|25|38|39|15</t>
+          <t>3|18|24|34|39|49|2</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
+        <v>34</v>
+      </c>
+      <c r="L48" t="n">
+        <v>39</v>
+      </c>
+      <c r="M48" t="n">
         <v>25</v>
       </c>
-      <c r="L48" t="n">
-        <v>38</v>
-      </c>
-      <c r="M48" t="n">
-        <v>49</v>
-      </c>
       <c r="N48" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.58035714285714</v>
+        <v>35.76785714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|9|12|25|38|44|49</t>
+          <t>3|12|20|34|39|45|25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5006,19 +5006,19 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
         <v>139</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.4375</v>
+        <v>35.625</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
         <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N50" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.3125</v>
+        <v>35.5</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|4|20|29|42|45|18</t>
+          <t>3|14|21|29|38|46|24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N51" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.20220588235294</v>
+        <v>35.38970588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>5|6|24|34|39|45|13</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
@@ -5297,34 +5297,34 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
         <v>20</v>
       </c>
       <c r="K52" t="n">
+        <v>29</v>
+      </c>
+      <c r="L52" t="n">
+        <v>40</v>
+      </c>
+      <c r="M52" t="n">
+        <v>4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>161</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>31</v>
-      </c>
-      <c r="L52" t="n">
-        <v>42</v>
-      </c>
-      <c r="M52" t="n">
-        <v>10</v>
-      </c>
-      <c r="N52" t="n">
-        <v>165</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>37</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.10416666666666</v>
+        <v>35.29166666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>9|17|20|31|42|46|10</t>
+          <t>11|19|20|29|40|42|4</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L53" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M53" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="N53" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.01644736842105</v>
+        <v>35.20394736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|11</t>
+          <t>3|12|23|34|39|40|48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M54" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="N54" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>34.9375</v>
+        <v>35.125</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|6|15|40|42|49|46</t>
+          <t>3|4|24|29|31|34|28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N55" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.86607142857143</v>
+        <v>35.05357142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|5|20|34|38|39|4</t>
+          <t>3|8|15|38|42|49|18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.58</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,25 +677,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.58</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -769,25 +769,25 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,28 +858,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.58</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2|9|19|31|34|2</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1001,19 +1001,19 @@
         <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>50.08</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1042,28 +1042,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>49.33</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|13</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1137,22 +1137,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>37</v>
+      </c>
+      <c r="M8" t="n">
         <v>12</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K8" t="n">
-        <v>29</v>
-      </c>
-      <c r="L8" t="n">
-        <v>45</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12|15|20|29|45|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
         <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
         <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.86571428571428</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|19|24|28|31|3</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>45.91333333333333</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|15|24|29|36|1</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|19|24|34|35|18</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.72</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,23 +2629,23 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" t="n">
         <v>10</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.72</v>
+        <v>47.9</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>7|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.72</v>
+        <v>42.9</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>6|10|13|21|25</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2812,20 +2812,20 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.22</v>
+        <v>40.4</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>4|5|6|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,13 +2899,13 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.72</v>
+        <v>38.9</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|13|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,32 +2989,32 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>3</v>
-      </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.72</v>
+        <v>37.9</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,13 +3079,13 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
         <v>4</v>
       </c>
-      <c r="I29" t="n">
-        <v>6</v>
-      </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.00571428571428</v>
+        <v>37.18571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3172,29 +3172,29 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
-        <v>14</v>
-      </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.47</v>
+        <v>36.65</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3262,20 +3262,20 @@
         <v>6</v>
       </c>
       <c r="I31" t="n">
+        <v>9</v>
+      </c>
+      <c r="J31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>11</v>
-      </c>
       <c r="K31" t="n">
+        <v>21</v>
+      </c>
+      <c r="L31" t="n">
         <v>25</v>
-      </c>
-      <c r="L31" t="n">
-        <v>33</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.05333333333333</v>
+        <v>36.23333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|10|11|25|33</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.72</v>
+        <v>35.9</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>7|10|12|23|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,32 +3439,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.44727272727273</v>
+        <v>35.62727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5|6|9|22|25</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L35" t="n">
         <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.625</v>
+        <v>48.75</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>2|19|24|31|40|47|10</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L36" t="n">
         <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.625</v>
+        <v>43.75</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>2|16|19|37|44|49|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N37" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,16 +3878,16 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.125</v>
+        <v>41.25</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>7|19|20|30|44|45|15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J38" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N38" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.625</v>
+        <v>39.75</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>5|9|24|30|44|45|32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N39" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.625</v>
+        <v>38.75</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
+        <v>26</v>
+      </c>
+      <c r="L40" t="n">
         <v>31</v>
       </c>
-      <c r="L40" t="n">
-        <v>41</v>
-      </c>
       <c r="M40" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.91071428571428</v>
+        <v>38.03571428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|32</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L41" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="N41" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.375</v>
+        <v>37.5</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M42" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N42" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.95833333333333</v>
+        <v>37.08333333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,34 +4415,34 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
+        <v>16</v>
+      </c>
+      <c r="J43" t="n">
         <v>19</v>
       </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
       <c r="K43" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L43" t="n">
+        <v>41</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>163</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>38</v>
-      </c>
-      <c r="M43" t="n">
-        <v>33</v>
-      </c>
-      <c r="N43" t="n">
-        <v>165</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>23</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.625</v>
+        <v>36.75</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17|19|24|27|38|40|33</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L44" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="N44" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,16 +4564,16 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.35227272727273</v>
+        <v>36.47727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17|20|24|29|39|40|7</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="N46" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,19 +4757,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.125</v>
+        <v>38.89285714285714</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>9|11|20|26|42|49|38</t>
+          <t>1|2|20|42|45|49|9</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="N47" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.93269230769231</v>
+        <v>36.25</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|18|24|34|39|49|2</t>
+          <t>3|8|23|38|44|49|40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
+        <v>31</v>
+      </c>
+      <c r="L48" t="n">
         <v>34</v>
       </c>
-      <c r="L48" t="n">
-        <v>39</v>
-      </c>
       <c r="M48" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.76785714285714</v>
+        <v>36.05769230769231</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|25</t>
+          <t>6|15|24|31|34|49|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
         <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M49" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="N49" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.625</v>
+        <v>35.75</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|12|20|34|39|45|24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L50" t="n">
         <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="N50" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5</v>
+        <v>35.625</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|14|21|29|38|46|24</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5202,7 +5202,7 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
@@ -5214,10 +5214,10 @@
         <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="N51" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.38970588235294</v>
+        <v>35.51470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
@@ -5348,7 +5348,7 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.29166666666666</v>
+        <v>35.41666666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L53" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M53" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.20394736842105</v>
+        <v>35.32894736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|23|34|39|40|48</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L54" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M54" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.125</v>
+        <v>35.25</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|4|24|29|31|34|28</t>
+          <t>10|19|20|28|35|45|5</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.05357142857143</v>
+        <v>35.17857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>5|11|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,25 +1505,25 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L12" t="n">
+        <v>52</v>
+      </c>
+      <c r="M12" t="n">
         <v>8</v>
       </c>
-      <c r="K12" t="n">
-        <v>44</v>
-      </c>
-      <c r="L12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M12" t="n">
-        <v>23</v>
-      </c>
       <c r="N12" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1560,16 +1560,16 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|23</t>
+          <t>1|4|44|49|52|56|8</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -1599,34 +1599,34 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
+        <v>31</v>
+      </c>
+      <c r="L13" t="n">
+        <v>37</v>
+      </c>
+      <c r="M13" t="n">
+        <v>28</v>
+      </c>
+      <c r="N13" t="n">
+        <v>157</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>43</v>
-      </c>
-      <c r="L13" t="n">
-        <v>47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>151</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>46</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1654,16 +1654,16 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2|3|8|43|47|48|12</t>
+          <t>6|12|22|31|37|49|28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M14" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1748,16 +1748,16 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2|17|23|27|40|44|32</t>
+          <t>13|14|29|32|35|46|6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -1790,22 +1790,22 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1842,16 +1842,16 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>4|7|27|39|44|48|17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>7</v>
       </c>
       <c r="J16" t="n">
         <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1936,16 +1936,16 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|7|29|33|40|46|13</t>
+          <t>1|2|29|40|42|49|34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1975,13 +1975,13 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
         <v>33</v>
@@ -1990,10 +1990,10 @@
         <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N17" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2030,16 +2030,16 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4|8|27|33|40|43|20</t>
+          <t>8|12|29|33|40|47|41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="N18" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2124,16 +2124,16 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L19" t="n">
         <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2218,16 +2218,16 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1|8|27|32|42|45|10</t>
+          <t>9|10|22|37|42|49|55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
         <v>30</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="M20" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="N20" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2312,16 +2312,16 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|17|19|30|42|49|24</t>
+          <t>7|9|22|30|33|46|55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="N21" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2406,16 +2406,16 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2|3|24|43|44|47|10</t>
+          <t>3|13|18|32|36|49|53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L22" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2500,16 +2500,16 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1|13|14|30|32|47|21</t>
+          <t>8|12|17|37|41|48|6</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.81</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|8</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
@@ -1608,16 +1608,16 @@
         <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,16 +1650,16 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.81</v>
+        <v>47.85</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6|12|22|31|37|49|28</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="N14" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,20 +1744,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.81</v>
+        <v>42.85</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13|14|29|32|35|46|6</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
+        <v>32</v>
+      </c>
+      <c r="L15" t="n">
         <v>39</v>
       </c>
-      <c r="L15" t="n">
-        <v>44</v>
-      </c>
       <c r="M15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.31</v>
+        <v>40.35</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|7|27|39|44|48|17</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.81</v>
+        <v>38.85</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1|2|29|40|42|49|34</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1975,22 +1975,22 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="N17" t="n">
         <v>169</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,16 +2026,16 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.81</v>
+        <v>37.85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8|12|29|33|40|47|41</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.09571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.56</v>
+        <v>36.6</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9|10|22|37|42|49|55</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L20" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.14333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7|9|22|30|33|46|55</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2351,13 +2351,13 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
         <v>32</v>
@@ -2366,10 +2366,10 @@
         <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,16 +2402,16 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.81</v>
+        <v>35.85</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3|13|18|32|36|49|53</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,16 +2496,16 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.53727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8|12|17|37|41|48|6</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.90000000000001</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.9</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -2731,11 +2731,11 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.9</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
         <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.4</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|5|6|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,19 +2899,19 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="J27" t="n">
-        <v>13</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.9</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|13|25|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
         <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.9</v>
+        <v>37.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.18571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,19 +3169,19 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.65</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.23333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" t="n">
         <v>9</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="J32" t="n">
-        <v>14</v>
-      </c>
       <c r="K32" t="n">
+        <v>21</v>
+      </c>
+      <c r="L32" t="n">
         <v>25</v>
-      </c>
-      <c r="L32" t="n">
-        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.9</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,32 +3439,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>36</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.62727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
         <v>26</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="N35" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.75</v>
+        <v>48.8667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
         <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
         <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.75</v>
+        <v>43.8667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|26</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
+        <v>16</v>
+      </c>
+      <c r="J37" t="n">
         <v>19</v>
       </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L37" t="n">
         <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.25</v>
+        <v>41.3667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>7|19|20|30|44|45|15</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -3925,34 +3925,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
+        <v>6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>143</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>32</v>
-      </c>
-      <c r="N38" t="n">
-        <v>157</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>40</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.75</v>
+        <v>39.8667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|32</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
+        <v>44</v>
+      </c>
+      <c r="M39" t="n">
         <v>31</v>
       </c>
-      <c r="M39" t="n">
-        <v>8</v>
-      </c>
       <c r="N39" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.75</v>
+        <v>38.8667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,7 +4121,7 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
         <v>19</v>
@@ -4136,10 +4136,10 @@
         <v>31</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.03571428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.5</v>
+        <v>37.6167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.08333333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,22 +4415,22 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
         <v>163</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.75</v>
+        <v>36.8667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
+        <v>31</v>
+      </c>
+      <c r="L44" t="n">
+        <v>41</v>
+      </c>
+      <c r="M44" t="n">
         <v>30</v>
       </c>
-      <c r="L44" t="n">
-        <v>31</v>
-      </c>
-      <c r="M44" t="n">
-        <v>41</v>
-      </c>
       <c r="N44" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.47727272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="N46" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,19 +4757,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.89285714285714</v>
+        <v>36.3667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|9</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>23</v>
       </c>
       <c r="K47" t="n">
+        <v>34</v>
+      </c>
+      <c r="L47" t="n">
         <v>38</v>
       </c>
-      <c r="L47" t="n">
-        <v>44</v>
-      </c>
       <c r="M47" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.25</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|40</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>15</v>
@@ -4914,7 +4914,7 @@
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
         <v>34</v>
@@ -4923,7 +4923,7 @@
         <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.05769230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>6|15|24|31|34|49|27</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
@@ -5009,19 +5009,19 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.75</v>
+        <v>35.8667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|24</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5107,19 +5107,19 @@
         <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.625</v>
+        <v>35.7417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N51" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.51470588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.41666666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11|19|20|29|40|42|4</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
+        <v>32</v>
+      </c>
+      <c r="L53" t="n">
         <v>38</v>
       </c>
-      <c r="L53" t="n">
-        <v>44</v>
-      </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N53" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.32894736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N54" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.25</v>
+        <v>35.3667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10|19|20|28|35|45|5</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -5591,22 +5591,22 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
         <v>11</v>
       </c>
-      <c r="J55" t="n">
-        <v>20</v>
-      </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M55" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
         <v>149</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.17857142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>5|11|20|32|37|44|12</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
         <v>12</v>
-      </c>
-      <c r="J24" t="n">
-        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,16 +2645,16 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2818,14 +2818,14 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,23 +2899,23 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L28" t="n">
         <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" t="n">
         <v>25</v>
-      </c>
-      <c r="L29" t="n">
-        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>4|10|15|21|25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,19 +3169,19 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
-        <v>15</v>
-      </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
       </c>
       <c r="K31" t="n">
+        <v>21</v>
+      </c>
+      <c r="L31" t="n">
         <v>25</v>
-      </c>
-      <c r="L31" t="n">
-        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>5|6|10|21|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.86669999999999</v>
+        <v>74.9333</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>17</v>
-      </c>
-      <c r="I35" t="n">
-        <v>19</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.8667</v>
+        <v>48.9333</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>1|17|24|28|41|44|47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
         <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
         <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.8667</v>
+        <v>43.9333</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>2|16|19|37|44|49|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
         <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.3667</v>
+        <v>41.4333</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>7|19|20|30|44|45|15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3928,22 +3928,22 @@
         <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.8667</v>
+        <v>39.9333</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M39" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.8667</v>
+        <v>38.9333</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L40" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.15241428571429</v>
+        <v>38.21901428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.6167</v>
+        <v>37.6833</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
+        <v>40</v>
+      </c>
+      <c r="L42" t="n">
+        <v>43</v>
+      </c>
+      <c r="M42" t="n">
         <v>33</v>
       </c>
-      <c r="L42" t="n">
-        <v>38</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4</v>
-      </c>
       <c r="N42" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.20003333333333</v>
+        <v>37.26663333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L43" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N43" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.8667</v>
+        <v>36.9333</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
+        <v>30</v>
+      </c>
+      <c r="L44" t="n">
         <v>31</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>41</v>
       </c>
-      <c r="M44" t="n">
-        <v>30</v>
-      </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.59397272727273</v>
+        <v>36.66057272727272</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.86669999999999</v>
+        <v>74.9333</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J46" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.3667</v>
+        <v>36.4333</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>6|11|20|31|45|46|9</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
@@ -4807,25 +4807,25 @@
         <v>12</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M47" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N47" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.17439230769231</v>
+        <v>36.24099230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>6|11|20|38|39|49|8</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L48" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.00955714285714</v>
+        <v>36.07615714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5009,19 +5009,19 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M49" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="N49" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.8667</v>
+        <v>35.9333</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|12|23|25|30|38|49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
@@ -5101,10 +5101,10 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
         <v>20</v>
@@ -5113,10 +5113,10 @@
         <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N50" t="n">
         <v>149</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.7417</v>
+        <v>35.8083</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>6|9|20|31|34|49|16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M51" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="N51" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.63140588235294</v>
+        <v>35.69800588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L52" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.53336666666667</v>
+        <v>35.59996666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>5|11|20|31|44|46|8</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -5401,19 +5401,19 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K53" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
         <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N53" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.44564736842106</v>
+        <v>35.51224736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|20|22|29|38|39|18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
+        <v>32</v>
+      </c>
+      <c r="L54" t="n">
         <v>37</v>
       </c>
-      <c r="L54" t="n">
-        <v>38</v>
-      </c>
       <c r="M54" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="N54" t="n">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.3667</v>
+        <v>35.4333</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|5|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="L55" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="N55" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.29527142857143</v>
+        <v>35.36187142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|11|20|28|31|44|35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -585,25 +585,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -633,19 +633,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>60.57</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>9|15|20|38|43|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,25 +677,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>55.57</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>2|22|23|31|43|17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>43</v>
+      </c>
+      <c r="M4" t="n">
         <v>11</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -817,19 +817,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>50.07</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,28 +858,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>49.32</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>48.90333333333333</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>9|19|20|30|43|3</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1042,28 +1042,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
         <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1093,19 +1093,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.57</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1152,7 +1152,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.57</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>7|19|24|34|37|13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" t="n">
         <v>13</v>
       </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>28</v>
-      </c>
-      <c r="L9" t="n">
-        <v>39</v>
-      </c>
-      <c r="M9" t="n">
-        <v>18</v>
-      </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>47.57</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>8|9|22|29|35|13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
@@ -1330,16 +1330,16 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.85571428571428</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>14|19|24|29|35|5</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
         <v>13</v>
-      </c>
-      <c r="I11" t="n">
-        <v>15</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.29727272727273</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:37</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.9333</v>
+        <v>74.6875</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|42</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L35" t="n">
         <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N35" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.9333</v>
+        <v>48.6875</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|17|24|28|41|44|47</t>
+          <t>5|13|24|30|41|48|28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="N36" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.9333</v>
+        <v>43.6875</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|26</t>
+          <t>17|19|24|30|39|40|45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N37" t="n">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.4333</v>
+        <v>41.1875</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>7|19|20|30|44|45|15</t>
+          <t>3|9|14|26|40|41|11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" t="n">
+        <v>27</v>
+      </c>
+      <c r="L38" t="n">
+        <v>38</v>
+      </c>
+      <c r="M38" t="n">
         <v>18</v>
       </c>
-      <c r="J38" t="n">
-        <v>19</v>
-      </c>
-      <c r="K38" t="n">
-        <v>30</v>
-      </c>
-      <c r="L38" t="n">
-        <v>44</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3</v>
-      </c>
       <c r="N38" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.9333</v>
+        <v>39.6875</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>14|17|24|27|38|41|18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L39" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M39" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N39" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.9333</v>
+        <v>38.6875</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|16|24|34|39|45|17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="N40" t="n">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.21901428571429</v>
+        <v>37.97321428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>3|9|13|26|30|40|41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" t="n">
+        <v>13</v>
+      </c>
+      <c r="J41" t="n">
         <v>17</v>
       </c>
-      <c r="I41" t="n">
-        <v>19</v>
-      </c>
-      <c r="J41" t="n">
-        <v>24</v>
-      </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L41" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N41" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.6833</v>
+        <v>37.4375</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>10|13|17|40|41|44|30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M42" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.26663333333333</v>
+        <v>37.02083333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>17|19|24|26|34|39|3</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
@@ -4415,22 +4415,22 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
         <v>41</v>
       </c>
       <c r="M43" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="N43" t="n">
         <v>151</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.9333</v>
+        <v>36.6875</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>1|14|24|26|41|45|9</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M44" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="N44" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.66057272727272</v>
+        <v>36.41477272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>5|14|24|38|43|45|9</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.9333</v>
+        <v>74.6875</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|42</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4760,7 +4760,7 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.4333</v>
+        <v>36.1875</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4858,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.24099230769231</v>
+        <v>35.99519230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4956,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.07615714285714</v>
+        <v>35.83035714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5054,7 +5054,7 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.9333</v>
+        <v>35.6875</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5152,7 +5152,7 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.8083</v>
+        <v>35.5625</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5250,7 +5250,7 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.69800588235294</v>
+        <v>35.45220588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5348,7 +5348,7 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.59996666666666</v>
+        <v>35.35416666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5446,7 +5446,7 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.51224736842106</v>
+        <v>35.26644736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.4333</v>
+        <v>35.1875</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5642,7 +5642,7 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.36187142857143</v>
+        <v>35.11607142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1517,19 +1517,19 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="N12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>55</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.84999999999999</v>
+        <v>73.86</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>1|4|44|49|51|56|29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,34 +1599,34 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
         <v>32</v>
       </c>
       <c r="L13" t="n">
+        <v>35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>165</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>37</v>
-      </c>
-      <c r="M13" t="n">
-        <v>21</v>
-      </c>
-      <c r="N13" t="n">
-        <v>163</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>38</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,16 +1650,16 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.85</v>
+        <v>47.86</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>12|13|24|32|35|49|11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M14" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1744,20 +1744,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.85</v>
+        <v>42.86</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>8|11|17|32|36|49|50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1790,22 +1790,22 @@
         <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="N15" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1838,16 +1838,16 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.35</v>
+        <v>40.36</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>8|12|29|33|40|47|41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="N16" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.85</v>
+        <v>38.86</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>7|8|22|32|37|49|52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1975,34 +1975,34 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L17" t="n">
+        <v>37</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>149</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
         <v>44</v>
-      </c>
-      <c r="M17" t="n">
-        <v>27</v>
-      </c>
-      <c r="N17" t="n">
-        <v>169</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>40</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.85</v>
+        <v>37.86</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>1|12|22|32|37|45|8</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N18" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.13571428571429</v>
+        <v>37.14571428571428</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -2163,13 +2163,13 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
         <v>32</v>
@@ -2178,10 +2178,10 @@
         <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.6</v>
+        <v>36.61</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>12|13|28|32|41|49|2</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
         <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N20" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.18333333333334</v>
+        <v>36.19333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M21" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,16 +2402,16 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.85</v>
+        <v>35.86</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>6|12|26|31|35|49|25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2445,34 +2445,34 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L22" t="n">
+        <v>36</v>
+      </c>
+      <c r="M22" t="n">
+        <v>53</v>
+      </c>
+      <c r="N22" t="n">
+        <v>143</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
         <v>40</v>
-      </c>
-      <c r="M22" t="n">
-        <v>15</v>
-      </c>
-      <c r="N22" t="n">
-        <v>151</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.57727272727273</v>
+        <v>35.58727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>6|9|15|31|36|46|53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
@@ -2645,16 +2645,16 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.82</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>7|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.84</v>
+        <v>42.82</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
-      </c>
-      <c r="J26" t="n">
-        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.34</v>
+        <v>40.82</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.84</v>
+        <v>40.32</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>10|11|14|25|33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.84</v>
+        <v>38.82</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
@@ -3088,14 +3088,14 @@
         <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.12571428571429</v>
+        <v>37.10571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4|10|15|21|25</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.59</v>
+        <v>36.57</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,32 +3259,32 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L31" t="n">
         <v>25</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.17333333333333</v>
+        <v>36.15333333333334</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5|6|10|21|25</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,19 +3349,19 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K32" t="n">
         <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.84</v>
+        <v>35.82</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>10|11|16|25|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>35.54727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.6875</v>
+        <v>74.7333</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3682,7 +3682,7 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6875</v>
+        <v>48.7333</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3780,7 +3780,7 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6875</v>
+        <v>43.7333</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3878,7 +3878,7 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1875</v>
+        <v>41.2333</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3976,7 +3976,7 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6875</v>
+        <v>39.7333</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4074,7 +4074,7 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6875</v>
+        <v>38.7333</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4172,7 +4172,7 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.97321428571428</v>
+        <v>38.01901428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4270,7 +4270,7 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4375</v>
+        <v>37.4833</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4368,7 +4368,7 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.02083333333333</v>
+        <v>37.06663333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4466,7 +4466,7 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6875</v>
+        <v>36.7333</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4564,7 +4564,7 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.41477272727273</v>
+        <v>36.46057272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.6875</v>
+        <v>74.7333</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M46" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="N46" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1875</v>
+        <v>36.2333</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>6|11|20|31|45|46|9</t>
+          <t>3|5|24|38|46|49|43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4807,25 +4807,25 @@
         <v>12</v>
       </c>
       <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
         <v>6</v>
-      </c>
-      <c r="I47" t="n">
-        <v>11</v>
       </c>
       <c r="J47" t="n">
         <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M47" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.99519230769231</v>
+        <v>36.04099230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>6|11|20|38|39|49|8</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="N48" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.83035714285714</v>
+        <v>35.87615714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|10|24|33|38|49|35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -5003,25 +5003,25 @@
         <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J49" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
         <v>49</v>
       </c>
       <c r="N49" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6875</v>
+        <v>35.7333</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|23|25|30|38|49</t>
+          <t>9|11|20|32|38|45|49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L50" t="n">
         <v>34</v>
       </c>
       <c r="M50" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N50" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5625</v>
+        <v>35.6083</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>6|9|20|31|34|49|16</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M51" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="N51" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.45220588235294</v>
+        <v>35.49800588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>5|6|24|31|32|37|40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L52" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="N52" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.35416666666666</v>
+        <v>35.39996666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>5|11|20|31|44|46|8</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5395,25 +5395,25 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
+        <v>11</v>
+      </c>
+      <c r="J53" t="n">
         <v>20</v>
       </c>
-      <c r="J53" t="n">
-        <v>22</v>
-      </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M53" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="N53" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.26644736842105</v>
+        <v>35.31224736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|20|22|29|38|39|18</t>
+          <t>2|11|20|32|35|45|30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N54" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1875</v>
+        <v>35.2333</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|5|20|32|37|44|12</t>
+          <t>2|13|24|37|38|49|28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
         <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M55" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="N55" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5642,16 +5642,16 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.11607142857143</v>
+        <v>35.16187142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|11|20|28|31|44|35</t>
+          <t>3|5|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|30</t>
+          <t>1|3|5|44|46|49|46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L35" t="n">
         <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N35" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,16 +3682,16 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.7333</v>
+        <v>48.6</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|28</t>
+          <t>9|14|17|40|41|48|29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3729,10 +3729,10 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
@@ -3741,13 +3741,13 @@
         <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="N36" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.7333</v>
+        <v>43.6</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17|19|24|30|39|40|45</t>
+          <t>5|13|24|30|41|48|28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L37" t="n">
         <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="N37" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.2333</v>
+        <v>41.1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>3|9|14|26|40|41|11</t>
+          <t>9|16|19|31|40|44|42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="N38" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.7333</v>
+        <v>39.6</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14|17|24|27|38|41|18</t>
+          <t>17|19|24|30|39|40|45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M39" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.7333</v>
+        <v>38.6</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|16|24|34|39|45|17</t>
+          <t>13|17|20|30|40|41|6</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N40" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.01901428571428</v>
+        <v>37.88571428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>3|9|13|26|30|40|41</t>
+          <t>9|16|22|31|44|45|37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
+        <v>19</v>
+      </c>
+      <c r="J41" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" t="n">
+        <v>26</v>
+      </c>
+      <c r="L41" t="n">
+        <v>31</v>
+      </c>
+      <c r="M41" t="n">
         <v>13</v>
       </c>
-      <c r="J41" t="n">
-        <v>17</v>
-      </c>
-      <c r="K41" t="n">
-        <v>40</v>
-      </c>
-      <c r="L41" t="n">
-        <v>41</v>
-      </c>
-      <c r="M41" t="n">
-        <v>30</v>
-      </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4833</v>
+        <v>37.35</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10|13|17|40|41|44|30</t>
+          <t>14|19|24|26|31|45|13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4329,13 +4329,13 @@
         <v>26</v>
       </c>
       <c r="L42" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.06663333333333</v>
+        <v>36.93333333333334</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17|19|24|26|34|39|3</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
@@ -4415,34 +4415,34 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L43" t="n">
+        <v>40</v>
+      </c>
+      <c r="M43" t="n">
+        <v>48</v>
+      </c>
+      <c r="N43" t="n">
+        <v>167</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>41</v>
-      </c>
-      <c r="M43" t="n">
-        <v>9</v>
-      </c>
-      <c r="N43" t="n">
-        <v>151</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>44</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.7333</v>
+        <v>36.6</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|14|24|26|41|45|9</t>
+          <t>6|19|24|31|40|47|48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
@@ -4513,22 +4513,22 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
+        <v>33</v>
+      </c>
+      <c r="L44" t="n">
         <v>38</v>
       </c>
-      <c r="L44" t="n">
-        <v>43</v>
-      </c>
       <c r="M44" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
         <v>169</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.46057272727273</v>
+        <v>36.32727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|14|24|38|43|45|9</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|30</t>
+          <t>1|3|5|44|46|49|46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,10 +4709,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
@@ -4721,13 +4721,13 @@
         <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.2333</v>
+        <v>36.1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|5|24|38|46|49|43</t>
+          <t>1|3|24|38|45|46|44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
@@ -4813,19 +4813,19 @@
         <v>6</v>
       </c>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L47" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="N47" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.04099230769231</v>
+        <v>35.90769230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L48" t="n">
         <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="N48" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.87615714285714</v>
+        <v>35.74285714285715</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|10|24|33|38|49|35</t>
+          <t>3|12|13|34|38|45|49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5003,25 +5003,25 @@
         <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N49" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.7333</v>
+        <v>35.6</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>9|11|20|32|38|45|49</t>
+          <t>3|6|21|34|40|49|41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L50" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M50" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="N50" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.6083</v>
+        <v>35.475</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>3|6|24|25|31|44|15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
@@ -5199,7 +5199,7 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>6</v>
@@ -5208,25 +5208,25 @@
         <v>24</v>
       </c>
       <c r="K51" t="n">
+        <v>25</v>
+      </c>
+      <c r="L51" t="n">
+        <v>33</v>
+      </c>
+      <c r="M51" t="n">
+        <v>30</v>
+      </c>
+      <c r="N51" t="n">
+        <v>125</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="n">
         <v>31</v>
-      </c>
-      <c r="L51" t="n">
-        <v>32</v>
-      </c>
-      <c r="M51" t="n">
-        <v>40</v>
-      </c>
-      <c r="N51" t="n">
-        <v>135</v>
-      </c>
-      <c r="O51" t="n">
-        <v>3</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>32</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.49800588235294</v>
+        <v>35.36470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>5|6|24|31|32|37|40</t>
+          <t>3|6|24|25|33|34|30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M52" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N52" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.39996666666666</v>
+        <v>35.26666666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>6|9|18|33|40|49|17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5395,7 +5395,7 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I53" t="n">
         <v>11</v>
@@ -5404,16 +5404,16 @@
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L53" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M53" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="N53" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.31224736842105</v>
+        <v>35.17894736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>2|11|20|32|35|45|30</t>
+          <t>6|11|20|38|43|49|41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M54" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="N54" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.2333</v>
+        <v>35.1</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|28</t>
+          <t>9|18|24|25|33|42|49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
@@ -5591,22 +5591,22 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L55" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M55" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="N55" t="n">
         <v>141</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.16187142857143</v>
+        <v>35.02857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|5|20|32|37|44|12</t>
+          <t>6|9|24|31|34|37|48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.59999999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|46</t>
+          <t>1|3|5|44|46|49|37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J35" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L35" t="n">
         <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,16 +3682,16 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6</v>
+        <v>48.6667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9|14|17|40|41|48|29</t>
+          <t>5|13|24|30|41|48|28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3732,22 +3732,22 @@
         <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="N36" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6</v>
+        <v>43.6667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|28</t>
+          <t>5|16|17|26|38|41|48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
+        <v>26</v>
+      </c>
+      <c r="L37" t="n">
         <v>31</v>
       </c>
-      <c r="L37" t="n">
-        <v>40</v>
-      </c>
       <c r="M37" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="N37" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1</v>
+        <v>41.1667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9|16|19|31|40|44|42</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,22 +3925,22 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
+        <v>16</v>
+      </c>
+      <c r="I38" t="n">
         <v>17</v>
-      </c>
-      <c r="I38" t="n">
-        <v>19</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M38" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="N38" t="n">
         <v>169</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6</v>
+        <v>39.6667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17|19|24|30|39|40|45</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6</v>
+        <v>38.6667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13|17|20|30|40|41|6</t>
+          <t>1|17|24|26|38|39|6</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
         <v>9</v>
       </c>
-      <c r="I40" t="n">
-        <v>16</v>
-      </c>
       <c r="J40" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N40" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.88571428571429</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>9|16|22|31|44|45|37</t>
+          <t>3|9|24|32|40|43|41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
@@ -4219,22 +4219,22 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L41" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N41" t="n">
         <v>159</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.35</v>
+        <v>37.4167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14|19|24|26|31|45|13</t>
+          <t>2|16|24|31|39|47|14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
+        <v>9</v>
+      </c>
+      <c r="I42" t="n">
         <v>17</v>
       </c>
-      <c r="I42" t="n">
-        <v>19</v>
-      </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K42" t="n">
+        <v>31</v>
+      </c>
+      <c r="L42" t="n">
+        <v>40</v>
+      </c>
+      <c r="M42" t="n">
         <v>26</v>
       </c>
-      <c r="L42" t="n">
-        <v>31</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4</v>
-      </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.93333333333334</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>9|17|20|31|40|44|26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
+        <v>13</v>
+      </c>
+      <c r="J43" t="n">
         <v>19</v>
       </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
       <c r="K43" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L43" t="n">
         <v>40</v>
       </c>
       <c r="M43" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6</v>
+        <v>36.6667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|47|48</t>
+          <t>9|13|19|34|40|44|6</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -4513,22 +4513,22 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L44" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N44" t="n">
         <v>169</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.32727272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>5|14|24|38|43|45|9</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.59999999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|46</t>
+          <t>1|3|5|44|46|49|37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L46" t="n">
         <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="N46" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1</v>
+        <v>36.1667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|3|24|38|45|46|44</t>
+          <t>11|18|20|29|45|46|27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L47" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N47" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.90769230769231</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>3|12|14|37|38|39|13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
+        <v>31</v>
+      </c>
+      <c r="L48" t="n">
         <v>34</v>
       </c>
-      <c r="L48" t="n">
-        <v>38</v>
-      </c>
       <c r="M48" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="N48" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,16 +4956,16 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.74285714285715</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|12|13|34|38|45|49</t>
+          <t>15|20|24|31|34|45|9</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N49" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6</v>
+        <v>35.6667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|6|21|34|40|49|41</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -5107,19 +5107,19 @@
         <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L50" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M50" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.475</v>
+        <v>35.5417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|24|25|31|44|15</t>
+          <t>3|6|18|38|43|49|2</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L51" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M51" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N51" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.36470588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|24|25|33|34|30</t>
+          <t>2|3|24|29|36|49|15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5300,19 +5300,19 @@
         <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M52" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N52" t="n">
         <v>155</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.26666666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>6|9|18|33|40|49|17</t>
+          <t>6|19|20|31|35|44|15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
@@ -5395,25 +5395,25 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
         <v>6</v>
       </c>
-      <c r="I53" t="n">
-        <v>11</v>
-      </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
+        <v>32</v>
+      </c>
+      <c r="L53" t="n">
         <v>38</v>
       </c>
-      <c r="L53" t="n">
-        <v>43</v>
-      </c>
       <c r="M53" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="N53" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.17894736842106</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>6|11|20|38|43|49|41</t>
+          <t>3|6|19|32|38|49|24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" t="n">
         <v>9</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>18</v>
       </c>
-      <c r="J54" t="n">
-        <v>24</v>
-      </c>
       <c r="K54" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M54" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N54" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1</v>
+        <v>35.1667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>9|18|24|25|33|42|49</t>
+          <t>3|9|18|38|40|49|36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
         <v>6</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9</v>
-      </c>
-      <c r="J55" t="n">
-        <v>24</v>
       </c>
       <c r="K55" t="n">
         <v>31</v>
       </c>
       <c r="L55" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M55" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="N55" t="n">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.02857142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>6|9|24|31|34|37|48</t>
+          <t>1|3|6|31|38|46|15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.81999999999999</v>
+        <v>73.86</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.82</v>
+        <v>47.86</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -2731,11 +2731,11 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.82</v>
+        <v>42.86</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>9</v>
@@ -2821,11 +2821,11 @@
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.82</v>
+        <v>40.36</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>4|9|10|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="I27" t="n">
-        <v>11</v>
-      </c>
-      <c r="J27" t="n">
-        <v>14</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.32</v>
+        <v>38.86</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10|11|14|25|33</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.82</v>
+        <v>38.86</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>10|12|13|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="n">
-        <v>15</v>
-      </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
         <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.10571428571428</v>
+        <v>37.86</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>6|7|10|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
         <v>9</v>
       </c>
-      <c r="I30" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" t="n">
-        <v>14</v>
-      </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.57</v>
+        <v>37.14571428571428</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L31" t="n">
         <v>25</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
@@ -3284,7 +3284,7 @@
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.15333333333334</v>
+        <v>36.61</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>6|10|12|21|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,16 +3346,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
         <v>10</v>
-      </c>
-      <c r="I32" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>16</v>
       </c>
       <c r="K32" t="n">
         <v>25</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.82</v>
+        <v>36.19333333333333</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10|11|16|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
         <v>25</v>
@@ -3455,13 +3455,13 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>23</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.54727272727273</v>
+        <v>35.58727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>4|6|12|25|27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|37</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I35" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="N35" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6667</v>
+        <v>48.8</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|28</t>
+          <t>14|19|24|31|40|41|45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M36" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6667</v>
+        <v>43.8</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|16|17|26|38|41|48</t>
+          <t>16|17|19|31|36|44|1</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -3878,7 +3878,7 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1667</v>
+        <v>41.3</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3976,7 +3976,7 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6667</v>
+        <v>39.8</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6667</v>
+        <v>38.8</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>1|17|24|26|38|39|6</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L40" t="n">
         <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.95241428571428</v>
+        <v>38.08571428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>3|9|24|32|40|43|41</t>
+          <t>5|6|13|30|40|41|17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L41" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4167</v>
+        <v>37.55</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2|16|24|31|39|47|14</t>
+          <t>5|16|17|34|36|49|8</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -4323,19 +4323,19 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M42" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="N42" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.00003333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|17|20|31|40|44|26</t>
+          <t>9|17|24|26|34|41|12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="N43" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6667</v>
+        <v>36.8</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>9|13|19|34|40|44|6</t>
+          <t>6|19|24|26|33|41|47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L44" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.39397272727273</v>
+        <v>36.52727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|14|24|38|43|45|9</t>
+          <t>9|13|19|34|40|44|6</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|37</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M46" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N46" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1667</v>
+        <v>36.3</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11|18|20|29|45|46|27</t>
+          <t>3|5|24|38|46|49|44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M47" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="N47" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.97439230769231</v>
+        <v>36.1076923076923</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|12|14|37|38|39|13</t>
+          <t>3|18|24|29|34|39|27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L48" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M48" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="N48" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.80955714285714</v>
+        <v>35.94285714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15|20|24|31|34|45|9</t>
+          <t>3|5|24|36|37|40|49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M49" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N49" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6667</v>
+        <v>35.8</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|6|20|29|44|45|23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L50" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5417</v>
+        <v>35.675</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|18|38|43|49|2</t>
+          <t>1|11|20|40|44|45|3</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N51" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,16 +5250,16 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.43140588235294</v>
+        <v>35.56470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2|3|24|29|36|49|15</t>
+          <t>6|9|24|31|44|49|20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" t="n">
         <v>6</v>
       </c>
-      <c r="I52" t="n">
-        <v>19</v>
-      </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L52" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M52" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="N52" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.33336666666666</v>
+        <v>35.46666666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>6|19|20|31|35|44|15</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5398,13 +5398,13 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L53" t="n">
         <v>38</v>
@@ -5413,7 +5413,7 @@
         <v>24</v>
       </c>
       <c r="N53" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.24564736842105</v>
+        <v>35.37894736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|6|19|32|38|49|24</t>
+          <t>3|11|20|28|38|45|24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
+        <v>31</v>
+      </c>
+      <c r="L54" t="n">
+        <v>44</v>
+      </c>
+      <c r="M54" t="n">
         <v>38</v>
       </c>
-      <c r="L54" t="n">
-        <v>40</v>
-      </c>
-      <c r="M54" t="n">
-        <v>36</v>
-      </c>
       <c r="N54" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1667</v>
+        <v>35.3</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|9|18|38|40|49|36</t>
+          <t>1|11|20|31|44|46|38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K55" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
         <v>38</v>
       </c>
       <c r="M55" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N55" t="n">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>35.22857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>1|3|6|31|38|46|15</t>
+          <t>3|6|19|32|38|49|24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -585,25 +585,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
         <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M2" t="n">
         <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -636,16 +636,16 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.57</v>
+        <v>60.55</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9|15|20|38|43|18</t>
+          <t>7|13|20|34|41|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -728,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.57</v>
+        <v>55.55</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -769,13 +769,13 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
         <v>29</v>
@@ -784,10 +784,10 @@
         <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -817,19 +817,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>50.07</v>
+        <v>53.05</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,28 +858,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -912,16 +912,16 @@
         <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>49.32</v>
+        <v>50.55</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>5|21|22|29|38|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>48.90333333333333</v>
+        <v>49.83571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1048,22 +1048,22 @@
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.57</v>
+        <v>48.55</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>15|22|25|31|36|5</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -1152,7 +1152,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1185,19 +1185,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.57</v>
+        <v>46.3</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|13</t>
+          <t>7|19|24|34|37|16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1280,16 +1280,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.57</v>
+        <v>45.88333333333333</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8|9|22|29|35|13</t>
+          <t>9|15|24|29|36|1</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.85571428571428</v>
+        <v>45.55</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14|19|24|29|35|5</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1413,25 +1413,25 @@
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.29727272727273</v>
+        <v>45.27727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>9|20|25|26|29|17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.86</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.86</v>
+        <v>47.96</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.86</v>
+        <v>42.96</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
+        <v>21</v>
+      </c>
+      <c r="L26" t="n">
         <v>25</v>
-      </c>
-      <c r="L26" t="n">
-        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.36</v>
+        <v>40.46</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|9|10|25|35</t>
+          <t>5|10|12|21|25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
@@ -2911,11 +2911,11 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.86</v>
+        <v>38.96</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>6|7|10|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,26 +2986,26 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="n">
         <v>10</v>
-      </c>
-      <c r="I28" t="n">
-        <v>12</v>
-      </c>
-      <c r="J28" t="n">
-        <v>13</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.86</v>
+        <v>38.96</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10|12|13|25|35</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.86</v>
+        <v>37.96</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6|7|10|25|27</t>
+          <t>10|12|13|25|35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3172,20 +3172,20 @@
         <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
         <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.14571428571428</v>
+        <v>37.24571428571429</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>5|8|10|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,32 +3259,32 @@
         <v>7</v>
       </c>
       <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
         <v>6</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10</v>
       </c>
       <c r="J31" t="n">
         <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.61</v>
+        <v>36.71</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|10|12|21|25</t>
+          <t>3|6|12|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,16 +3349,16 @@
         <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L32" t="n">
         <v>27</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.19333333333333</v>
+        <v>36.29333333333334</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,32 +3439,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
+        <v>21</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.58727272727273</v>
+        <v>35.68727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|6|12|25|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.8</v>
+        <v>74.5333</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3682,7 +3682,7 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.8</v>
+        <v>48.5333</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3729,10 +3729,10 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
         <v>19</v>
@@ -3741,13 +3741,13 @@
         <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N36" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.8</v>
+        <v>43.5333</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16|17|19|31|36|44|1</t>
+          <t>9|18|19|31|40|44|24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3827,10 +3827,10 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
         <v>24</v>
@@ -3839,13 +3839,13 @@
         <v>26</v>
       </c>
       <c r="L37" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N37" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,16 +3878,16 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.3</v>
+        <v>41.0333</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|9|24|26|44|45|42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L38" t="n">
         <v>38</v>
       </c>
       <c r="M38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N38" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.8</v>
+        <v>39.5333</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>7|19|24|31|38|40|15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K39" t="n">
         <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N39" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.8</v>
+        <v>38.5333</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>5|6|13|30|40|41|16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L40" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
         <v>17</v>
       </c>
       <c r="N40" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.08571428571428</v>
+        <v>37.81901428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>5|6|13|30|40|41|17</t>
+          <t>6|9|19|42|44|45|17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L41" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M41" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="N41" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.55</v>
+        <v>37.2833</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>5|16|17|34|36|49|8</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4320,22 +4320,22 @@
         <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L42" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M42" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N42" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4368,16 +4368,16 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.13333333333333</v>
+        <v>36.86663333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|17|24|26|34|41|12</t>
+          <t>9|13|16|38|40|41|35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L43" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M43" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="N43" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.8</v>
+        <v>36.5333</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>6|19|24|26|33|41|47</t>
+          <t>3|17|20|40|41|48|10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L44" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N44" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.52727272727273</v>
+        <v>36.26057272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>9|13|19|34|40|44|6</t>
+          <t>16|17|24|29|31|34|10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.8</v>
+        <v>74.5333</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4712,22 +4712,22 @@
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
         <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M46" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.3</v>
+        <v>36.0333</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|5|24|38|46|49|44</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N47" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.1076923076923</v>
+        <v>35.8409923076923</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|18|24|29|34|39|27</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L48" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.94285714285714</v>
+        <v>35.67615714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|5|24|36|37|40|49</t>
+          <t>1|11|20|40|44|45|3</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K49" t="n">
         <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N49" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.8</v>
+        <v>35.5333</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|6|20|29|44|45|23</t>
+          <t>3|20|22|29|38|39|18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="N50" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.675</v>
+        <v>35.4083</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>1|11|20|40|44|45|3</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K51" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L51" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="N51" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.56470588235294</v>
+        <v>35.29800588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>6|9|24|31|44|49|20</t>
+          <t>3|12|13|34|38|45|49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I52" t="n">
         <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M52" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N52" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.46666666666667</v>
+        <v>35.19996666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>5|6|20|31|44|45|11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M53" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N53" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.37894736842105</v>
+        <v>35.11224736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|11|20|28|38|45|24</t>
+          <t>3|20|24|29|34|49|8</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M54" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="N54" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.3</v>
+        <v>35.0333</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>1|11|20|31|44|46|38</t>
+          <t>3|4|20|29|42|45|19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J55" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M55" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="N55" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.22857142857143</v>
+        <v>34.96187142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|6|19|32|38|49|24</t>
+          <t>3|15|24|25|36|42|10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -1520,19 +1520,19 @@
         <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="N12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.86</v>
+        <v>73.84</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1|4|44|49|51|56|29</t>
+          <t>2|4|44|49|51|56|47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
         <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="N13" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.86</v>
+        <v>47.84</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12|13|24|32|35|49|11</t>
+          <t>1|11|27|32|38|48|46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="N14" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,20 +1744,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.86</v>
+        <v>42.84</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8|11|17|32|36|49|50</t>
+          <t>3|9|23|30|44|48|37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M15" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="N15" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.36</v>
+        <v>40.34</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8|12|29|33|40|47|41</t>
+          <t>9|13|21|32|36|46|11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="N16" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.86</v>
+        <v>38.84</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7|8|22|32|37|49|52</t>
+          <t>5|8|24|43|44|45|38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -1975,34 +1975,34 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
         <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L17" t="n">
+        <v>39</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>157</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
         <v>37</v>
-      </c>
-      <c r="M17" t="n">
-        <v>8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>149</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>44</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,16 +2026,16 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.86</v>
+        <v>37.84</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1|12|22|32|37|45|8</t>
+          <t>8|12|15|38|39|45|18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2069,34 +2069,34 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
+        <v>37</v>
+      </c>
+      <c r="L18" t="n">
+        <v>42</v>
+      </c>
+      <c r="M18" t="n">
+        <v>43</v>
+      </c>
+      <c r="N18" t="n">
+        <v>173</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>38</v>
-      </c>
-      <c r="L18" t="n">
-        <v>43</v>
-      </c>
-      <c r="M18" t="n">
-        <v>16</v>
-      </c>
-      <c r="N18" t="n">
-        <v>161</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>45</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.14571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L19" t="n">
         <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N19" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,16 +2214,16 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.61</v>
+        <v>36.59</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12|13|28|32|41|49|2</t>
+          <t>8|9|16|36|41|49|20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L20" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.19333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>6|12|26|31|35|49|25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2354,22 +2354,22 @@
         <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
         <v>35</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N21" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.86</v>
+        <v>35.84</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6|12|26|31|35|49|25</t>
+          <t>6|13|15|32|35|46|17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L22" t="n">
         <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="N22" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,16 +2496,16 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.58727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6|9|15|31|36|46|53</t>
+          <t>9|10|29|35|36|46|43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2539,13 +2539,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
         <v>33</v>
@@ -2555,16 +2555,16 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.95999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.96</v>
+        <v>47.78</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,26 +2716,26 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.96</v>
+        <v>43.28</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
@@ -2818,14 +2818,14 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.46</v>
+        <v>42.78</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|10|12|21|25</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,23 +2899,23 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.96</v>
+        <v>38.78</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|7|10|25|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,26 +2986,26 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.96</v>
+        <v>37.78</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>10|12|13|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
-      </c>
-      <c r="I29" t="n">
-        <v>12</v>
-      </c>
-      <c r="J29" t="n">
-        <v>13</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.96</v>
+        <v>37.06571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10|12|13|25|35</t>
+          <t>5|8|10|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" t="n">
         <v>6</v>
       </c>
-      <c r="H30" t="n">
-        <v>5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>8</v>
-      </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L30" t="n">
         <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.24571428571429</v>
+        <v>36.53</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5|8|10|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.71</v>
+        <v>36.11333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3|6|12|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.29333333333334</v>
+        <v>35.78</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.68727272727273</v>
+        <v>35.50727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.5333</v>
+        <v>74.6875</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|45</t>
+          <t>1|3|5|44|46|49|39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
         <v>19</v>
@@ -3640,13 +3640,13 @@
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N35" t="n">
         <v>169</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.5333</v>
+        <v>48.6875</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14|19|24|31|40|41|45</t>
+          <t>9|19|24|28|44|45|49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
         <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
         <v>24</v>
       </c>
       <c r="N36" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.5333</v>
+        <v>43.6875</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9|18|19|31|40|44|24</t>
+          <t>17|19|20|31|38|44|24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="N37" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.0333</v>
+        <v>41.1875</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>5|9|24|26|44|45|42</t>
+          <t>9|14|19|38|40|41|12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
@@ -3925,7 +3925,7 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
         <v>19</v>
@@ -3934,7 +3934,7 @@
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L38" t="n">
         <v>38</v>
@@ -3943,7 +3943,7 @@
         <v>15</v>
       </c>
       <c r="N38" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.5333</v>
+        <v>39.6875</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>7|19|24|31|38|40|15</t>
+          <t>14|19|24|27|38|41|15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
         <v>40</v>
       </c>
       <c r="M39" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.5333</v>
+        <v>38.6875</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|6|13|30|40|41|16</t>
+          <t>11|19|24|26|40|41|5</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J40" t="n">
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="N40" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.81901428571428</v>
+        <v>37.97321428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6|9|19|42|44|45|17</t>
+          <t>9|13|19|32|38|40|29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L41" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="M41" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="N41" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.2833</v>
+        <v>37.4375</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>11|19|24|31|32|40|42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -4317,34 +4317,34 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="n">
         <v>9</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
+        <v>24</v>
+      </c>
+      <c r="K42" t="n">
+        <v>26</v>
+      </c>
+      <c r="L42" t="n">
+        <v>38</v>
+      </c>
+      <c r="M42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" t="n">
-        <v>16</v>
-      </c>
-      <c r="K42" t="n">
+      <c r="N42" t="n">
+        <v>145</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>38</v>
-      </c>
-      <c r="L42" t="n">
-        <v>40</v>
-      </c>
-      <c r="M42" t="n">
-        <v>35</v>
-      </c>
-      <c r="N42" t="n">
-        <v>157</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>32</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.86663333333333</v>
+        <v>37.02083333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|13|16|38|40|41|35</t>
+          <t>5|9|24|26|38|43|13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.5333</v>
+        <v>36.6875</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|17|20|40|41|48|10</t>
+          <t>1|7|24|26|38|45|6</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M44" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.26057272727273</v>
+        <v>36.41477272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16|17|24|29|31|34|10</t>
+          <t>9|11|14|40|44|45|39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.5333</v>
+        <v>74.6875</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|45</t>
+          <t>1|3|5|44|46|49|39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4760,7 +4760,7 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.0333</v>
+        <v>36.1875</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4858,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.8409923076923</v>
+        <v>35.99519230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4956,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.67615714285714</v>
+        <v>35.83035714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5054,7 +5054,7 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.5333</v>
+        <v>35.6875</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5152,7 +5152,7 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.4083</v>
+        <v>35.5625</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5250,7 +5250,7 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.29800588235294</v>
+        <v>35.45220588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5348,7 +5348,7 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.19996666666667</v>
+        <v>35.35416666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5446,7 +5446,7 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.11224736842105</v>
+        <v>35.26644736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.0333</v>
+        <v>35.1875</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5642,7 +5642,7 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.96187142857143</v>
+        <v>35.11607142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:52</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -591,19 +591,19 @@
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L2" t="n">
         <v>34</v>
       </c>
-      <c r="L2" t="n">
-        <v>41</v>
-      </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -633,19 +633,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.55</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|20|34|41|18</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,25 +677,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.55</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2|22|23|31|43|17</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,25 +766,25 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>119</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>53.05</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -873,13 +873,13 @@
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.55</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5|21|22|29|38|11</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.83571428571428</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9|19|20|30|43|3</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1042,28 +1042,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
         <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1093,19 +1093,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.55</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15|22|25|31|36|5</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -1152,7 +1152,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1185,19 +1185,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>46.3</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|16</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>45.88333333333333</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9|15|24|29|36|1</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>45.55</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
         <v>20</v>
       </c>
-      <c r="J11" t="n">
-        <v>25</v>
-      </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.27727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|20|25|26|29|17</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -1517,10 +1517,10 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.84</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|47</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,34 +1599,34 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
         <v>32</v>
       </c>
       <c r="L13" t="n">
+        <v>37</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>163</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>38</v>
-      </c>
-      <c r="M13" t="n">
-        <v>46</v>
-      </c>
-      <c r="N13" t="n">
-        <v>157</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>47</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.84</v>
+        <v>47.85</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1|11|27|32|38|48|46</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
         <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="N14" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,16 +1744,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.84</v>
+        <v>42.85</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3|9|23|30|44|48|37</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1787,22 +1787,22 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
         <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
         <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
         <v>157</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.34</v>
+        <v>40.35</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9|13|21|32|36|46|11</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
+        <v>38</v>
+      </c>
+      <c r="L16" t="n">
         <v>43</v>
       </c>
-      <c r="L16" t="n">
-        <v>44</v>
-      </c>
       <c r="M16" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.84</v>
+        <v>38.85</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5|8|24|43|44|45|38</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="N17" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.84</v>
+        <v>37.85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8|12|15|38|39|45|18</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.12571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2163,22 +2163,22 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
         <v>8</v>
       </c>
-      <c r="I19" t="n">
-        <v>9</v>
-      </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
         <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
         <v>159</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.59</v>
+        <v>36.6</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8|9|16|36|41|49|20</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L20" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,16 +2308,16 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.17333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6|12|26|31|35|49|25</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
         <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.84</v>
+        <v>35.85</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6|13|15|32|35|46|17</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.56727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9|10|29|35|36|46|43</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2539,13 +2539,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
         <v>6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>10</v>
-      </c>
-      <c r="J23" t="n">
-        <v>12</v>
       </c>
       <c r="K23" t="n">
         <v>33</v>
@@ -2555,16 +2555,16 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="P23" t="n">
-        <v>3</v>
-      </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.78</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.78</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,26 +2716,26 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>43.28</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
@@ -2818,14 +2818,14 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
         <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>42.78</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,23 +2899,23 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="J27" t="n">
-        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.78</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.78</v>
+        <v>37.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10|12|13|25|35</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.06571428571429</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|8|10|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
         <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.53</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3262,7 +3262,7 @@
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.11333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.78</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.50727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.6875</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|39</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
         <v>19</v>
@@ -3640,13 +3640,13 @@
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N35" t="n">
         <v>169</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,16 +3682,16 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6875</v>
+        <v>48.8667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9|19|24|28|44|45|49</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
+        <v>14</v>
+      </c>
+      <c r="I36" t="n">
         <v>17</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>19</v>
       </c>
-      <c r="J36" t="n">
-        <v>20</v>
-      </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6875</v>
+        <v>43.8667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|24</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
         <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L37" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1875</v>
+        <v>41.3667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9|14|19|38|40|41|12</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,16 +3976,16 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6875</v>
+        <v>39.8667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14|19|24|27|38|41|15</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4023,34 +4023,34 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
+        <v>44</v>
+      </c>
+      <c r="M39" t="n">
+        <v>31</v>
+      </c>
+      <c r="N39" t="n">
+        <v>157</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
         <v>40</v>
-      </c>
-      <c r="M39" t="n">
-        <v>5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>161</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>30</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6875</v>
+        <v>38.8667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11|19|24|26|40|41|5</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,22 +4121,22 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M40" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
         <v>151</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.97321428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>9|13|19|32|38|40|29</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
+        <v>18</v>
+      </c>
+      <c r="J41" t="n">
         <v>19</v>
       </c>
-      <c r="J41" t="n">
-        <v>24</v>
-      </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4375</v>
+        <v>37.6167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11|19|24|31|32|40|42</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L42" t="n">
         <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.02083333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>5|9|24|26|38|43|13</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,10 +4415,10 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
@@ -4427,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6875</v>
+        <v>36.8667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|7|24|26|38|45|6</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
         <v>9</v>
       </c>
-      <c r="I44" t="n">
-        <v>11</v>
-      </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M44" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="N44" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.41477272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>9|11|14|40|44|45|39</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.6875</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|39</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4712,22 +4712,22 @@
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
         <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N46" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1875</v>
+        <v>36.3667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L47" t="n">
         <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.99519230769231</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.83035714285714</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>1|11|20|40|44|45|3</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
         <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6875</v>
+        <v>35.8667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|20|22|29|38|39|18</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5107,19 +5107,19 @@
         <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5625</v>
+        <v>35.7417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N51" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.45220588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|12|13|34|38|45|49</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
         <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L52" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.35416666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>5|6|20|31|44|45|11</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5401,19 +5401,19 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L53" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N53" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.26644736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|20|24|29|34|49|8</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="N54" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1875</v>
+        <v>35.3667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|4|20|29|42|45|19</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.11607142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|15|24|25|36|42|10</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:52</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>57.6</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,10 +677,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -689,13 +689,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>55.6</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>53.1</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>3|21|22|29|38|4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,28 +858,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>49.88571428571429</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>48.93333333333333</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>3|15|20|29|38|14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1042,28 +1042,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1093,19 +1093,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.6</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1137,22 +1137,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
         <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.6</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>9|19|20|30|43|3</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
         <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>47.6</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.35</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.32727272727273</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>7|19|24|34|37|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -1517,10 +1517,10 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.84999999999999</v>
+        <v>73.84</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>2|4|44|49|51|56|47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
         <v>11</v>
       </c>
-      <c r="I13" t="n">
-        <v>12</v>
-      </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
         <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N13" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.85</v>
+        <v>47.84</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>1|11|27|32|38|48|46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
         <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N14" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,16 +1744,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.85</v>
+        <v>42.84</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>3|9|23|30|44|48|37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1787,22 +1787,22 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
         <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
         <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N15" t="n">
         <v>157</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.35</v>
+        <v>40.34</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>9|13|21|32|36|46|11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
+        <v>43</v>
+      </c>
+      <c r="L16" t="n">
+        <v>44</v>
+      </c>
+      <c r="M16" t="n">
         <v>38</v>
       </c>
-      <c r="L16" t="n">
-        <v>43</v>
-      </c>
-      <c r="M16" t="n">
-        <v>16</v>
-      </c>
       <c r="N16" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.85</v>
+        <v>38.84</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>5|8|24|43|44|45|38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M17" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.85</v>
+        <v>37.84</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>8|12|15|38|39|45|18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
         <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="N18" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.13571428571429</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2163,22 +2163,22 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L19" t="n">
         <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="N19" t="n">
         <v>159</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.6</v>
+        <v>36.59</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>8|9|16|36|41|49|20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,16 +2308,16 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.18333333333334</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>6|12|26|31|35|49|25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
+        <v>13</v>
+      </c>
+      <c r="J21" t="n">
         <v>15</v>
-      </c>
-      <c r="J21" t="n">
-        <v>27</v>
       </c>
       <c r="K21" t="n">
         <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N21" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.85</v>
+        <v>35.84</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>6|13|15|32|35|46|17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N22" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.57727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>9|10|29|35|36|46|43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -2539,13 +2539,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
         <v>33</v>
@@ -2555,16 +2555,16 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.79</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>10|14|15|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,26 +2716,26 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
+        <v>9</v>
+      </c>
+      <c r="J25" t="n">
         <v>10</v>
-      </c>
-      <c r="J25" t="n">
-        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.84</v>
+        <v>43.29</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>4|9|10|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
@@ -2818,14 +2818,14 @@
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
         <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.34</v>
+        <v>42.79</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
@@ -2911,7 +2911,7 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.84</v>
+        <v>39.54</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,26 +2986,26 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="n">
         <v>6</v>
       </c>
-      <c r="I28" t="n">
-        <v>13</v>
-      </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L28" t="n">
         <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.84</v>
+        <v>38.79</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.12571428571429</v>
+        <v>37.79</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>5|8|14|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
-        <v>15</v>
-      </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
         <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.59</v>
+        <v>37.07571428571428</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L31" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.17333333333333</v>
+        <v>36.12333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|15|23|33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.84</v>
+        <v>35.79</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,13 +3439,13 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" t="n">
         <v>10</v>
-      </c>
-      <c r="J33" t="n">
-        <v>14</v>
       </c>
       <c r="K33" t="n">
         <v>23</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>35.51727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>5|6|10|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.86669999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3637,16 +3637,16 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
         <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="N35" t="n">
         <v>169</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.8667</v>
+        <v>48.6667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>17|19|20|31|38|44|24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.8667</v>
+        <v>43.6667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>11|19|24|26|40|41|6</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.3667</v>
+        <v>41.1667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>17|20|24|29|35|44|14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
         <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N38" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.8667</v>
+        <v>39.6667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>14|16|17|34|39|49|7</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
@@ -4026,7 +4026,7 @@
         <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
@@ -4035,13 +4035,13 @@
         <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.8667</v>
+        <v>38.6667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>5|21|24|30|38|45|6</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,10 +4121,10 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
@@ -4133,13 +4133,13 @@
         <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.15241428571429</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>5|9|24|26|38|43|13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
@@ -4219,34 +4219,34 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
+        <v>26</v>
+      </c>
+      <c r="L41" t="n">
+        <v>38</v>
+      </c>
+      <c r="M41" t="n">
+        <v>35</v>
+      </c>
+      <c r="N41" t="n">
+        <v>161</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" t="n">
         <v>30</v>
-      </c>
-      <c r="L41" t="n">
-        <v>44</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>165</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3</v>
-      </c>
-      <c r="P41" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>36</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.6167</v>
+        <v>37.4167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>11|21|24|26|38|41|35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -4317,34 +4317,34 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
+        <v>31</v>
+      </c>
+      <c r="L42" t="n">
+        <v>40</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>163</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>33</v>
-      </c>
-      <c r="L42" t="n">
-        <v>38</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4</v>
-      </c>
-      <c r="N42" t="n">
-        <v>169</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>25</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,16 +4368,16 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.20003333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>8|19|24|31|40|41|5</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L43" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.8667</v>
+        <v>36.6667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>1|23|24|32|38|41|5</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
         <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M44" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,16 +4564,16 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.59397272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>9|17|20|31|40|44|23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.86669999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4724,7 +4724,7 @@
         <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N46" t="n">
         <v>165</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.3667</v>
+        <v>36.1667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|8|23|38|44|49|36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M47" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="N47" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.17439230769231</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>3|5|24|36|37|40|49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
@@ -4914,16 +4914,16 @@
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L48" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
         <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.00955714285714</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>3|15|24|30|38|49|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -5009,19 +5009,19 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M49" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="N49" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.8667</v>
+        <v>35.6667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|12|20|29|31|44|35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
+        <v>24</v>
+      </c>
+      <c r="K50" t="n">
+        <v>37</v>
+      </c>
+      <c r="L50" t="n">
+        <v>38</v>
+      </c>
+      <c r="M50" t="n">
         <v>20</v>
       </c>
-      <c r="K50" t="n">
-        <v>31</v>
-      </c>
-      <c r="L50" t="n">
-        <v>44</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
       <c r="N50" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.7417</v>
+        <v>35.5417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="N51" t="n">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.63140588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|4|5|31|44|46|15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
         <v>34</v>
       </c>
       <c r="L52" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N52" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.53336666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|15|18|34|45|46|5</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -5401,19 +5401,19 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K53" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
         <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N53" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.44564736842106</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|20|22|29|38|39|18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K54" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M54" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.3667</v>
+        <v>35.1667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
+        <v>25</v>
+      </c>
+      <c r="L55" t="n">
+        <v>46</v>
+      </c>
+      <c r="M55" t="n">
         <v>38</v>
       </c>
-      <c r="L55" t="n">
-        <v>44</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
       <c r="N55" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5642,16 +5642,16 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.29527142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|6|24|25|46|49|38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.84</v>
+        <v>73.75</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|47</t>
+          <t>2|4|44|49|51|56|22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
         <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M13" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N13" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.84</v>
+        <v>47.75</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1|11|27|32|38|48|46</t>
+          <t>9|12|15|32|41|46|23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N14" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,20 +1744,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.84</v>
+        <v>42.75</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3|9|23|30|44|48|37</t>
+          <t>11|12|20|39|40|45|28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L15" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,16 +1838,16 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.34</v>
+        <v>40.25</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9|13|21|32|36|46|11</t>
+          <t>4|8|17|35|43|46|24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.84</v>
+        <v>38.75</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5|8|24|43|44|45|38</t>
+          <t>8|11|22|33|42|49|10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1978,22 +1978,22 @@
         <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L17" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M17" t="n">
         <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2026,16 +2026,16 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.84</v>
+        <v>37.75</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8|12|15|38|39|45|18</t>
+          <t>8|27|28|32|33|45|18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2069,22 +2069,22 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="N18" t="n">
         <v>173</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.12571428571429</v>
+        <v>37.03571428571428</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|28|40|43|49|51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
         <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N19" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.59</v>
+        <v>36.5</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8|9|16|36|41|49|20</t>
+          <t>7|10|29|32|41|46|16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K20" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L20" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
         <v>25</v>
       </c>
       <c r="N20" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.17333333333333</v>
+        <v>36.08333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6|12|26|31|35|49|25</t>
+          <t>8|18|24|33|43|45|25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -2351,22 +2351,22 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K21" t="n">
         <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>147</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.84</v>
+        <v>35.75</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6|13|15|32|35|46|17</t>
+          <t>7|8|17|32|36|47|1</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K22" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M22" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.56727272727272</v>
+        <v>35.47727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9|10|29|35|36|46|43</t>
+          <t>2|6|23|30|41|49|20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.79</v>
+        <v>47.81</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,26 +2716,26 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>43.29</v>
+        <v>42.81</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4|9|10|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
-      </c>
-      <c r="J26" t="n">
-        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>42.79</v>
+        <v>40.81</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
+        <v>21</v>
+      </c>
+      <c r="L27" t="n">
         <v>25</v>
-      </c>
-      <c r="L27" t="n">
-        <v>36</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>39.54</v>
+        <v>40.31</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>5|10|12|21|25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3038,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.79</v>
+        <v>38.81</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" t="n">
         <v>25</v>
-      </c>
-      <c r="L29" t="n">
-        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.79</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|8|14|25|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
+        <v>23</v>
+      </c>
+      <c r="L30" t="n">
         <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.07571428571428</v>
+        <v>36.56</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.12333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|10|15|23|33</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,32 +3349,32 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
         <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.79</v>
+        <v>35.81</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>4|6|12|25|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
         <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.51727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5|6|10|23|25</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
+        <v>14</v>
+      </c>
+      <c r="J35" t="n">
         <v>19</v>
       </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6667</v>
+        <v>48.8</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|24</t>
+          <t>9|14|19|38|40|41|12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N36" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6667</v>
+        <v>43.8</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11|19|24|26|40|41|6</t>
+          <t>1|16|24|29|38|45|8</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N37" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,16 +3878,16 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1667</v>
+        <v>41.3</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17|20|24|29|35|44|14</t>
+          <t>3|9|19|30|40|44|11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
         <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N38" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6667</v>
+        <v>39.8</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14|16|17|34|39|49|7</t>
+          <t>1|10|17|38|41|44|15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
         <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="N39" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6667</v>
+        <v>38.8</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|21|24|30|38|45|6</t>
+          <t>13|17|24|26|38|39|31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L40" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="N40" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.95241428571428</v>
+        <v>38.08571428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>5|9|24|26|38|43|13</t>
+          <t>3|17|22|38|40|41|32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L41" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M41" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4167</v>
+        <v>37.55</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11|21|24|26|38|41|35</t>
+          <t>8|19|24|31|40|41|5</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
         <v>8</v>
       </c>
-      <c r="I42" t="n">
-        <v>19</v>
-      </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.00003333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|5</t>
+          <t>3|8|9|40|44|45|1</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6667</v>
+        <v>36.8</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|23|24|32|38|41|5</t>
+          <t>5|17|24|26|44|49|8</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
+        <v>30</v>
+      </c>
+      <c r="L44" t="n">
         <v>31</v>
       </c>
-      <c r="L44" t="n">
-        <v>40</v>
-      </c>
       <c r="M44" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="N44" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.39397272727273</v>
+        <v>36.52727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>9|17|20|31|40|44|23</t>
+          <t>11|19|24|30|31|40|32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,19 +4757,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1667</v>
+        <v>38.94285714285714</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|36</t>
+          <t>1|2|20|42|45|49|9</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J47" t="n">
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L47" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M47" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="N47" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.97439230769231</v>
+        <v>36.3</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|5|24|36|37|40|49</t>
+          <t>6|15|24|31|34|49|29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L48" t="n">
+        <v>44</v>
+      </c>
+      <c r="M48" t="n">
         <v>38</v>
       </c>
-      <c r="M48" t="n">
-        <v>27</v>
-      </c>
       <c r="N48" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,16 +4956,16 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.80955714285714</v>
+        <v>36.1076923076923</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|15|24|30|38|49|27</t>
+          <t>6|11|20|39|44|49|38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5012,16 +5012,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M49" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N49" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6667</v>
+        <v>35.8</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|20|29|31|44|35</t>
+          <t>3|12|20|34|39|45|27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="N50" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5417</v>
+        <v>35.675</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|18|24|29|44|49|35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L51" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M51" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="N51" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.43140588235294</v>
+        <v>35.56470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|4|5|31|44|46|15</t>
+          <t>11|18|20|29|39|44|49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J52" t="n">
         <v>15</v>
-      </c>
-      <c r="J52" t="n">
-        <v>18</v>
       </c>
       <c r="K52" t="n">
         <v>34</v>
       </c>
       <c r="L52" t="n">
+        <v>46</v>
+      </c>
+      <c r="M52" t="n">
         <v>45</v>
       </c>
-      <c r="M52" t="n">
-        <v>5</v>
-      </c>
       <c r="N52" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.33336666666666</v>
+        <v>35.46666666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|15|18|34|45|46|5</t>
+          <t>3|6|15|34|46|49|45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5398,19 +5398,19 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L53" t="n">
         <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N53" t="n">
         <v>151</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.24564736842105</v>
+        <v>35.37894736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|20|22|29|38|39|18</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J54" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
+        <v>25</v>
+      </c>
+      <c r="L54" t="n">
         <v>38</v>
       </c>
-      <c r="L54" t="n">
-        <v>44</v>
-      </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N54" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1667</v>
+        <v>35.3</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|12|15|25|38|44|13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K55" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="M55" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N55" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>35.22857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|6|24|25|46|49|38</t>
+          <t>3|12|17|38|39|46|35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.81</v>
+        <v>73.92</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.81</v>
+        <v>47.92</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,13 +2719,13 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.81</v>
+        <v>42.92</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.81</v>
+        <v>40.42</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>9|10|12|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="n">
-        <v>12</v>
-      </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.31</v>
+        <v>38.92</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5|10|12|21|25</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
         <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.81</v>
+        <v>38.92</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|7|10|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
         <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.09571428571429</v>
+        <v>37.92</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>5|8|10|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.56</v>
+        <v>37.20571428571429</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>4|5|6|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
         <v>9</v>
       </c>
-      <c r="I31" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" t="n">
-        <v>14</v>
-      </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L31" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.14333333333333</v>
+        <v>36.67</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,35 +3346,35 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
+        <v>21</v>
+      </c>
+      <c r="L32" t="n">
         <v>25</v>
-      </c>
-      <c r="L32" t="n">
-        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
-        <v>3</v>
-      </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.81</v>
+        <v>36.25333333333333</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|6|12|25|27</t>
+          <t>4|7|10|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
         <v>10</v>
       </c>
       <c r="K33" t="n">
+        <v>21</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>31</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.53727272727272</v>
+        <v>35.64727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.8</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|15</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
         <v>9</v>
       </c>
-      <c r="I35" t="n">
-        <v>14</v>
-      </c>
       <c r="J35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
         <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="N35" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.8</v>
+        <v>48.6667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9|14|19|38|40|41|12</t>
+          <t>3|9|22|38|44|49|43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L36" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="N36" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.8</v>
+        <v>43.6667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>1|16|24|29|38|45|8</t>
+          <t>17|19|22|26|31|44|33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L37" t="n">
         <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N37" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.3</v>
+        <v>41.1667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>3|9|19|30|40|44|11</t>
+          <t>10|19|24|31|40|41|15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" t="n">
+        <v>29</v>
+      </c>
+      <c r="L38" t="n">
+        <v>39</v>
+      </c>
+      <c r="M38" t="n">
         <v>17</v>
       </c>
-      <c r="K38" t="n">
-        <v>38</v>
-      </c>
-      <c r="L38" t="n">
-        <v>41</v>
-      </c>
-      <c r="M38" t="n">
-        <v>15</v>
-      </c>
       <c r="N38" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.8</v>
+        <v>39.6667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>1|10|17|38|41|44|15</t>
+          <t>16|20|24|29|39|41|17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L39" t="n">
         <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.8</v>
+        <v>38.6667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13|17|24|26|38|39|31</t>
+          <t>5|22|24|31|38|45|6</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
+        <v>19</v>
+      </c>
+      <c r="K40" t="n">
+        <v>27</v>
+      </c>
+      <c r="L40" t="n">
+        <v>31</v>
+      </c>
+      <c r="M40" t="n">
         <v>22</v>
       </c>
-      <c r="K40" t="n">
-        <v>38</v>
-      </c>
-      <c r="L40" t="n">
-        <v>40</v>
-      </c>
-      <c r="M40" t="n">
-        <v>32</v>
-      </c>
       <c r="N40" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.08571428571428</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>3|17|22|38|40|41|32</t>
+          <t>6|18|19|27|31|44|22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -4219,7 +4219,7 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
@@ -4231,13 +4231,13 @@
         <v>31</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N41" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.55</v>
+        <v>37.4167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|5</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="N42" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.13333333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>3|8|9|40|44|45|1</t>
+          <t>9|14|19|26|38|41|42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,10 +4415,10 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
@@ -4427,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.8</v>
+        <v>36.6667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|17|24|26|44|49|8</t>
+          <t>1|3|24|26|41|44|6</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -4522,16 +4522,16 @@
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M44" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="N44" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.52727272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11|19|24|30|31|40|32</t>
+          <t>11|19|24|27|40|44|7</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.8</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|15</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M46" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="N46" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,23 +4757,23 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.94285714285714</v>
+        <v>36.1667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|9</t>
+          <t>3|18|24|33|35|38|27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
+        <v>12</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
         <v>11</v>
       </c>
-      <c r="H47" t="n">
-        <v>6</v>
-      </c>
-      <c r="I47" t="n">
-        <v>15</v>
-      </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="M47" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="N47" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.3</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>6|15|24|31|34|49|29</t>
+          <t>2|11|18|38|45|49|41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M48" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="N48" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.1076923076923</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|38</t>
+          <t>1|3|18|38|45|46|8</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J49" t="n">
         <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N49" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.8</v>
+        <v>35.6667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|27</t>
+          <t>3|15|20|29|38|46|17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
         <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N50" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.675</v>
+        <v>35.5417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|18|24|29|44|49|35</t>
+          <t>3|12|20|31|44|45|32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
         <v>18</v>
       </c>
-      <c r="J51" t="n">
-        <v>20</v>
-      </c>
       <c r="K51" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="N51" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.56470588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11|18|20|29|39|44|49</t>
+          <t>3|5|18|38|44|49|33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J52" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M52" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="N52" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.46666666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|15|34|46|49|45</t>
+          <t>9|11|18|33|42|44|17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M53" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.37894736842105</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5499,19 +5499,19 @@
         <v>12</v>
       </c>
       <c r="J54" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
         <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="N54" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.3</v>
+        <v>35.1667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|12|15|25|38|44|13</t>
+          <t>3|12|24|37|38|45|32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
+        <v>36</v>
+      </c>
+      <c r="L55" t="n">
         <v>38</v>
       </c>
-      <c r="L55" t="n">
-        <v>39</v>
-      </c>
       <c r="M55" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.22857142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|12|17|38|39|46|35</t>
+          <t>3|15|18|36|38|39|10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.92</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
         <v>10</v>
       </c>
-      <c r="I24" t="n">
-        <v>14</v>
-      </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.92</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10|14|15|25|27</t>
+          <t>5|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,19 +2719,19 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
         <v>12</v>
-      </c>
-      <c r="J25" t="n">
-        <v>14</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.92</v>
+        <v>45.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>3|10|12|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2815,7 +2815,7 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.42</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>9|10|12|25|35</t>
+          <t>9|10|14|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.92</v>
+        <v>39.59</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>6|10|11|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,13 +2989,13 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.92</v>
+        <v>38.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|7|10|25|27</t>
+          <t>1|10|14|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,13 +3076,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" t="n">
         <v>10</v>
@@ -3091,11 +3091,11 @@
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
         <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.92</v>
+        <v>38.84</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|8|10|25|27</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.20571428571429</v>
+        <v>37.84</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|5|6|25|27</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.67</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.25333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|7|10|21|25</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.64727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.5</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,22 +3631,22 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N35" t="n">
         <v>165</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6667</v>
+        <v>48.5</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|43</t>
+          <t>6|19|24|31|41|44|23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J36" t="n">
         <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L36" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="N36" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6667</v>
+        <v>43.5</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17|19|22|26|31|44|33</t>
+          <t>3|9|22|38|44|49|43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37">
@@ -3827,7 +3827,7 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I37" t="n">
         <v>19</v>
@@ -3836,16 +3836,16 @@
         <v>24</v>
       </c>
       <c r="K37" t="n">
+        <v>27</v>
+      </c>
+      <c r="L37" t="n">
         <v>31</v>
       </c>
-      <c r="L37" t="n">
-        <v>40</v>
-      </c>
       <c r="M37" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="N37" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1667</v>
+        <v>41</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10|19|24|31|40|41|15</t>
+          <t>14|19|24|27|31|44|35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N38" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,16 +3976,16 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6667</v>
+        <v>39.5</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16|20|24|29|39|41|17</t>
+          <t>10|19|24|31|40|41|15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6667</v>
+        <v>38.5</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|22|24|31|38|45|6</t>
+          <t>11|17|24|26|44|45|12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N40" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,16 +4172,16 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.95241428571428</v>
+        <v>37.78571428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6|18|19|27|31|44|22</t>
+          <t>1|17|20|31|38|44|23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
+        <v>16</v>
+      </c>
+      <c r="K41" t="n">
+        <v>38</v>
+      </c>
+      <c r="L41" t="n">
+        <v>41</v>
+      </c>
+      <c r="M41" t="n">
         <v>24</v>
       </c>
-      <c r="K41" t="n">
-        <v>31</v>
-      </c>
-      <c r="L41" t="n">
-        <v>36</v>
-      </c>
-      <c r="M41" t="n">
-        <v>14</v>
-      </c>
       <c r="N41" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4167</v>
+        <v>37.25</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>1|2|16|38|41|45|24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4320,22 +4320,22 @@
         <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M42" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N42" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.00003333333333</v>
+        <v>36.83333333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|14|19|26|38|41|42</t>
+          <t>9|11|24|31|40|44|30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N43" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,16 +4466,16 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6667</v>
+        <v>36.5</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|3|24|26|41|44|6</t>
+          <t>11|19|24|27|40|44|7</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4513,34 +4513,34 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L44" t="n">
+        <v>38</v>
+      </c>
+      <c r="M44" t="n">
+        <v>21</v>
+      </c>
+      <c r="N44" t="n">
+        <v>159</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" t="n">
         <v>40</v>
-      </c>
-      <c r="M44" t="n">
-        <v>7</v>
-      </c>
-      <c r="N44" t="n">
-        <v>165</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3</v>
-      </c>
-      <c r="P44" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>33</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.39397272727273</v>
+        <v>36.22727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11|19|24|27|40|44|7</t>
+          <t>5|17|20|34|38|45|21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.66670000000001</v>
+        <v>74.5</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4760,7 +4760,7 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1667</v>
+        <v>36</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4858,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.97439230769231</v>
+        <v>35.80769230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4956,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.80955714285714</v>
+        <v>35.64285714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5054,7 +5054,7 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6667</v>
+        <v>35.5</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5152,7 +5152,7 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5417</v>
+        <v>35.375</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5250,7 +5250,7 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.43140588235294</v>
+        <v>35.26470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5348,7 +5348,7 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.33336666666666</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5446,7 +5446,7 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.24564736842105</v>
+        <v>35.07894736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1667</v>
+        <v>35</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5642,7 +5642,7 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>34.92857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:29</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.6</v>
+        <v>57.58</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -728,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.6</v>
+        <v>55.58</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -820,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>53.1</v>
+        <v>51.58</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,28 +858,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>49.88571428571429</v>
+        <v>50.08</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>48.93333333333333</v>
+        <v>49.86571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|14</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
         <v>19</v>
@@ -1054,16 +1054,16 @@
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1093,19 +1093,19 @@
         <v>0.5</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.6</v>
+        <v>48.91333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>9|19|24|34|41|19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1137,22 +1137,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.6</v>
+        <v>48.58</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9|19|20|30|43|3</t>
+          <t>7|13|25|34|42|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1229,25 +1229,25 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1280,16 +1280,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.6</v>
+        <v>47.58</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1321,25 +1321,25 @@
         <v>7</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
         <v>9</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>22</v>
       </c>
-      <c r="J10" t="n">
-        <v>24</v>
-      </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.35</v>
+        <v>46.33</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>8|9|22|29|35|13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1413,25 +1413,25 @@
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
         <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.32727272727273</v>
+        <v>45.30727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|16</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.85</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -2735,16 +2735,16 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>45.84</v>
+        <v>45.85</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3|10|12|25|35</t>
+          <t>4|10|12|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.34</v>
+        <v>40.35</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>9|10|14|25|35</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>39.59</v>
+        <v>38.85</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|11|25|35</t>
+          <t>6|11|14|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3038,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.84</v>
+        <v>38.85</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
         <v>36</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>38.84</v>
+        <v>38.57727272727273</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>6|13|15|23|36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>5</v>
       </c>
       <c r="H30" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
         <v>9</v>
       </c>
-      <c r="I30" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" t="n">
-        <v>16</v>
-      </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L30" t="n">
         <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.84</v>
+        <v>37.85</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>37.12571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
+        <v>23</v>
+      </c>
+      <c r="L32" t="n">
         <v>25</v>
-      </c>
-      <c r="L32" t="n">
-        <v>33</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.17333333333333</v>
+        <v>36.6</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3436,26 +3436,26 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>5|14|22|25|27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.5</v>
+        <v>74.4375</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,22 +3631,22 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N35" t="n">
         <v>165</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.5</v>
+        <v>48.4375</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>6|19|24|31|41|44|23</t>
+          <t>3|9|22|38|44|49|43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M36" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N36" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.5</v>
+        <v>43.4375</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|43</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
+        <v>40.9375</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2|13|17|30|40|41|9</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:59:53</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
         <v>41</v>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14|19|24|27|31|44|35</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-06-09 14:12:28</t>
-        </is>
-      </c>
-      <c r="AB37" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,7 +3925,7 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I38" t="n">
         <v>19</v>
@@ -3937,13 +3937,13 @@
         <v>31</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N38" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.5</v>
+        <v>39.4375</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10|19|24|31|40|41|15</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="N39" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.5</v>
+        <v>38.4375</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11|17|24|26|44|45|12</t>
+          <t>5|17|20|34|38|45|21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
         <v>23</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.78571428571428</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>1|17|20|31|38|44|23</t>
+          <t>5|18|19|26|44|45|23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L41" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M41" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.25</v>
+        <v>37.1875</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1|2|16|38|41|45|24</t>
+          <t>6|16|24|29|43|45|5</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,34 +4317,34 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
+        <v>29</v>
+      </c>
+      <c r="L42" t="n">
+        <v>34</v>
+      </c>
+      <c r="M42" t="n">
+        <v>12</v>
+      </c>
+      <c r="N42" t="n">
+        <v>163</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>31</v>
-      </c>
-      <c r="L42" t="n">
-        <v>40</v>
-      </c>
-      <c r="M42" t="n">
-        <v>30</v>
-      </c>
-      <c r="N42" t="n">
-        <v>159</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>35</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.83333333333333</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|11|24|31|40|44|30</t>
+          <t>14|17|24|29|34|45|12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
+        <v>26</v>
+      </c>
+      <c r="L43" t="n">
+        <v>41</v>
+      </c>
+      <c r="M43" t="n">
         <v>27</v>
       </c>
-      <c r="L43" t="n">
-        <v>40</v>
-      </c>
-      <c r="M43" t="n">
-        <v>7</v>
-      </c>
       <c r="N43" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,16 +4466,16 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.5</v>
+        <v>36.4375</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11|19|24|27|40|44|7</t>
+          <t>1|13|24|26|41|44|27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I44" t="n">
+        <v>9</v>
+      </c>
+      <c r="J44" t="n">
         <v>17</v>
       </c>
-      <c r="J44" t="n">
-        <v>20</v>
-      </c>
       <c r="K44" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L44" t="n">
         <v>38</v>
       </c>
       <c r="M44" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.22727272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|17|20|34|38|45|21</t>
+          <t>8|9|17|30|38|41|4</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.5</v>
+        <v>74.4375</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M46" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="N46" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.0625</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,23 +4757,23 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>36</v>
+        <v>38.3125</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|18|24|33|35|38|27</t>
+          <t>1|3|6|38|42|49|9</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
         <v>11</v>
       </c>
       <c r="J47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L47" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M47" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="N47" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.80769230769231</v>
+        <v>35.9375</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>2|11|18|38|45|49|41</t>
+          <t>6|11|20|39|40|49|8</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,25 +4902,25 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L48" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N48" t="n">
         <v>151</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.64285714285714</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>1|3|18|38|45|46|8</t>
+          <t>3|18|24|33|35|38|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
@@ -5000,28 +5000,28 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J49" t="n">
         <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M49" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="N49" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.5</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|46|17</t>
+          <t>2|11|20|33|34|45|49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5098,28 +5098,28 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N50" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5137,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.0625</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.375</v>
+        <v>35.4375</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|12|20|31|44|45|32</t>
+          <t>2|3|24|33|42|49|27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
         <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N51" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.26470588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|5|18|38|44|49|33</t>
+          <t>3|12|20|31|44|45|32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J52" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
+        <v>37</v>
+      </c>
+      <c r="L52" t="n">
+        <v>38</v>
+      </c>
+      <c r="M52" t="n">
         <v>33</v>
       </c>
-      <c r="L52" t="n">
-        <v>42</v>
-      </c>
-      <c r="M52" t="n">
-        <v>17</v>
-      </c>
       <c r="N52" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.16666666666666</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>9|11|18|33|42|44|17</t>
+          <t>2|13|24|37|38|49|33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5395,25 +5395,25 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
+        <v>11</v>
+      </c>
+      <c r="J53" t="n">
+        <v>18</v>
+      </c>
+      <c r="K53" t="n">
+        <v>42</v>
+      </c>
+      <c r="L53" t="n">
+        <v>45</v>
+      </c>
+      <c r="M53" t="n">
         <v>4</v>
       </c>
-      <c r="J53" t="n">
-        <v>11</v>
-      </c>
-      <c r="K53" t="n">
-        <v>38</v>
-      </c>
-      <c r="L53" t="n">
-        <v>44</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1</v>
-      </c>
       <c r="N53" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.07894736842105</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>2|11|18|42|45|49|4</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K54" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M54" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="N54" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35</v>
+        <v>34.9375</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|12|24|37|38|45|32</t>
+          <t>6|11|18|29|40|49|46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K55" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
         <v>38</v>
       </c>
       <c r="M55" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="N55" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.92857142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|15|18|36|38|39|10</t>
+          <t>3|12|13|32|38|49|41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:29</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.58</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,10 +677,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -689,13 +689,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.58</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -769,25 +769,25 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3|21|22|29|38|4</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -861,25 +861,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -912,16 +912,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.08</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.86571428571428</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1045,25 +1045,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
         <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.91333333333333</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|19</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1140,19 +1140,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|13|25|34|42|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.58</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.33</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8|9|22|29|35|13</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -1517,10 +1517,10 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.75</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|22</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
         <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.75</v>
+        <v>47.85</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9|12|15|32|41|46|23</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
         <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
         <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="N14" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,20 +1744,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.75</v>
+        <v>42.85</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11|12|20|39|40|45|28</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.25</v>
+        <v>40.35</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|8|17|35|43|46|24</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
         <v>8</v>
       </c>
-      <c r="I16" t="n">
-        <v>11</v>
-      </c>
       <c r="J16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.75</v>
+        <v>38.85</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8|11|22|33|42|49|10</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
+        <v>11</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="n">
+        <v>40</v>
+      </c>
+      <c r="L17" t="n">
+        <v>44</v>
+      </c>
+      <c r="M17" t="n">
         <v>27</v>
       </c>
-      <c r="J17" t="n">
-        <v>28</v>
-      </c>
-      <c r="K17" t="n">
-        <v>32</v>
-      </c>
-      <c r="L17" t="n">
-        <v>33</v>
-      </c>
-      <c r="M17" t="n">
-        <v>18</v>
-      </c>
       <c r="N17" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.75</v>
+        <v>37.85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8|27|28|32|33|45|18</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -2075,19 +2075,19 @@
         <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
+        <v>36</v>
+      </c>
+      <c r="L18" t="n">
         <v>40</v>
       </c>
-      <c r="L18" t="n">
-        <v>43</v>
-      </c>
       <c r="M18" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.03571428571428</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|12|28|40|43|49|51</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2163,13 +2163,13 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
         <v>32</v>
@@ -2178,10 +2178,10 @@
         <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,16 +2214,16 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7|10|29|32|41|46|16</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2260,22 +2260,22 @@
         <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.08333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|18|24|33|43|45|25</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2351,13 +2351,13 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
         <v>32</v>
@@ -2366,10 +2366,10 @@
         <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.75</v>
+        <v>35.85</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7|8|17|32|36|47|1</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2445,22 +2445,22 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
         <v>151</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.47727272727273</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2|6|23|30|41|49|20</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2539,13 +2539,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
         <v>6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>10</v>
-      </c>
-      <c r="J23" t="n">
-        <v>12</v>
       </c>
       <c r="K23" t="n">
         <v>33</v>
@@ -2555,16 +2555,16 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="P23" t="n">
-        <v>3</v>
-      </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84999999999999</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.85</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>5|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -2731,20 +2731,20 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>45.85</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4|10|12|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
         <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.35</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.85</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|11|14|25|35</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
         <v>14</v>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.85</v>
+        <v>37.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1|10|14|25|27</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
         <v>10</v>
       </c>
-      <c r="H29" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>13</v>
-      </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
         <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>38.57727272727273</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6|13|15|23|36</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
         <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.85</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>37.13571428571429</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="J32" t="n">
-        <v>14</v>
-      </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.6</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3436,26 +3436,26 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" t="n">
         <v>14</v>
       </c>
-      <c r="J33" t="n">
-        <v>22</v>
-      </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>36.18333333333334</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5|14|22|25|27</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.4375</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
+        <v>26</v>
+      </c>
+      <c r="L35" t="n">
         <v>38</v>
       </c>
-      <c r="L35" t="n">
-        <v>44</v>
-      </c>
       <c r="M35" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N35" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.4375</v>
+        <v>48.8667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|43</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
         <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.4375</v>
+        <v>43.8667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3830,22 +3830,22 @@
         <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L37" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>40.9375</v>
+        <v>41.3667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|13|17|30|40|41|9</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.4375</v>
+        <v>39.8667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4026,22 +4026,22 @@
         <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N39" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.4375</v>
+        <v>38.8667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|17|20|34|38|45|21</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
         <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M40" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,16 +4172,16 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.72321428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>5|18|19|26|44|45|23</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.1875</v>
+        <v>37.6167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>6|16|24|29|43|45|5</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,7 +4317,7 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
         <v>17</v>
@@ -4326,16 +4326,16 @@
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L42" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.77083333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14|17|24|29|34|45|12</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,10 +4415,10 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
@@ -4427,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.4375</v>
+        <v>36.8667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|13|24|26|41|44|27</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>9</v>
       </c>
       <c r="J44" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
+        <v>31</v>
+      </c>
+      <c r="L44" t="n">
+        <v>41</v>
+      </c>
+      <c r="M44" t="n">
         <v>30</v>
       </c>
-      <c r="L44" t="n">
-        <v>38</v>
-      </c>
-      <c r="M44" t="n">
-        <v>4</v>
-      </c>
       <c r="N44" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.16477272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>8|9|17|30|38|41|4</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.4375</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
         <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="N46" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.0625</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,19 +4757,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.3125</v>
+        <v>36.3667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|3|6|38|42|49|9</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="L47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.9375</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>6|11|20|39|40|49|8</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M48" t="n">
         <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.74519230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|18|24|33|35|38|27</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
@@ -5000,28 +5000,28 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.58035714285714</v>
+        <v>35.8667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>2|11|20|33|34|45|49</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5098,38 +5098,38 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
+        <v>44</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>149</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" t="n">
         <v>42</v>
       </c>
-      <c r="M50" t="n">
-        <v>27</v>
-      </c>
-      <c r="N50" t="n">
-        <v>153</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3</v>
-      </c>
-      <c r="P50" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>47</v>
-      </c>
       <c r="R50" t="n">
         <v>1</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.4375</v>
+        <v>35.7417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2|3|24|33|42|49|27</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5202,19 +5202,19 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="N51" t="n">
         <v>155</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.20220588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|12|20|31|44|45|32</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L52" t="n">
         <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.10416666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|33</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5395,25 +5395,25 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L53" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N53" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.01644736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>2|11|18|42|45|49|4</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N54" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>34.9375</v>
+        <v>35.3667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>6|11|18|29|40|49|46</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M55" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5642,16 +5642,16 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.86607142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|12|13|32|38|49|41</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>57.58</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,10 +677,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -689,13 +689,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>55.58</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -769,25 +769,25 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>51.58</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>3|21|22|29|38|4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -861,25 +861,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -912,16 +912,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>50.08</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>15|20|24|29|39|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>49.86571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1045,25 +1045,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
         <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.91333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>9|19|24|34|41|19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1140,19 +1140,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.58</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>7|13|25|34|42|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>47.58</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.33</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>8|9|22|29|35|13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
+        <v>27</v>
+      </c>
+      <c r="L11" t="n">
         <v>29</v>
       </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.30727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -1517,10 +1517,10 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>2|4|44|49|51|56|47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
@@ -1608,16 +1608,16 @@
         <v>22</v>
       </c>
       <c r="K13" t="n">
+        <v>31</v>
+      </c>
+      <c r="L13" t="n">
         <v>32</v>
       </c>
-      <c r="L13" t="n">
-        <v>37</v>
-      </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="N13" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,16 +1650,16 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.85</v>
+        <v>47.79</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>9|12|22|31|32|49|38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1693,22 +1693,22 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N14" t="n">
         <v>163</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,20 +1744,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.85</v>
+        <v>42.79</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>4|12|17|40|41|49|43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
         <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
         <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="N15" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.35</v>
+        <v>40.29</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>9|13|22|32|37|46|54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="N16" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.85</v>
+        <v>38.79</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>1|8|26|39|40|45|42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41</v>
+      </c>
+      <c r="L17" t="n">
+        <v>43</v>
+      </c>
+      <c r="M17" t="n">
         <v>11</v>
       </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>40</v>
-      </c>
-      <c r="L17" t="n">
-        <v>44</v>
-      </c>
-      <c r="M17" t="n">
-        <v>27</v>
-      </c>
       <c r="N17" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.85</v>
+        <v>37.79</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>4|12|16|41|43|49|11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L18" t="n">
         <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="N18" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.13571428571429</v>
+        <v>37.07571428571428</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>8|11|23|30|40|45|33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
         <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M19" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="N19" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,16 +2214,16 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.6</v>
+        <v>36.54</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>1|13|15|32|36|46|52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2260,22 +2260,22 @@
         <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2308,16 +2308,16 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.18333333333334</v>
+        <v>36.12333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>8|12|17|38|43|49|5</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
         <v>8</v>
       </c>
-      <c r="I21" t="n">
-        <v>15</v>
-      </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L21" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,16 +2402,16 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.85</v>
+        <v>35.79</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>4|8|17|36|41|49|3</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="N22" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.57727272727273</v>
+        <v>35.51727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>2|8|27|31|38|49|26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2539,13 +2539,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
         <v>33</v>
@@ -2555,16 +2555,16 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
         <v>12</v>
-      </c>
-      <c r="J24" t="n">
-        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.96</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>3|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,13 +2719,13 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.84</v>
+        <v>42.96</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
         <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.34</v>
+        <v>40.46</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>10|11|12|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,23 +2899,23 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.84</v>
+        <v>38.96</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
         <v>14</v>
@@ -3001,11 +3001,11 @@
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.84</v>
+        <v>38.68727272727273</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>4|9|14|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.12571428571429</v>
+        <v>37.96</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>5|10|14|25|33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
         <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.59</v>
+        <v>37.24571428571429</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,13 +3256,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.17333333333333</v>
+        <v>36.71</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.84</v>
+        <v>36.29333333333334</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3436,35 +3436,35 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>35.96</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K34" t="n">
         <v>44</v>
@@ -3548,16 +3548,16 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N34" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
         <v>48</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.86669999999999</v>
+        <v>74.5</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|42|44|46|49|34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" t="n">
         <v>17</v>
-      </c>
-      <c r="I35" t="n">
-        <v>19</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
         <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.8667</v>
+        <v>48.5</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>9|17|24|31|38|44|21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.8667</v>
+        <v>43.5</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>9|19|20|31|40|44|5</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3830,22 +3830,22 @@
         <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J37" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.3667</v>
+        <v>41</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>2|13|17|30|40|41|9</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N38" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.8667</v>
+        <v>39.5</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M39" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.8667</v>
+        <v>38.5</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>6|16|24|29|43|45|7</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L40" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,16 +4172,16 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.15241428571429</v>
+        <v>37.78571428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>5|17|20|34|38|45|22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4219,7 +4219,7 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I41" t="n">
         <v>18</v>
@@ -4228,16 +4228,16 @@
         <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L41" t="n">
         <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.6167</v>
+        <v>37.25</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>5|18|19|26|44|45|23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I42" t="n">
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N42" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.20003333333333</v>
+        <v>36.83333333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>14|17|19|34|39|44|12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
+        <v>13</v>
+      </c>
+      <c r="I43" t="n">
         <v>17</v>
       </c>
-      <c r="I43" t="n">
-        <v>19</v>
-      </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L43" t="n">
         <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N43" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.8667</v>
+        <v>36.5</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>13|17|20|30|31|44|23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
         <v>9</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
         <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M44" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.59397272727273</v>
+        <v>36.22727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>6|9|19|31|32|40|10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -4617,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
         <v>44</v>
@@ -4626,16 +4626,16 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N45" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
         <v>48</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.86669999999999</v>
+        <v>74.5</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|42|44|46|49|34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K46" t="n">
+        <v>34</v>
+      </c>
+      <c r="L46" t="n">
         <v>38</v>
       </c>
-      <c r="L46" t="n">
-        <v>44</v>
-      </c>
       <c r="M46" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,19 +4757,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.3667</v>
+        <v>38.5</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>1|3|12|34|38|49|15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N47" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.17439230769231</v>
+        <v>36</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>3|8|24|38|39|49|16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M48" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="N48" t="n">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.00955714285714</v>
+        <v>35.80769230769231</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>3|18|24|38|39|45|47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5000,28 +5000,28 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="N49" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5054,16 +5054,16 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.8667</v>
+        <v>35.64285714285714</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|6|23|38|40|49|45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
         <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N50" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.7417</v>
+        <v>35.375</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>11|18|20|29|45|46|15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L51" t="n">
         <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="N51" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,16 +5250,16 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.63140588235294</v>
+        <v>35.26470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>6|11|20|39|40|49|8</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
         <v>34</v>
       </c>
       <c r="L52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M52" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="N52" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.53336666666667</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|12|20|34|39|45|27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M53" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="N53" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.44564736842106</v>
+        <v>35.07894736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|12|24|34|45|49|48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
       </c>
       <c r="K54" t="n">
+        <v>32</v>
+      </c>
+      <c r="L54" t="n">
         <v>37</v>
       </c>
-      <c r="L54" t="n">
-        <v>38</v>
-      </c>
       <c r="M54" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N54" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.3667</v>
+        <v>35</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|18|24|32|37|39|41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L55" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="N55" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.29527142857143</v>
+        <v>34.92857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>2|11|20|33|34|45|49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
         <v>24</v>
@@ -597,10 +597,10 @@
         <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
         <v>107</v>
@@ -636,16 +636,16 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.58</v>
+        <v>57.57</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,25 +677,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -728,16 +728,16 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.58</v>
+        <v>55.57</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>1|7|21|30|34|2</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>53.07</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3|21|22|29|38|4</t>
+          <t>1|20|24|41|43|13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
         <v>15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -873,13 +873,13 @@
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.08</v>
+        <v>51.57</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -953,25 +953,25 @@
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.86571428571428</v>
+        <v>49.85571428571428</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>9|11|20|41|42|3</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1048,19 +1048,19 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
         <v>127</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.91333333333333</v>
+        <v>48.90333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|19</t>
+          <t>9|14|22|39|43|11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1134,28 +1134,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
+        <v>29</v>
+      </c>
+      <c r="L8" t="n">
         <v>34</v>
       </c>
-      <c r="L8" t="n">
-        <v>42</v>
-      </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.29727272727273</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|13|25|34|42|11</t>
+          <t>1|11|16|29|34|6</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1229,25 +1229,25 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" t="n">
         <v>19</v>
       </c>
-      <c r="J9" t="n">
-        <v>24</v>
-      </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1280,16 +1280,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.58</v>
+        <v>47.57</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>9|16|19|29|34|2</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
         <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>22</v>
@@ -1333,13 +1333,13 @@
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.33</v>
+        <v>46.32</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8|9|22|29|35|13</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>45.57</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>11|19|24|28|31|3</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.96</v>
+        <v>47.92</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
         <v>9</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>10</v>
-      </c>
-      <c r="J25" t="n">
-        <v>16</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.96</v>
+        <v>45.92</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|9|10|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,23 +2809,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>10</v>
       </c>
-      <c r="I26" t="n">
-        <v>11</v>
-      </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.46</v>
+        <v>40.42</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10|11|12|25|35</t>
+          <t>1|10|14|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,23 +2899,23 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.96</v>
+        <v>38.92</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,26 +2986,26 @@
         </is>
       </c>
       <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
         <v>10</v>
       </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>9</v>
-      </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.68727272727273</v>
+        <v>37.92</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4|9|14|25|35</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
         <v>5</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.96</v>
+        <v>37.20571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,35 +3166,35 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K30" t="n">
+        <v>21</v>
+      </c>
+      <c r="L30" t="n">
         <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.24571428571429</v>
+        <v>36.67</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
         <v>7</v>
       </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L31" t="n">
         <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.71</v>
+        <v>36.25333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>7|10|12|21|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
         <v>21</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.29333333333334</v>
+        <v>35.92</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>10|12|15|21|23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3436,35 +3436,35 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.96</v>
+        <v>35.64727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>4|6|11|25|27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>185</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.5</v>
+        <v>74.4667</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|34</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3682,7 +3682,7 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.5</v>
+        <v>48.4667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3780,7 +3780,7 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.5</v>
+        <v>43.4667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3878,7 +3878,7 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41</v>
+        <v>40.9667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3976,7 +3976,7 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.5</v>
+        <v>39.4667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4074,7 +4074,7 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.5</v>
+        <v>38.4667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4172,7 +4172,7 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.78571428571428</v>
+        <v>37.75241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4270,7 +4270,7 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.25</v>
+        <v>37.2167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4368,7 +4368,7 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.83333333333333</v>
+        <v>36.80003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4466,7 +4466,7 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.5</v>
+        <v>36.4667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4564,7 +4564,7 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.22727272727273</v>
+        <v>36.19397272727272</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N45" t="n">
         <v>185</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.5</v>
+        <v>74.4667</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|34</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M46" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="N46" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,23 +4757,23 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.5</v>
+        <v>35.9667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|3|12|34|38|49|15</t>
+          <t>3|18|24|38|39|45|47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M47" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36</v>
+        <v>35.77439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|8|24|38|39|49|16</t>
+          <t>3|18|24|35|40|49|2</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" t="n">
         <v>3</v>
@@ -4914,16 +4914,16 @@
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L48" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M48" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N48" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.80769230769231</v>
+        <v>35.60955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|18|24|38|39|45|47</t>
+          <t>3|18|24|32|37|39|41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
@@ -5000,28 +5000,28 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
+        <v>37</v>
+      </c>
+      <c r="L49" t="n">
         <v>38</v>
       </c>
-      <c r="L49" t="n">
-        <v>40</v>
-      </c>
       <c r="M49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N49" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.64285714285714</v>
+        <v>35.4667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|6|23|38|40|49|45</t>
+          <t>3|12|14|37|38|45|49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
+        <v>12</v>
+      </c>
+      <c r="J50" t="n">
         <v>18</v>
       </c>
-      <c r="J50" t="n">
-        <v>20</v>
-      </c>
       <c r="K50" t="n">
+        <v>25</v>
+      </c>
+      <c r="L50" t="n">
         <v>29</v>
       </c>
-      <c r="L50" t="n">
-        <v>45</v>
-      </c>
       <c r="M50" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N50" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.375</v>
+        <v>35.3417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11|18|20|29|45|46|15</t>
+          <t>3|12|18|25|29|38|24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" t="n">
         <v>6</v>
       </c>
-      <c r="I51" t="n">
-        <v>11</v>
-      </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="N51" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,16 +5250,16 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.26470588235294</v>
+        <v>35.23140588235295</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>6|11|20|39|40|49|8</t>
+          <t>3|6|24|33|44|49|34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5297,34 +5297,34 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L52" t="n">
+        <v>42</v>
+      </c>
+      <c r="M52" t="n">
+        <v>13</v>
+      </c>
+      <c r="N52" t="n">
+        <v>167</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>39</v>
-      </c>
-      <c r="M52" t="n">
-        <v>27</v>
-      </c>
-      <c r="N52" t="n">
-        <v>153</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>42</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.16666666666666</v>
+        <v>35.13336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|27</t>
+          <t>6|20|21|33|42|45|13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5395,25 +5395,25 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L53" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M53" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N53" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.07894736842105</v>
+        <v>35.04564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|24|34|45|49|48</t>
+          <t>4|19|20|31|42|45|33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N54" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35</v>
+        <v>34.9667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|18|24|32|37|39|41</t>
+          <t>11|16|20|29|38|45|35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M55" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="N55" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.92857142857143</v>
+        <v>34.89527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>2|11|20|33|34|45|49</t>
+          <t>3|6|21|32|40|49|9</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N13" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,16 +1650,16 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.79</v>
+        <v>47.82</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9|12|22|31|32|49|38</t>
+          <t>4|8|15|40|43|49|27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1693,34 +1693,34 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M14" t="n">
+        <v>58</v>
+      </c>
+      <c r="N14" t="n">
+        <v>151</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
         <v>43</v>
-      </c>
-      <c r="N14" t="n">
-        <v>163</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>45</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,16 +1744,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.79</v>
+        <v>42.82</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4|12|17|40|41|49|43</t>
+          <t>6|13|15|32|36|49|58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1787,10 +1787,10 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>22</v>
@@ -1799,13 +1799,13 @@
         <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N15" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.29</v>
+        <v>40.32</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9|13|22|32|37|46|54</t>
+          <t>1|8|22|32|41|49|34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.79</v>
+        <v>38.82</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1|8|26|39|40|45|42</t>
+          <t>11|12|27|34|44|47|9</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1975,22 +1975,22 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
         <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
         <v>165</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.79</v>
+        <v>37.82</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4|12|16|41|43|49|11</t>
+          <t>7|11|16|39|44|48|17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L18" t="n">
         <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.07571428571428</v>
+        <v>37.10571428571428</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8|11|23|30|40|45|33</t>
+          <t>10|17|27|33|40|48|8</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -2166,22 +2166,22 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="N19" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.54</v>
+        <v>36.57</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1|13|15|32|36|46|52</t>
+          <t>1|11|21|30|40|48|34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" t="n">
+        <v>26</v>
+      </c>
+      <c r="K20" t="n">
+        <v>30</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33</v>
+      </c>
+      <c r="M20" t="n">
         <v>8</v>
       </c>
-      <c r="I20" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>38</v>
-      </c>
-      <c r="L20" t="n">
-        <v>43</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
       <c r="N20" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.12333333333333</v>
+        <v>36.15333333333334</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|12|17|38|43|49|5</t>
+          <t>9|11|26|30|33|46|8</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -2351,34 +2351,34 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
+        <v>39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>31</v>
+      </c>
+      <c r="N21" t="n">
+        <v>171</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
         <v>41</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>155</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>45</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,16 +2402,16 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.79</v>
+        <v>35.82</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4|8|17|36|41|49|3</t>
+          <t>8|16|27|32|39|49|31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2445,34 +2445,34 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L22" t="n">
+        <v>43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>28</v>
+      </c>
+      <c r="N22" t="n">
+        <v>171</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
         <v>38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>26</v>
-      </c>
-      <c r="N22" t="n">
-        <v>155</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>47</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.51727272727273</v>
+        <v>35.54727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2|8|27|31|38|49|26</t>
+          <t>8|13|22|39|43|46|28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.92</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.92</v>
+        <v>47.93</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>45.92</v>
+        <v>42.93</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4|9|10|25|35</t>
+          <t>9|10|15|25|36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -2815,17 +2815,17 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.42</v>
+        <v>41.93</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|10|14|25|27</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.92</v>
+        <v>40.43</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,26 +2986,26 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
         <v>10</v>
-      </c>
-      <c r="J28" t="n">
-        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.92</v>
+        <v>39.68</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,13 +3076,13 @@
         </is>
       </c>
       <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
         <v>6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>10</v>
       </c>
       <c r="J29" t="n">
         <v>14</v>
@@ -3091,20 +3091,20 @@
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.20571428571429</v>
+        <v>37.93</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|10|14|25|33</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,32 +3166,32 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>21</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.67</v>
+        <v>37.21571428571428</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>6|10|13|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>12</v>
-      </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
         <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.25333333333333</v>
+        <v>36.26333333333334</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>7|10|12|21|27</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" t="n">
         <v>10</v>
       </c>
-      <c r="I32" t="n">
-        <v>12</v>
-      </c>
       <c r="J32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.92</v>
+        <v>35.93</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10|12|15|21|23</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J33" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
         <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.64727272727273</v>
+        <v>35.65727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|6|11|25|27</t>
+          <t>10|14|15|25|31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
         <v>44</v>
@@ -3548,16 +3548,16 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N34" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
         <v>48</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.4667</v>
+        <v>74.8</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|32</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
         <v>9</v>
       </c>
-      <c r="I35" t="n">
-        <v>17</v>
-      </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N35" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.4667</v>
+        <v>48.8</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9|17|24|31|38|44|21</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
+        <v>27</v>
+      </c>
+      <c r="L36" t="n">
         <v>31</v>
       </c>
-      <c r="L36" t="n">
-        <v>40</v>
-      </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="N36" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.4667</v>
+        <v>43.8</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|44|5</t>
+          <t>14|19|24|27|31|44|37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L37" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="N37" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>40.9667</v>
+        <v>41.3</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|13|17|30|40|41|9</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L38" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.4667</v>
+        <v>39.8</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>2|9|13|38|41|44|5</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -4023,34 +4023,34 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L39" t="n">
+        <v>36</v>
+      </c>
+      <c r="M39" t="n">
+        <v>35</v>
+      </c>
+      <c r="N39" t="n">
+        <v>153</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
         <v>43</v>
-      </c>
-      <c r="M39" t="n">
-        <v>7</v>
-      </c>
-      <c r="N39" t="n">
-        <v>163</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>39</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.4667</v>
+        <v>38.8</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|16|24|29|43|45|7</t>
+          <t>1|17|24|31|36|44|35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M40" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N40" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.75241428571429</v>
+        <v>38.08571428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>5|17|20|34|38|45|22</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
         <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N41" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.2167</v>
+        <v>37.55</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>5|18|19|26|44|45|23</t>
+          <t>6|9|19|31|36|40|37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
         <v>34</v>
       </c>
       <c r="L42" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N42" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.80003333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14|17|19|34|39|44|12</t>
+          <t>5|9|16|34|44|45|8</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,34 +4415,34 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I43" t="n">
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
+        <v>34</v>
+      </c>
+      <c r="L43" t="n">
+        <v>39</v>
+      </c>
+      <c r="M43" t="n">
+        <v>12</v>
+      </c>
+      <c r="N43" t="n">
+        <v>167</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>30</v>
-      </c>
-      <c r="L43" t="n">
-        <v>31</v>
-      </c>
-      <c r="M43" t="n">
-        <v>23</v>
-      </c>
-      <c r="N43" t="n">
-        <v>155</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>31</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,16 +4466,16 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.4667</v>
+        <v>36.8</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13|17|20|30|31|44|23</t>
+          <t>14|17|19|34|39|44|12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
+        <v>30</v>
+      </c>
+      <c r="L44" t="n">
         <v>31</v>
       </c>
-      <c r="L44" t="n">
-        <v>32</v>
-      </c>
       <c r="M44" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N44" t="n">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.19397272727272</v>
+        <v>36.52727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>6|9|19|31|32|40|10</t>
+          <t>13|17|20|30|31|44|23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4617,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
         <v>44</v>
@@ -4626,16 +4626,16 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N45" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
         <v>48</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.4667</v>
+        <v>74.8</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|32</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L46" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N46" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>35.9667</v>
+        <v>36.3</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|18|24|38|39|45|47</t>
+          <t>6|11|20|39|44|49|40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4816,16 +4816,16 @@
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L47" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N47" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.77439230769231</v>
+        <v>36.1076923076923</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|18|24|35|40|49|2</t>
+          <t>3|18|24|25|34|37|9</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L48" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M48" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="N48" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.60955714285714</v>
+        <v>35.94285714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|18|24|32|37|39|41</t>
+          <t>3|6|20|34|43|45|16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5006,10 +5006,10 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
         <v>37</v>
@@ -5018,10 +5018,10 @@
         <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="N49" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5054,16 +5054,16 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.4667</v>
+        <v>35.8</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|14|37|38|45|49</t>
+          <t>3|4|20|37|38|45|27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N50" t="n">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.3417</v>
+        <v>35.675</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|12|18|25|29|38|24</t>
+          <t>3|20|21|37|38|42|35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M51" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N51" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,16 +5250,16 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.23140588235295</v>
+        <v>35.56470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|24|33|44|49|34</t>
+          <t>2|3|15|38|46|49|29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
+        <v>18</v>
+      </c>
+      <c r="J52" t="n">
         <v>20</v>
       </c>
-      <c r="J52" t="n">
-        <v>21</v>
-      </c>
       <c r="K52" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L52" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M52" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N52" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.13336666666666</v>
+        <v>35.46666666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>6|20|21|33|42|45|13</t>
+          <t>3|18|20|29|37|38|7</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53">
@@ -5395,25 +5395,25 @@
         <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L53" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N53" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.04564736842106</v>
+        <v>35.37894736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>4|19|20|31|42|45|33</t>
+          <t>3|6|20|33|38|49|26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5493,10 +5493,10 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
         <v>20</v>
@@ -5505,13 +5505,13 @@
         <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M54" t="n">
         <v>35</v>
       </c>
       <c r="N54" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>34.9667</v>
+        <v>35.3</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11|16|20|29|38|45|35</t>
+          <t>3|18|20|29|42|49|35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L55" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M55" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="N55" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.89527142857143</v>
+        <v>35.22857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|6|21|32|40|49|9</t>
+          <t>3|19|24|28|35|38|20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.93000000000001</v>
+        <v>73.77</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.93</v>
+        <v>47.77</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3|10|12|25|27</t>
+          <t>1|10|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -2731,11 +2731,11 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.93</v>
+        <v>42.77</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>9|10|15|25|36</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>41.93</v>
+        <v>41.77</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,32 +2899,32 @@
         <v>3</v>
       </c>
       <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="I27" t="n">
-        <v>10</v>
-      </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.43</v>
+        <v>40.27</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,16 +2986,16 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.125</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>39.68</v>
+        <v>38.49727272727273</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>4|13|15|25|36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,13 +3079,13 @@
         <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
@@ -3095,16 +3095,16 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
         <v>2</v>
       </c>
-      <c r="P29" t="n">
-        <v>3</v>
-      </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.93</v>
+        <v>37.77</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3172,20 +3172,20 @@
         <v>6</v>
       </c>
       <c r="I30" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
-        <v>13</v>
-      </c>
       <c r="K30" t="n">
+        <v>21</v>
+      </c>
+      <c r="L30" t="n">
         <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.21571428571428</v>
+        <v>37.05571428571429</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|10|13|25|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
+        <v>23</v>
+      </c>
+      <c r="L31" t="n">
         <v>25</v>
-      </c>
-      <c r="L31" t="n">
-        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.26333333333334</v>
+        <v>36.52</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,35 +3346,35 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.93</v>
+        <v>36.10333333333333</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3436,26 +3436,26 @@
         </is>
       </c>
       <c r="G33" t="n">
+        <v>9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" t="n">
         <v>10</v>
-      </c>
-      <c r="H33" t="n">
-        <v>10</v>
-      </c>
-      <c r="I33" t="n">
-        <v>14</v>
-      </c>
-      <c r="J33" t="n">
-        <v>15</v>
       </c>
       <c r="K33" t="n">
         <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.65727272727273</v>
+        <v>35.77</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10|14|15|25|31</t>
+          <t>5|9|10|25|30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K34" t="n">
         <v>44</v>
@@ -3548,16 +3548,16 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N34" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
         <v>48</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.8</v>
+        <v>74.7333</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3682,7 +3682,7 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.8</v>
+        <v>48.7333</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="N36" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,16 +3780,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.8</v>
+        <v>43.7333</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14|19|24|27|31|44|37</t>
+          <t>9|17|24|31|38|44|21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
+        <v>41</v>
+      </c>
+      <c r="L37" t="n">
+        <v>44</v>
+      </c>
+      <c r="M37" t="n">
         <v>31</v>
       </c>
-      <c r="L37" t="n">
-        <v>36</v>
-      </c>
-      <c r="M37" t="n">
-        <v>48</v>
-      </c>
       <c r="N37" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.3</v>
+        <v>41.2333</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>6|7|24|41|44|45|31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L38" t="n">
         <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N38" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,16 +3976,16 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.8</v>
+        <v>39.7333</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>2|9|13|38|41|44|5</t>
+          <t>14|19|20|31|41|44|15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4029,19 +4029,19 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
         <v>31</v>
       </c>
       <c r="L39" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N39" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.8</v>
+        <v>38.7333</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>1|17|24|31|36|44|35</t>
+          <t>1|17|20|31|38|44|23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
+        <v>15</v>
+      </c>
+      <c r="J40" t="n">
         <v>19</v>
       </c>
-      <c r="J40" t="n">
-        <v>24</v>
-      </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L40" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N40" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.08571428571428</v>
+        <v>38.01901428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>2|15|19|40|44|45|17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,13 +4219,13 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
         <v>31</v>
@@ -4234,10 +4234,10 @@
         <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="N41" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.55</v>
+        <v>37.4833</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>6|9|19|31|36|40|37</t>
+          <t>11|19|24|31|36|40|15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J42" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L42" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N42" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.13333333333333</v>
+        <v>37.06663333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>5|9|16|34|44|45|8</t>
+          <t>1|15|24|38|40|41|29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L43" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M43" t="n">
         <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.8</v>
+        <v>36.7333</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14|17|19|34|39|44|12</t>
+          <t>1|9|22|38|42|45|12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M44" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N44" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.52727272727273</v>
+        <v>36.46057272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13|17|20|30|31|44|23</t>
+          <t>6|9|19|31|32|40|11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -4617,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
         <v>44</v>
@@ -4626,16 +4626,16 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N45" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
         <v>48</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.8</v>
+        <v>74.7333</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
         <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N46" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.3</v>
+        <v>36.2333</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|40</t>
+          <t>3|8|23|38|44|49|37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L47" t="n">
+        <v>45</v>
+      </c>
+      <c r="M47" t="n">
         <v>34</v>
       </c>
-      <c r="M47" t="n">
-        <v>9</v>
-      </c>
       <c r="N47" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.1076923076923</v>
+        <v>36.04099230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|18|24|25|34|37|9</t>
+          <t>3|6|20|32|45|49|34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M48" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N48" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4956,16 +4956,16 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.94285714285714</v>
+        <v>35.87615714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|6|20|34|43|45|16</t>
+          <t>3|12|24|38|39|45|32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5006,10 +5006,10 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
         <v>37</v>
@@ -5018,10 +5018,10 @@
         <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N49" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.8</v>
+        <v>35.7333</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|4|20|37|38|45|27</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
+        <v>11</v>
+      </c>
+      <c r="J50" t="n">
         <v>20</v>
       </c>
-      <c r="J50" t="n">
-        <v>21</v>
-      </c>
       <c r="K50" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="N50" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.675</v>
+        <v>35.6083</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|20|21|37|38|42|35</t>
+          <t>3|11|20|40|42|49|9</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="N51" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.56470588235294</v>
+        <v>35.49800588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2|3|15|38|46|49|29</t>
+          <t>3|6|20|31|40|45|13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L52" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N52" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.46666666666667</v>
+        <v>35.39996666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|18|20|29|37|38|7</t>
+          <t>6|20|21|31|45|46|32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J53" t="n">
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
         <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="N53" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.37894736842105</v>
+        <v>35.31224736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|6|20|33|38|49|26</t>
+          <t>3|15|20|29|38|46|17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
@@ -5496,16 +5496,16 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
         <v>35</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.3</v>
+        <v>35.2333</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|18|20|29|42|49|35</t>
+          <t>3|20|21|37|38|42|35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J55" t="n">
         <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M55" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="N55" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.22857142857143</v>
+        <v>35.16187142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|19|24|28|35|38|20</t>
+          <t>3|15|24|32|38|45|44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.77</v>
+        <v>73.86</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.77</v>
+        <v>47.86</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.77</v>
+        <v>42.86</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>41.77</v>
+        <v>41.86</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.27</v>
+        <v>40.36</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,35 +2986,35 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.49727272727273</v>
+        <v>39.19333333333333</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4|13|15|25|36</t>
+          <t>4|10|14|25|33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
-      </c>
-      <c r="J29" t="n">
-        <v>22</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
         <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.77</v>
+        <v>38.86</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>7|9|10|25|36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
         <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3215,19 +3215,19 @@
         <v>0.5</v>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.05571428571429</v>
+        <v>38.58727272727273</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>6|13|15|23|36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -3265,17 +3265,17 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.52</v>
+        <v>37.86</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>5|10|12|21|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O32" t="n">
         <v>2</v>
@@ -3374,7 +3374,7 @@
         <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.10333333333333</v>
+        <v>37.14571428571428</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>6|10|12|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3436,26 +3436,26 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
         <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>30</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.77</v>
+        <v>36.61</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5|9|10|25|30</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
         <v>44</v>
@@ -3548,16 +3548,16 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
         <v>48</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|5|44|46|49|4</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,13 +3631,13 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
         <v>38</v>
@@ -3646,10 +3646,10 @@
         <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.7333</v>
+        <v>48.6</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>1|9|24|38|44|45|4</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
+        <v>29</v>
+      </c>
+      <c r="L36" t="n">
         <v>31</v>
       </c>
-      <c r="L36" t="n">
-        <v>38</v>
-      </c>
       <c r="M36" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.7333</v>
+        <v>43.6</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9|17|24|31|38|44|21</t>
+          <t>2|16|24|29|31|41|7</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
         <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.2333</v>
+        <v>41.1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>6|7|24|41|44|45|31</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -3925,34 +3925,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I38" t="n">
+        <v>22</v>
+      </c>
+      <c r="J38" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" t="n">
+        <v>27</v>
+      </c>
+      <c r="L38" t="n">
+        <v>31</v>
+      </c>
+      <c r="M38" t="n">
+        <v>33</v>
+      </c>
+      <c r="N38" t="n">
+        <v>161</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>19</v>
-      </c>
-      <c r="J38" t="n">
-        <v>20</v>
-      </c>
-      <c r="K38" t="n">
-        <v>31</v>
-      </c>
-      <c r="L38" t="n">
-        <v>41</v>
-      </c>
-      <c r="M38" t="n">
-        <v>15</v>
-      </c>
-      <c r="N38" t="n">
-        <v>169</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>30</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.7333</v>
+        <v>39.6</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14|19|20|31|41|44|15</t>
+          <t>19|22|24|27|31|38|33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N39" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.7333</v>
+        <v>38.6</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>1|17|20|31|38|44|23</t>
+          <t>9|13|24|26|44|45|30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="M40" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="N40" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.01901428571428</v>
+        <v>37.88571428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|15|19|40|44|45|17</t>
+          <t>11|19|24|31|32|40|43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -4219,7 +4219,7 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
@@ -4228,16 +4228,16 @@
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L41" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N41" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4833</v>
+        <v>37.35</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|15</t>
+          <t>14|19|24|29|38|41|17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -4317,34 +4317,34 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
+        <v>37</v>
+      </c>
+      <c r="L42" t="n">
+        <v>41</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N42" t="n">
+        <v>163</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>38</v>
-      </c>
-      <c r="L42" t="n">
-        <v>40</v>
-      </c>
-      <c r="M42" t="n">
-        <v>29</v>
-      </c>
-      <c r="N42" t="n">
-        <v>159</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>40</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.06663333333333</v>
+        <v>36.93333333333334</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|15|24|38|40|41|29</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J43" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L43" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M43" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="N43" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.7333</v>
+        <v>36.6</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|9|22|38|42|45|12</t>
+          <t>5|14|16|34|45|49|25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -4516,22 +4516,22 @@
         <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
         <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M44" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="N44" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.46057272727273</v>
+        <v>36.32727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>6|9|19|31|32|40|11</t>
+          <t>6|19|24|31|40|49|38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45">
@@ -4617,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
         <v>44</v>
@@ -4626,16 +4626,16 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
         <v>48</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|5|44|46|49|4</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L46" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M46" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.2333</v>
+        <v>36.1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|37</t>
+          <t>11|20|21|29|42|44|48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L47" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M47" t="n">
         <v>34</v>
       </c>
       <c r="N47" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.04099230769231</v>
+        <v>35.90769230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|6|20|32|45|49|34</t>
+          <t>3|18|24|31|38|45|34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L48" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N48" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.87615714285714</v>
+        <v>35.74285714285715</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|12|24|38|39|45|32</t>
+          <t>3|8|20|29|44|49|30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L49" t="n">
         <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.7333</v>
+        <v>35.6</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|15|18|36|38|39|10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
@@ -5101,7 +5101,7 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I50" t="n">
         <v>11</v>
@@ -5110,16 +5110,16 @@
         <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L50" t="n">
         <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="N50" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,16 +5152,16 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.6083</v>
+        <v>35.475</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|11|20|40|42|49|9</t>
+          <t>9|11|20|28|42|49|37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="N51" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.49800588235294</v>
+        <v>35.36470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|20|31|40|45|13</t>
+          <t>3|12|20|33|38|49|46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L52" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M52" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N52" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.39996666666666</v>
+        <v>35.26666666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>6|20|21|31|45|46|32</t>
+          <t>2|3|15|38|46|49|28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J53" t="n">
+        <v>18</v>
+      </c>
+      <c r="K53" t="n">
+        <v>38</v>
+      </c>
+      <c r="L53" t="n">
+        <v>44</v>
+      </c>
+      <c r="M53" t="n">
         <v>20</v>
       </c>
-      <c r="K53" t="n">
-        <v>29</v>
-      </c>
-      <c r="L53" t="n">
-        <v>38</v>
-      </c>
-      <c r="M53" t="n">
-        <v>17</v>
-      </c>
       <c r="N53" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.31224736842105</v>
+        <v>35.17894736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|46|17</t>
+          <t>3|7|18|38|44|45|20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K54" t="n">
+        <v>26</v>
+      </c>
+      <c r="L54" t="n">
         <v>37</v>
       </c>
-      <c r="L54" t="n">
-        <v>38</v>
-      </c>
       <c r="M54" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="N54" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.2333</v>
+        <v>35.1</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|20|21|37|38|42|35</t>
+          <t>3|8|18|26|37|49|24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
+        <v>25</v>
+      </c>
+      <c r="L55" t="n">
         <v>32</v>
       </c>
-      <c r="L55" t="n">
-        <v>38</v>
-      </c>
       <c r="M55" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="N55" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.16187142857143</v>
+        <v>35.02857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|15|24|32|38|45|44</t>
+          <t>1|2|21|25|32|44|9</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -585,25 +585,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -633,19 +633,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.57</v>
+        <v>60.51</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>9|15|20|38|43|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -680,22 +680,22 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -728,16 +728,16 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.57</v>
+        <v>55.51</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1|7|21|30|34|2</t>
+          <t>1|20|24|41|43|13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>53.07</v>
+        <v>51.51</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1|20|24|41|43|13</t>
+          <t>8|15|24|29|43|6</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -873,13 +873,13 @@
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>51.57</v>
+        <v>50.01</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.85571428571428</v>
+        <v>49.26</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9|11|20|41|42|3</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.90333333333333</v>
+        <v>48.23727272727272</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
         <v>29</v>
@@ -1152,10 +1152,10 @@
         <v>34</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N8" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1185,19 +1185,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.29727272727273</v>
+        <v>47.51</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1|11|16|29|34|6</t>
+          <t>19|21|22|29|34|18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1280,16 +1280,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>47.57</v>
+        <v>46.79571428571428</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9|16|19|29|34|2</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.32</v>
+        <v>45.84333333333333</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>11|19|24|31|34|11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1413,25 +1413,25 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.57</v>
+        <v>45.51</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11|19|24|28|31|3</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.86</v>
+        <v>73.87</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.86</v>
+        <v>47.87</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1|10|14|25|27</t>
+          <t>6|14|15|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.86</v>
+        <v>42.87</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>41.86</v>
+        <v>41.87</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2902,29 +2902,29 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
+        <v>21</v>
+      </c>
+      <c r="L27" t="n">
         <v>25</v>
-      </c>
-      <c r="L27" t="n">
-        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="P27" t="n">
-        <v>3</v>
-      </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.36</v>
+        <v>40.37</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>4|7|10|21|25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3038,7 +3038,7 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>39.19333333333333</v>
+        <v>39.20333333333333</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,13 +3079,13 @@
         <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>38.86</v>
+        <v>38.87</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7|9|10|25|36</t>
+          <t>1|10|15|25|36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="H30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I30" t="n">
-        <v>13</v>
-      </c>
-      <c r="J30" t="n">
-        <v>15</v>
-      </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3215,19 +3215,19 @@
         <v>0.5</v>
       </c>
       <c r="X30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>38.58727272727273</v>
+        <v>37.87</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|13|15|23|36</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,7 +3308,7 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>37.86</v>
+        <v>37.15571428571428</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,35 +3346,35 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
-        <v>3</v>
-      </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>37.14571428571428</v>
+        <v>36.62</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|10|12|21|25</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3436,26 +3436,26 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.125</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>36.61</v>
+        <v>35.59727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>10|14|15|25|31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.59999999999999</v>
+        <v>74.4375</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|4</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N35" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6</v>
+        <v>48.4375</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|9|24|38|44|45|4</t>
+          <t>7|16|24|27|33|44|23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L36" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="N36" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6</v>
+        <v>43.4375</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2|16|24|29|31|41|7</t>
+          <t>1|9|24|40|44|45|34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -3827,22 +3827,22 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M37" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1</v>
+        <v>40.9375</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>5|20|24|30|41|45|13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>17</v>
+      </c>
+      <c r="K38" t="n">
+        <v>26</v>
+      </c>
+      <c r="L38" t="n">
+        <v>40</v>
+      </c>
+      <c r="M38" t="n">
         <v>22</v>
       </c>
-      <c r="J38" t="n">
-        <v>24</v>
-      </c>
-      <c r="K38" t="n">
-        <v>27</v>
-      </c>
-      <c r="L38" t="n">
-        <v>31</v>
-      </c>
-      <c r="M38" t="n">
-        <v>33</v>
-      </c>
       <c r="N38" t="n">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6</v>
+        <v>39.4375</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19|22|24|27|31|38|33</t>
+          <t>1|2|17|26|40|41|22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L39" t="n">
         <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6</v>
+        <v>38.4375</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>9|13|24|26|44|45|30</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
+        <v>16</v>
+      </c>
+      <c r="J40" t="n">
         <v>19</v>
-      </c>
-      <c r="J40" t="n">
-        <v>24</v>
       </c>
       <c r="K40" t="n">
         <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M40" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N40" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.88571428571429</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11|19|24|31|32|40|43</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
         <v>14</v>
       </c>
-      <c r="I41" t="n">
-        <v>19</v>
-      </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L41" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.35</v>
+        <v>37.1875</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14|19|24|29|38|41|17</t>
+          <t>5|14|16|34|45|49|25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L42" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.93333333333334</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>11|19|24|31|36|40|15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
         <v>34</v>
       </c>
       <c r="L43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6</v>
+        <v>36.4375</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|14|16|34|45|49|25</t>
+          <t>9|16|21|34|44|45|4</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -4564,7 +4564,7 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.32727272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.59999999999999</v>
+        <v>74.4375</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|4</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4760,7 +4760,7 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1</v>
+        <v>35.9375</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4858,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.90769230769231</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4956,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.74285714285715</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5054,7 +5054,7 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6</v>
+        <v>35.4375</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5152,7 +5152,7 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.475</v>
+        <v>35.3125</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5250,7 +5250,7 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.36470588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5348,7 +5348,7 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.26666666666667</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5446,7 +5446,7 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.17894736842106</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1</v>
+        <v>34.9375</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5642,7 +5642,7 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.02857142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
         <v>44</v>
@@ -1520,10 +1520,10 @@
         <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.81999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|47</t>
+          <t>6|8|44|49|51|56|20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L13" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N13" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.82</v>
+        <v>47.85</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|27</t>
+          <t>6|12|29|35|39|48|11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
         <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L14" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="N14" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,16 +1744,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.82</v>
+        <v>42.85</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6|13|15|32|36|49|58</t>
+          <t>4|8|15|40|43|49|26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,16 +1838,16 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.32</v>
+        <v>40.35</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1|8|22|32|41|49|34</t>
+          <t>4|8|16|33|37|49|10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.82</v>
+        <v>38.85</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11|12|27|34|44|47|9</t>
+          <t>9|13|15|32|40|48|8</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="N17" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.82</v>
+        <v>37.85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|17</t>
+          <t>8|11|24|36|43|49|34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="N18" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.10571428571428</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10|17|27|33|40|48|8</t>
+          <t>12|13|19|32|39|48|31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
         <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M19" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="N19" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,16 +2214,16 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.57</v>
+        <v>36.6</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1|11|21|30|40|48|34</t>
+          <t>7|11|16|39|44|48|15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L20" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M20" t="n">
         <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.15333333333334</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9|11|26|30|33|46|8</t>
+          <t>10|17|27|33|40|48|8</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2354,19 +2354,19 @@
         <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L21" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
         <v>171</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.82</v>
+        <v>35.85</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|16|27|32|39|49|31</t>
+          <t>8|13|22|39|43|46|28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
         <v>8</v>
       </c>
-      <c r="I22" t="n">
-        <v>13</v>
-      </c>
       <c r="J22" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.54727272727273</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8|13|22|39|43|46|28</t>
+          <t>4|8|29|37|40|49|36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2539,13 +2539,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
         <v>6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>10</v>
-      </c>
-      <c r="J23" t="n">
-        <v>12</v>
       </c>
       <c r="K23" t="n">
         <v>33</v>
@@ -2555,16 +2555,16 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="P23" t="n">
-        <v>3</v>
-      </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.87</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.87</v>
+        <v>47.9</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>6|14|15|25|27</t>
+          <t>4|5|10|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,32 +2719,32 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.87</v>
+        <v>42.9</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|10|14|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
-      </c>
-      <c r="J26" t="n">
-        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2858,16 +2858,16 @@
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>41.87</v>
+        <v>40.9</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,23 +2899,23 @@
         <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.37</v>
+        <v>40.4</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|7|10|21|25</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,35 +2986,35 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>3</v>
-      </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>39.20333333333333</v>
+        <v>40.18571428571428</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4|10|14|25|33</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,35 +3076,35 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
         <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>38.87</v>
+        <v>38.9</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1|10|15|25|36</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.87</v>
+        <v>36.65</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>37.15571428571428</v>
+        <v>36.23333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5|10|12|21|27</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="G32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" t="n">
         <v>7</v>
       </c>
-      <c r="H32" t="n">
-        <v>5</v>
-      </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J32" t="n">
         <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.62</v>
+        <v>35.9</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>7|9|14|24|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
+        <v>7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" t="n">
         <v>10</v>
-      </c>
-      <c r="I33" t="n">
-        <v>14</v>
-      </c>
-      <c r="J33" t="n">
-        <v>15</v>
       </c>
       <c r="K33" t="n">
         <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.59727272727272</v>
+        <v>35.62727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10|14|15|25|31</t>
+          <t>7|9|10|25|36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.4375</v>
+        <v>74.5625</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M35" t="n">
         <v>23</v>
       </c>
       <c r="N35" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.4375</v>
+        <v>48.5625</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>7|16|24|27|33|44|23</t>
+          <t>16|17|22|31|38|45|23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M36" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N36" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.4375</v>
+        <v>43.5625</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>1|9|24|40|44|45|34</t>
+          <t>16|17|24|29|31|34|27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
+        <v>19</v>
+      </c>
+      <c r="J37" t="n">
         <v>20</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
+        <v>31</v>
+      </c>
+      <c r="L37" t="n">
+        <v>37</v>
+      </c>
+      <c r="M37" t="n">
         <v>24</v>
       </c>
-      <c r="K37" t="n">
-        <v>30</v>
-      </c>
-      <c r="L37" t="n">
-        <v>41</v>
-      </c>
-      <c r="M37" t="n">
-        <v>13</v>
-      </c>
       <c r="N37" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>40.9375</v>
+        <v>41.0625</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>5|20|24|30|41|45|13</t>
+          <t>16|19|20|31|37|44|24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,13 +3925,13 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
         <v>26</v>
@@ -3940,10 +3940,10 @@
         <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="N38" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.4375</v>
+        <v>39.5625</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>1|2|17|26|40|41|22</t>
+          <t>3|19|24|26|40|45|9</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -4026,22 +4026,22 @@
         <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.4375</v>
+        <v>38.5625</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>6|19|24|30|41|43|23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
         <v>16</v>
       </c>
-      <c r="J40" t="n">
-        <v>19</v>
-      </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L40" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.72321428571428</v>
+        <v>37.84821428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>1|3|16|38|44|45|11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4222,22 +4222,22 @@
         <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L41" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="N41" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.1875</v>
+        <v>37.3125</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>5|14|16|34|45|49|25</t>
+          <t>5|9|24|26|38|43|13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
@@ -4317,34 +4317,34 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K42" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L42" t="n">
+        <v>44</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>169</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="n">
         <v>36</v>
-      </c>
-      <c r="M42" t="n">
-        <v>15</v>
-      </c>
-      <c r="N42" t="n">
-        <v>161</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>29</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.77083333333333</v>
+        <v>36.89583333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|15</t>
+          <t>9|16|21|34|44|45|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L43" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N43" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.4375</v>
+        <v>36.5625</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>9|16|21|34|44|45|4</t>
+          <t>3|20|24|31|38|41|30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -4513,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I44" t="n">
         <v>19</v>
@@ -4522,16 +4522,16 @@
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L44" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M44" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.16477272727273</v>
+        <v>36.28977272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|49|38</t>
+          <t>14|19|24|26|41|43|6</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.4375</v>
+        <v>74.5625</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,38 +4706,38 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H46" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" t="n">
         <v>20</v>
       </c>
-      <c r="J46" t="n">
-        <v>21</v>
-      </c>
       <c r="K46" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>161</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="n">
         <v>48</v>
       </c>
-      <c r="N46" t="n">
-        <v>167</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3</v>
-      </c>
-      <c r="P46" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>33</v>
-      </c>
       <c r="R46" t="n">
         <v>1</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,23 +4757,23 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>35.9375</v>
+        <v>38.70535714285714</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11|20|21|29|42|44|48</t>
+          <t>1|8|20|38|45|49|3</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
@@ -4816,16 +4816,16 @@
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M47" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="N47" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.74519230769231</v>
+        <v>36.0625</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|18|24|31|38|45|34</t>
+          <t>3|18|24|38|39|45|47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="N48" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.58035714285714</v>
+        <v>35.87019230769231</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|8|20|29|44|49|30</t>
+          <t>3|12|14|37|38|45|49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M49" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N49" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.4375</v>
+        <v>35.5625</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|15|18|36|38|39|10</t>
+          <t>3|12|20|31|45|46|34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K50" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L50" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="N50" t="n">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,16 +5152,16 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.3125</v>
+        <v>35.4375</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>9|11|20|28|42|49|37</t>
+          <t>3|6|15|26|38|49|13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L51" t="n">
         <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N51" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.20220588235294</v>
+        <v>35.32720588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|12|20|33|38|49|46</t>
+          <t>11|16|20|29|38|45|36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5297,34 +5297,34 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L52" t="n">
+        <v>45</v>
+      </c>
+      <c r="M52" t="n">
+        <v>17</v>
+      </c>
+      <c r="N52" t="n">
+        <v>161</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>46</v>
-      </c>
-      <c r="M52" t="n">
-        <v>28</v>
-      </c>
-      <c r="N52" t="n">
-        <v>153</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>47</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.10416666666666</v>
+        <v>35.22916666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>2|3|15|38|46|49|28</t>
+          <t>3|18|20|26|45|49|17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L53" t="n">
+        <v>32</v>
+      </c>
+      <c r="M53" t="n">
         <v>44</v>
       </c>
-      <c r="M53" t="n">
-        <v>20</v>
-      </c>
       <c r="N53" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.01644736842105</v>
+        <v>35.14144736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|7|18|38|44|45|20</t>
+          <t>3|12|20|31|32|37|44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L54" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M54" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="N54" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5544,16 +5544,16 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>34.9375</v>
+        <v>35.0625</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|8|18|26|37|49|24</t>
+          <t>3|18|24|27|40|49|38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L55" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N55" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.86607142857143</v>
+        <v>34.99107142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>1|2|21|25|32|44|9</t>
+          <t>3|5|22|34|37|40|11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -585,25 +585,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -633,19 +633,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.51</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9|15|20|38|43|18</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -677,22 +677,22 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
         <v>129</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.51</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1|20|24|41|43|13</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -769,22 +769,22 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>119</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -820,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.51</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|6</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -861,25 +861,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
         <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -912,16 +912,16 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.01</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -956,22 +956,22 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.26</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1042,28 +1042,28 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
-        <v>9</v>
-      </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.23727272727272</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|14|22|39|43|11</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1134,28 +1134,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
         <v>19</v>
       </c>
-      <c r="I8" t="n">
-        <v>21</v>
-      </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1185,19 +1185,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>47.51</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19|21|22|29|34|18</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
         <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.79571428571428</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
@@ -1330,16 +1330,16 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>45.84333333333333</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11|19|24|31|34|11</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
         <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.51</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:39</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>44</v>
@@ -1517,13 +1517,13 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N12" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6|8|44|49|51|56|20</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1654,16 +1654,16 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6|12|29|35|39|48|11</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
+        <v>33</v>
+      </c>
+      <c r="L14" t="n">
         <v>40</v>
       </c>
-      <c r="L14" t="n">
-        <v>43</v>
-      </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="N14" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1748,16 +1748,16 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|26</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
+        <v>18</v>
+      </c>
+      <c r="K15" t="n">
+        <v>32</v>
+      </c>
+      <c r="L15" t="n">
+        <v>39</v>
+      </c>
+      <c r="M15" t="n">
         <v>16</v>
       </c>
-      <c r="K15" t="n">
-        <v>33</v>
-      </c>
-      <c r="L15" t="n">
-        <v>37</v>
-      </c>
-      <c r="M15" t="n">
-        <v>10</v>
-      </c>
       <c r="N15" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1842,16 +1842,16 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|8|16|33|37|49|10</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1936,16 +1936,16 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9|13|15|32|40|48|8</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N17" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2030,16 +2030,16 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8|11|24|36|43|49|34</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>12</v>
       </c>
-      <c r="I18" t="n">
-        <v>13</v>
-      </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2124,16 +2124,16 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12|13|19|32|39|48|31</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2218,16 +2218,16 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|15</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2312,16 +2312,16 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10|17|27|33|40|48|8</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2354,22 +2354,22 @@
         <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2406,16 +2406,16 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|13|22|39|43|46|28</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
         <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2500,16 +2500,16 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4|8|29|37|40|49|36</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.90000000000001</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.9</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4|5|10|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,32 +2719,32 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.9</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4|10|14|25|35</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,22 +2806,22 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.9</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="J27" t="n">
-        <v>15</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.4</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,26 +2986,26 @@
         </is>
       </c>
       <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
         <v>6</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>40.18571428571428</v>
+        <v>37.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,35 +3076,35 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
         <v>2</v>
       </c>
-      <c r="P29" t="n">
-        <v>3</v>
-      </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>38.9</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.65</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>14</v>
-      </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.23333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
         <v>9</v>
       </c>
       <c r="J32" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.9</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>7|9|14|24|27</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3442,20 +3442,20 @@
         <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>36</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.62727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>7|9|10|25|36</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.5625</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,22 +3631,22 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L35" t="n">
         <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="N35" t="n">
         <v>169</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,16 +3682,16 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.5625</v>
+        <v>48.8667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16|17|22|31|38|45|23</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.5625</v>
+        <v>43.8667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16|17|24|29|31|34|27</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -3827,19 +3827,19 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
         <v>16</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>19</v>
       </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
       <c r="K37" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L37" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
         <v>24</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.0625</v>
+        <v>41.3667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16|19|20|31|37|44|24</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -3925,13 +3925,13 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
         <v>26</v>
@@ -3940,10 +3940,10 @@
         <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.5625</v>
+        <v>39.8667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>3|19|24|26|40|45|9</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,10 +4023,10 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
@@ -4035,13 +4035,13 @@
         <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="N39" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.5625</v>
+        <v>38.8667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|19|24|30|41|43|23</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,16 +4172,16 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.84821428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>1|3|16|38|44|45|11</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.3125</v>
+        <v>37.6167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>5|9|24|26|38|43|13</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4317,19 +4317,19 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L42" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
         <v>4</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.89583333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|16|21|34|44|45|4</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
+        <v>26</v>
+      </c>
+      <c r="L43" t="n">
         <v>31</v>
       </c>
-      <c r="L43" t="n">
-        <v>38</v>
-      </c>
       <c r="M43" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.5625</v>
+        <v>36.8667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|20|24|31|38|41|30</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L44" t="n">
         <v>41</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="N44" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.28977272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14|19|24|26|41|43|6</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.5625</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4706,28 +4706,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
         <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
         <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="N46" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4757,19 +4757,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.70535714285714</v>
+        <v>36.3667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|8|20|38|45|49|3</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4804,28 +4804,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
+        <v>34</v>
+      </c>
+      <c r="L47" t="n">
         <v>38</v>
       </c>
-      <c r="L47" t="n">
-        <v>39</v>
-      </c>
       <c r="M47" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="N47" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.0625</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|18|24|38|39|45|47</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4902,28 +4902,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M48" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.87019230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|12|14|37|38|45|49</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
@@ -5009,19 +5009,19 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.5625</v>
+        <v>35.8667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|20|31|45|46|34</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5107,19 +5107,19 @@
         <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.4375</v>
+        <v>35.7417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|15|26|38|49|13</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="N51" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.32720588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11|16|20|29|38|45|36</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L52" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5348,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.22916666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|18|20|26|45|49|17</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
+        <v>20</v>
+      </c>
+      <c r="J53" t="n">
+        <v>23</v>
+      </c>
+      <c r="K53" t="n">
+        <v>32</v>
+      </c>
+      <c r="L53" t="n">
+        <v>38</v>
+      </c>
+      <c r="M53" t="n">
         <v>12</v>
       </c>
-      <c r="J53" t="n">
-        <v>20</v>
-      </c>
-      <c r="K53" t="n">
-        <v>31</v>
-      </c>
-      <c r="L53" t="n">
-        <v>32</v>
-      </c>
-      <c r="M53" t="n">
-        <v>44</v>
-      </c>
       <c r="N53" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.14144736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|20|31|32|37|44</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="N54" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.0625</v>
+        <v>35.3667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|18|24|27|40|49|38</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M55" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.99107142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|5|22|34|37|40|11</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -585,25 +585,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -633,19 +633,19 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.59</v>
+        <v>60.63</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>9|15|20|38|43|18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -674,25 +674,25 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
         <v>129</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.59</v>
+        <v>53.13</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15|19|24|29|42|18</t>
+          <t>1|20|24|41|43|13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M4" t="n">
         <v>11</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>31</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -817,19 +817,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.59</v>
+        <v>52.63</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
@@ -876,10 +876,10 @@
         <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.09</v>
+        <v>50.63</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16|19|22|29|43|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -953,25 +953,25 @@
         <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
         <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.34</v>
+        <v>49.38</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|12|13|28|37|18</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1045,25 +1045,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.92333333333333</v>
+        <v>48.96333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10|20|23|31|41|15</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>19</v>
@@ -1146,16 +1146,16 @@
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1185,19 +1185,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.59</v>
+        <v>48.63</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|12</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1229,25 +1229,25 @@
         <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1280,16 +1280,16 @@
         <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.31727272727273</v>
+        <v>48.35727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|13|20|28|39|18</t>
+          <t>5|16|19|29|34|2</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>47.59</v>
+        <v>46.91571428571429</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17|19|24|26|43|3</t>
+          <t>19|21|22|29|34|18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
+        <v>27</v>
+      </c>
+      <c r="L11" t="n">
         <v>29</v>
       </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>46.87571428571429</v>
+        <v>45.63</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13|15|20|29|30|2</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
         <v>44</v>
@@ -1517,13 +1517,13 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>6|8|44|49|51|56|20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="N13" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1654,16 +1654,16 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>6|12|29|35|39|48|11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -1693,25 +1693,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N14" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1748,16 +1748,16 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>4|8|15|40|43|49|26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
         <v>8</v>
       </c>
-      <c r="I15" t="n">
-        <v>13</v>
-      </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1842,16 +1842,16 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>4|8|16|33|37|49|10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
+        <v>13</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>32</v>
+      </c>
+      <c r="L16" t="n">
+        <v>40</v>
+      </c>
+      <c r="M16" t="n">
         <v>8</v>
       </c>
-      <c r="J16" t="n">
-        <v>23</v>
-      </c>
-      <c r="K16" t="n">
-        <v>38</v>
-      </c>
-      <c r="L16" t="n">
-        <v>43</v>
-      </c>
-      <c r="M16" t="n">
-        <v>16</v>
-      </c>
       <c r="N16" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1936,16 +1936,16 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>9|13|15|32|40|48|8</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="N17" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2030,16 +2030,16 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>8|11|24|36|43|49|34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -2069,34 +2069,34 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
+        <v>32</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31</v>
+      </c>
+      <c r="N18" t="n">
+        <v>163</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>36</v>
-      </c>
-      <c r="L18" t="n">
-        <v>40</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>153</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>48</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2124,16 +2124,16 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>12|13|19|32|39|48|31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M19" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="N19" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2218,16 +2218,16 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>7|11|16|39|44|48|15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>27</v>
+      </c>
+      <c r="K20" t="n">
+        <v>33</v>
+      </c>
+      <c r="L20" t="n">
+        <v>40</v>
+      </c>
+      <c r="M20" t="n">
         <v>8</v>
       </c>
-      <c r="I20" t="n">
-        <v>11</v>
-      </c>
-      <c r="J20" t="n">
-        <v>15</v>
-      </c>
-      <c r="K20" t="n">
-        <v>36</v>
-      </c>
-      <c r="L20" t="n">
-        <v>42</v>
-      </c>
-      <c r="M20" t="n">
-        <v>28</v>
-      </c>
       <c r="N20" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2312,16 +2312,16 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>10|17|27|33|40|48|8</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2354,22 +2354,22 @@
         <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L21" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2406,16 +2406,16 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>8|13|22|39|43|46|28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L22" t="n">
         <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2500,16 +2500,16 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>4|8|29|37|40|49|36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2539,32 +2539,32 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
         <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.8</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1|6|10|33|35</t>
+          <t>5|7|10|34|36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,23 +2629,23 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
         <v>12</v>
-      </c>
-      <c r="J24" t="n">
-        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.8</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|12|14|25|27</t>
+          <t>9|10|12|25|35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,13 +2719,13 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.84</v>
+        <v>42.8</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|10|12|25|27</t>
+          <t>6|14|15|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,35 +2806,35 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="J26" t="n">
-        <v>12</v>
-      </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.34</v>
+        <v>41.8</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
+        <v>21</v>
+      </c>
+      <c r="L27" t="n">
         <v>25</v>
-      </c>
-      <c r="L27" t="n">
-        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.84</v>
+        <v>40.3</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>5|10|12|21|25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
         <v>14</v>
@@ -3001,7 +3001,7 @@
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.84</v>
+        <v>39.13333333333333</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|13|14|25|27</t>
+          <t>4|7|14|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
-      </c>
-      <c r="J29" t="n">
-        <v>11</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.12571428571429</v>
+        <v>37.8</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,32 +3166,32 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>21</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.59</v>
+        <v>37.08571428571428</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
       </c>
       <c r="K31" t="n">
+        <v>24</v>
+      </c>
+      <c r="L31" t="n">
         <v>25</v>
-      </c>
-      <c r="L31" t="n">
-        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.17333333333333</v>
+        <v>36.55</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>7|9|10|24|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.84</v>
+        <v>35.8</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>9|10|14|27|35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,13 +3439,13 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
         <v>23</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>35.52727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>8|10|15|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.86669999999999</v>
+        <v>74.7333</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I35" t="n">
         <v>19</v>
@@ -3640,16 +3640,16 @@
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M35" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.8667</v>
+        <v>48.7333</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>14|19|24|27|31|44|37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N36" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.8667</v>
+        <v>43.7333</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>2|17|22|31|38|41|23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" t="n">
         <v>16</v>
       </c>
-      <c r="J37" t="n">
-        <v>19</v>
-      </c>
       <c r="K37" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L37" t="n">
         <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.3667</v>
+        <v>41.2333</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,34 +3925,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
+        <v>41</v>
+      </c>
+      <c r="M38" t="n">
+        <v>48</v>
+      </c>
+      <c r="N38" t="n">
+        <v>165</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>40</v>
-      </c>
-      <c r="M38" t="n">
-        <v>6</v>
-      </c>
-      <c r="N38" t="n">
-        <v>143</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>32</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.8667</v>
+        <v>39.7333</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>5|20|24|30|41|45|48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.8667</v>
+        <v>38.7333</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>16|19|20|31|37|44|26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J40" t="n">
+        <v>13</v>
+      </c>
+      <c r="K40" t="n">
+        <v>38</v>
+      </c>
+      <c r="L40" t="n">
+        <v>41</v>
+      </c>
+      <c r="M40" t="n">
         <v>6</v>
       </c>
-      <c r="I40" t="n">
-        <v>19</v>
-      </c>
-      <c r="J40" t="n">
-        <v>24</v>
-      </c>
-      <c r="K40" t="n">
-        <v>26</v>
-      </c>
-      <c r="L40" t="n">
-        <v>31</v>
-      </c>
-      <c r="M40" t="n">
-        <v>7</v>
-      </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.15241428571429</v>
+        <v>38.01901428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>2|9|13|38|41|44|6</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.6167</v>
+        <v>37.4833</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>8|19|24|31|40|41|6</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
         <v>16</v>
-      </c>
-      <c r="I42" t="n">
-        <v>17</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.20003333333333</v>
+        <v>37.06663333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>3|16|24|31|43|48|5</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L43" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N43" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.8667</v>
+        <v>36.7333</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>5|13|21|30|32|38|7</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
@@ -4513,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I44" t="n">
         <v>9</v>
@@ -4522,16 +4522,16 @@
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L44" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M44" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.59397272727273</v>
+        <v>36.46057272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>7|9|24|34|44|45|16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.86669999999999</v>
+        <v>74.7333</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4712,22 +4712,22 @@
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L46" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M46" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.3667</v>
+        <v>36.2333</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|18|24|34|39|49|47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4810,10 +4810,10 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N47" t="n">
         <v>151</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.17439230769231</v>
+        <v>36.04099230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|4|23|34|38|49|17</t>
+          <t>3|11|20|34|38|45|33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L48" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="N48" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.00955714285714</v>
+        <v>35.87615714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|15|24|26|34|39|27</t>
+          <t>5|10|20|31|44|45|40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
         <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M49" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="N49" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.8667</v>
+        <v>35.7333</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|21|32|38|49|9</t>
+          <t>3|6|18|32|33|37|39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N50" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5152,16 +5152,16 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.7417</v>
+        <v>35.6083</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|20|31|44|45|1</t>
+          <t>3|8|12|29|34|45|23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
         <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="N51" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.63140588235294</v>
+        <v>35.49800588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|19|38|40|49|47</t>
+          <t>3|12|17|38|44|45|30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L52" t="n">
         <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="N52" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.53336666666667</v>
+        <v>35.39996666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>14|19|21|25|38|44|33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
+        <v>31</v>
+      </c>
+      <c r="L53" t="n">
         <v>32</v>
       </c>
-      <c r="L53" t="n">
-        <v>38</v>
-      </c>
       <c r="M53" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N53" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.44564736842106</v>
+        <v>35.31224736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|20|23|32|38|49|12</t>
+          <t>3|12|15|31|32|38|28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
@@ -5496,19 +5496,19 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M54" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N54" t="n">
         <v>165</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.3667</v>
+        <v>35.2333</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|9|20|38|46|49|41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N55" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.29527142857143</v>
+        <v>35.16187142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>5|6|21|32|37|38|17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,34 +1505,34 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.84999999999999</v>
+        <v>73.77</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6|8|44|49|51|56|20</t>
+          <t>8|11|13|15|52|56|48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.85</v>
+        <v>47.77</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6|12|29|35|39|48|11</t>
+          <t>8|11|15|40|44|49|50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1708,7 +1708,7 @@
         <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N14" t="n">
         <v>159</v>
@@ -1744,16 +1744,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.85</v>
+        <v>42.77</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|26</t>
+          <t>4|8|15|40|43|49|27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1790,22 +1790,22 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15" t="n">
+        <v>39</v>
+      </c>
+      <c r="M15" t="n">
         <v>37</v>
       </c>
-      <c r="M15" t="n">
-        <v>10</v>
-      </c>
       <c r="N15" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.35</v>
+        <v>40.27</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|8|16|33|37|49|10</t>
+          <t>4|7|21|32|39|46|37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
         <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,16 +1932,16 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.85</v>
+        <v>38.77</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9|13|15|32|40|48|8</t>
+          <t>2|11|27|39|40|48|34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -1975,34 +1975,34 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
+        <v>32</v>
+      </c>
+      <c r="L17" t="n">
         <v>36</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
+        <v>58</v>
+      </c>
+      <c r="N17" t="n">
+        <v>151</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
         <v>43</v>
-      </c>
-      <c r="M17" t="n">
-        <v>34</v>
-      </c>
-      <c r="N17" t="n">
-        <v>171</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>41</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,16 +2026,16 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.85</v>
+        <v>37.77</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8|11|24|36|43|49|34</t>
+          <t>6|13|15|32|36|49|58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2069,34 +2069,34 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
         <v>12</v>
       </c>
-      <c r="I18" t="n">
-        <v>13</v>
-      </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L18" t="n">
+        <v>38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>52</v>
+      </c>
+      <c r="N18" t="n">
+        <v>155</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>39</v>
-      </c>
-      <c r="M18" t="n">
-        <v>31</v>
-      </c>
-      <c r="N18" t="n">
-        <v>163</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>36</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.13571428571429</v>
+        <v>37.05571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12|13|19|32|39|48|31</t>
+          <t>8|12|15|35|38|47|52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
+        <v>31</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33</v>
+      </c>
+      <c r="M19" t="n">
         <v>39</v>
       </c>
-      <c r="L19" t="n">
-        <v>44</v>
-      </c>
-      <c r="M19" t="n">
-        <v>15</v>
-      </c>
       <c r="N19" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.6</v>
+        <v>36.52</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|15</t>
+          <t>4|8|21|31|33|46|39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M20" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.18333333333334</v>
+        <v>36.10333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10|17|27|33|40|48|8</t>
+          <t>4|13|25|32|36|49|16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="N21" t="n">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.85</v>
+        <v>35.77</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|13|22|39|43|46|28</t>
+          <t>3|11|15|30|40|48|41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M22" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.57727272727273</v>
+        <v>35.49727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4|8|29|37|40|49|36</t>
+          <t>13|21|24|32|41|46|3</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -2539,23 +2539,23 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
@@ -2564,7 +2564,7 @@
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.8</v>
+        <v>73.97</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5|7|10|34|36</t>
+          <t>6|10|12|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,23 +2629,23 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.8</v>
+        <v>47.97</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>9|10|12|25|35</t>
+          <t>6|14|15|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,35 +2716,35 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
         <v>6</v>
       </c>
-      <c r="I25" t="n">
-        <v>14</v>
-      </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.8</v>
+        <v>43.47</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>6|14|15|25|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,35 +2806,35 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="P26" t="n">
-        <v>3</v>
-      </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>41.8</v>
+        <v>42.97</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
@@ -2908,14 +2908,14 @@
         <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.3</v>
+        <v>41.97</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5|10|12|21|25</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>8</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>39.13333333333333</v>
+        <v>39.30333333333333</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4|7|14|25|35</t>
+          <t>7|9|10|25|36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,19 +3079,19 @@
         <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L29" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.8</v>
+        <v>37.97</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>5|10|12|21|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3172,29 +3172,29 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
-        <v>14</v>
-      </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.08571428571428</v>
+        <v>37.25571428571428</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,23 +3259,23 @@
         <v>7</v>
       </c>
       <c r="H31" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" t="n">
         <v>7</v>
-      </c>
-      <c r="I31" t="n">
-        <v>9</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L31" t="n">
         <v>25</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.55</v>
+        <v>36.72</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>7|9|10|24|25</t>
+          <t>6|7|10|23|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.8</v>
+        <v>35.97</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9|10|14|27|35</t>
+          <t>4|6|7|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" t="n">
         <v>10</v>
       </c>
-      <c r="J33" t="n">
-        <v>15</v>
-      </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.52727272727273</v>
+        <v>35.69727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>8|10|15|23|25</t>
+          <t>1|9|10|22|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.7333</v>
+        <v>74.5333</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|25</t>
+          <t>1|3|5|44|46|49|29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>16</v>
+      </c>
+      <c r="J35" t="n">
+        <v>17</v>
+      </c>
+      <c r="K35" t="n">
+        <v>34</v>
+      </c>
+      <c r="L35" t="n">
+        <v>44</v>
+      </c>
+      <c r="M35" t="n">
         <v>14</v>
       </c>
-      <c r="I35" t="n">
-        <v>19</v>
-      </c>
-      <c r="J35" t="n">
-        <v>24</v>
-      </c>
-      <c r="K35" t="n">
-        <v>27</v>
-      </c>
-      <c r="L35" t="n">
-        <v>31</v>
-      </c>
-      <c r="M35" t="n">
-        <v>37</v>
-      </c>
       <c r="N35" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.7333</v>
+        <v>48.5333</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14|19|24|27|31|44|37</t>
+          <t>9|16|17|34|44|45|14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K36" t="n">
         <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.7333</v>
+        <v>43.5333</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2|17|22|31|38|41|23</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
         <v>31</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="N37" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.2333</v>
+        <v>41.0333</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="N38" t="n">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.7333</v>
+        <v>39.5333</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>5|20|24|30|41|45|48</t>
+          <t>1|2|17|26|40|41|22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4038,7 +4038,7 @@
         <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N39" t="n">
         <v>167</v>
@@ -4074,16 +4074,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.7333</v>
+        <v>38.5333</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16|19|20|31|37|44|26</t>
+          <t>16|19|20|31|37|44|25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,16 +4172,16 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.01901428571428</v>
+        <v>37.81901428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|9|13|38|41|44|6</t>
+          <t>9|19|20|31|40|44|5</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M41" t="n">
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4833</v>
+        <v>37.2833</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|6</t>
+          <t>2|9|13|38|41|44|6</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
@@ -4317,10 +4317,10 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
@@ -4329,13 +4329,13 @@
         <v>31</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.06663333333333</v>
+        <v>36.86663333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>3|16|24|31|43|48|5</t>
+          <t>8|19|24|31|40|41|6</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -4466,7 +4466,7 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.7333</v>
+        <v>36.5333</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L44" t="n">
         <v>44</v>
       </c>
       <c r="M44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N44" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,16 +4564,16 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.46057272727273</v>
+        <v>36.26057272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>7|9|24|34|44|45|16</t>
+          <t>2|15|19|40|44|45|17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.7333</v>
+        <v>74.5333</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|25</t>
+          <t>1|3|5|44|46|49|29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
         <v>34</v>
       </c>
       <c r="L46" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M46" t="n">
         <v>47</v>
       </c>
       <c r="N46" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.2333</v>
+        <v>36.0333</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|18|24|34|39|49|47</t>
+          <t>6|11|20|34|41|45|47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L47" t="n">
         <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="N47" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.04099230769231</v>
+        <v>35.8409923076923</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|11|20|34|38|45|33</t>
+          <t>3|12|18|25|38|41|9</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
@@ -4905,10 +4905,10 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
         <v>20</v>
@@ -4917,13 +4917,13 @@
         <v>31</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M48" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N48" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.87615714285714</v>
+        <v>35.67615714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>5|10|20|31|44|45|40</t>
+          <t>9|19|20|31|40|42|49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J49" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L49" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.7333</v>
+        <v>35.5333</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|6|18|32|33|37|39</t>
+          <t>3|13|24|36|40|49|5</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K50" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L50" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M50" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="N50" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.6083</v>
+        <v>35.4083</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|8|12|29|34|45|23</t>
+          <t>3|5|22|32|37|40|38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L51" t="n">
+        <v>37</v>
+      </c>
+      <c r="M51" t="n">
         <v>44</v>
       </c>
-      <c r="M51" t="n">
-        <v>30</v>
-      </c>
       <c r="N51" t="n">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.49800588235294</v>
+        <v>35.29800588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|12|17|38|44|45|30</t>
+          <t>1|3|18|32|37|40|44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
         <v>25</v>
       </c>
       <c r="L52" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M52" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N52" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.39996666666666</v>
+        <v>35.19996666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14|19|21|25|38|44|33</t>
+          <t>3|6|24|25|42|49|37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5401,7 +5401,7 @@
         <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
         <v>31</v>
@@ -5410,10 +5410,10 @@
         <v>32</v>
       </c>
       <c r="M53" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="N53" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.31224736842105</v>
+        <v>35.11224736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|15|31|32|38|28</t>
+          <t>3|12|20|31|32|37|44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L54" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M54" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="N54" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,16 +5544,16 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.2333</v>
+        <v>35.0333</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|9|20|38|46|49|41</t>
+          <t>5|6|24|32|33|49|13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M55" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N55" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.16187142857143</v>
+        <v>34.96187142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>5|6|21|32|37|38|17</t>
+          <t>3|12|17|38|44|45|30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.97</v>
+        <v>73.88</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.97</v>
+        <v>47.88</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>6|14|15|25|27</t>
+          <t>10|14|15|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2722,29 +2722,29 @@
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>43.47</v>
+        <v>43.38</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>4|10|15|25|33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
@@ -2825,16 +2825,16 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>42.97</v>
+        <v>42.88</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,13 +2899,13 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>41.97</v>
+        <v>41.88</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>4|11|14|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,26 +2986,26 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>39.30333333333333</v>
+        <v>40.88</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>7|9|10|25|36</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,35 +3076,35 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="n">
-        <v>12</v>
-      </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
         <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.97</v>
+        <v>39.21333333333333</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|10|12|21|27</t>
+          <t>4|8|10|25|35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.25571428571428</v>
+        <v>37.16571428571429</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,13 +3259,13 @@
         <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
         <v>23</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.72</v>
+        <v>36.63</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|7|10|23|25</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3352,29 +3352,29 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.97</v>
+        <v>35.88</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|6|7|21|25</t>
+          <t>4|10|14|25|31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
         <v>9</v>
@@ -3448,14 +3448,14 @@
         <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.69727272727273</v>
+        <v>35.60727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1|9|10|22|25</t>
+          <t>7|9|10|24|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K34" t="n">
         <v>44</v>
@@ -3548,16 +3548,16 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="N34" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
         <v>48</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|29</t>
+          <t>1|3|42|44|46|49|45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,22 +3631,22 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
         <v>9</v>
       </c>
-      <c r="I35" t="n">
-        <v>16</v>
-      </c>
       <c r="J35" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
         <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="N35" t="n">
         <v>165</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.5333</v>
+        <v>48.6667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9|16|17|34|44|45|14</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I36" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
         <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N36" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.5333</v>
+        <v>43.6667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>13|17|24|31|38|44|10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" t="n">
         <v>16</v>
-      </c>
-      <c r="J37" t="n">
-        <v>19</v>
       </c>
       <c r="K37" t="n">
         <v>31</v>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.0333</v>
+        <v>41.1667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
         <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="N38" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.5333</v>
+        <v>39.6667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>1|2|17|26|40|41|22</t>
+          <t>14|16|17|34|39|49|8</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
@@ -4026,31 +4026,31 @@
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
+        <v>29</v>
+      </c>
+      <c r="L39" t="n">
         <v>31</v>
       </c>
-      <c r="L39" t="n">
-        <v>37</v>
-      </c>
       <c r="M39" t="n">
+        <v>14</v>
+      </c>
+      <c r="N39" t="n">
+        <v>161</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
         <v>25</v>
-      </c>
-      <c r="N39" t="n">
-        <v>167</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>28</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.5333</v>
+        <v>38.6667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16|19|20|31|37|44|25</t>
+          <t>16|20|24|29|31|41|14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -4124,22 +4124,22 @@
         <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L40" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="N40" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.81901428571428</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|44|5</t>
+          <t>9|13|24|28|38|41|46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
+        <v>16</v>
+      </c>
+      <c r="J41" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" t="n">
+        <v>29</v>
+      </c>
+      <c r="L41" t="n">
+        <v>35</v>
+      </c>
+      <c r="M41" t="n">
         <v>9</v>
       </c>
-      <c r="J41" t="n">
-        <v>13</v>
-      </c>
-      <c r="K41" t="n">
-        <v>38</v>
-      </c>
-      <c r="L41" t="n">
-        <v>41</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6</v>
-      </c>
       <c r="N41" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.2833</v>
+        <v>37.4167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2|9|13|38|41|44|6</t>
+          <t>1|16|24|29|35|44|9</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
+        <v>16</v>
+      </c>
+      <c r="J42" t="n">
         <v>19</v>
-      </c>
-      <c r="J42" t="n">
-        <v>24</v>
       </c>
       <c r="K42" t="n">
         <v>31</v>
       </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.86663333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|6</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L43" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.5333</v>
+        <v>36.6667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|13|21|30|32|38|7</t>
+          <t>9|16|24|35|41|44|4</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L44" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="M44" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N44" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.26057272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|15|19|40|44|45|17</t>
+          <t>7|16|24|29|30|39|23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
@@ -4617,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
         <v>44</v>
@@ -4626,16 +4626,16 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="N45" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
         <v>48</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|29</t>
+          <t>1|3|42|44|46|49|45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
         <v>6</v>
       </c>
-      <c r="I46" t="n">
-        <v>11</v>
-      </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
         <v>34</v>
       </c>
       <c r="L46" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M46" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.0333</v>
+        <v>36.1667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>6|11|20|34|41|45|47</t>
+          <t>3|6|24|34|37|49|4</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L47" t="n">
         <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="N47" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.8409923076923</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|12|18|25|38|41|9</t>
+          <t>3|6|8|29|38|49|35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M48" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.67615714285714</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|42|49</t>
+          <t>3|20|21|25|36|44|4</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -5003,25 +5003,25 @@
         <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M49" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N49" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,16 +5054,16 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.5333</v>
+        <v>35.6667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|13|24|36|40|49|5</t>
+          <t>6|15|24|31|44|49|16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
         <v>32</v>
       </c>
       <c r="L50" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N50" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.4083</v>
+        <v>35.5417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|5|22|32|37|40|38</t>
+          <t>3|12|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5199,25 +5199,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
+        <v>25</v>
+      </c>
+      <c r="L51" t="n">
         <v>32</v>
       </c>
-      <c r="L51" t="n">
-        <v>37</v>
-      </c>
       <c r="M51" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="N51" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.29800588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>1|3|18|32|37|40|44</t>
+          <t>3|12|20|25|32|33|7</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
@@ -5303,19 +5303,19 @@
         <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L52" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M52" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N52" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5348,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.19996666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|37</t>
+          <t>3|6|18|37|44|49|33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M53" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="N53" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.11224736842105</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|20|31|32|37|44</t>
+          <t>3|6|20|29|46|49|15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K54" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M54" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="N54" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.0333</v>
+        <v>35.1667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>5|6|24|32|33|49|13</t>
+          <t>3|12|17|38|44|45|30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J55" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
+        <v>36</v>
+      </c>
+      <c r="L55" t="n">
         <v>38</v>
       </c>
-      <c r="L55" t="n">
-        <v>44</v>
-      </c>
       <c r="M55" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="N55" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5642,16 +5642,16 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.96187142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|12|17|38|44|45|30</t>
+          <t>3|14|15|36|38|45|49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.88</v>
+        <v>73.95</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
         <v>10</v>
       </c>
-      <c r="I24" t="n">
-        <v>14</v>
-      </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.88</v>
+        <v>47.95</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10|14|15|25|27</t>
+          <t>9|10|16|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,23 +2719,23 @@
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
         <v>10</v>
-      </c>
-      <c r="J25" t="n">
-        <v>15</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>43.38</v>
+        <v>43.45</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4|10|15|25|33</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,32 +2809,32 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="P26" t="n">
-        <v>3</v>
-      </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>42.88</v>
+        <v>42.95</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|6|14|25|27</t>
+          <t>6|10|15|25|33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2899,13 +2899,13 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2948,16 +2948,16 @@
         <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>41.88</v>
+        <v>41.95</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|11|14|25|35</t>
+          <t>1|10|12|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,16 +2986,16 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" t="n">
         <v>10</v>
-      </c>
-      <c r="J28" t="n">
-        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
@@ -3005,16 +3005,16 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>40.88</v>
+        <v>39.7</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>4|8|10|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,35 +3076,35 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
         <v>2</v>
       </c>
-      <c r="P29" t="n">
-        <v>3</v>
-      </c>
       <c r="Q29" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
         <v>0.5</v>
       </c>
       <c r="X29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>39.21333333333333</v>
+        <v>37.95</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4|8|10|25|35</t>
+          <t>5|10|22|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
-      </c>
-      <c r="J30" t="n">
-        <v>22</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.16571428571429</v>
+        <v>37.23571428571429</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>4|5|10|25|31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.63</v>
+        <v>36.28333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>5|10|14|23|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,32 +3349,32 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="J32" t="n">
-        <v>14</v>
-      </c>
       <c r="K32" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
-        <v>3</v>
-      </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.88</v>
+        <v>35.95</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|10|14|25|31</t>
+          <t>1|6|10|21|29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.60727272727273</v>
+        <v>35.67727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -636,7 +636,7 @@
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.63</v>
+        <v>60.58</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -674,28 +674,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>53.13</v>
+        <v>52.58</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1|20|24|41|43|13</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
@@ -781,13 +781,13 @@
         <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -817,19 +817,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>52.63</v>
+        <v>51.58</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -861,25 +861,25 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N5" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -912,16 +912,16 @@
         <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.63</v>
+        <v>50.58</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>19</v>
@@ -962,16 +962,16 @@
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1001,19 +1001,19 @@
         <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.38</v>
+        <v>50.08</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1045,22 +1045,22 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
         <v>14</v>
-      </c>
-      <c r="I7" t="n">
-        <v>19</v>
       </c>
       <c r="J7" t="n">
         <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
         <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
         <v>127</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.96333333333333</v>
+        <v>48.91333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>9|14|22|39|43|11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1134,28 +1134,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
@@ -1185,19 +1185,19 @@
         <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.63</v>
+        <v>48.58</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>7|13|25|34|42|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
         <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.35727272727273</v>
+        <v>46.86571428571428</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5|16|19|29|34|2</t>
+          <t>14|19|22|29|43|4</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L10" t="n">
         <v>29</v>
       </c>
-      <c r="L10" t="n">
-        <v>34</v>
-      </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N10" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.91571428571429</v>
+        <v>46.33</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19|21|22|29|34|18</t>
+          <t>9|22|24|27|29|16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.63</v>
+        <v>45.30727272727272</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>3|12|15|29|32|15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.95</v>
+        <v>73.78</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,32 +2629,32 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2675,19 +2675,19 @@
         <v>0.5</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.95</v>
+        <v>50.78</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>9|10|16|25|27</t>
+          <t>4|10|14|25|35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J25" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>43.45</v>
+        <v>42.78</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>6|9|10|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>42.95</v>
+        <v>40.28</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>6|10|15|25|33</t>
+          <t>10|12|13|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>41.95</v>
+        <v>39.53</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|10|12|25|35</t>
+          <t>6|13|15|23|36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,35 +2986,35 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>3</v>
-      </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>8</v>
       </c>
       <c r="Y28" t="n">
-        <v>39.7</v>
+        <v>38.78</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4|8|10|25|35</t>
+          <t>4|13|15|25|36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
       <c r="I29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>22</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>25</v>
-      </c>
-      <c r="L29" t="n">
-        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.95</v>
+        <v>38.78</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|10|22|25|27</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,13 +3166,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
         <v>4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
       </c>
       <c r="J30" t="n">
         <v>10</v>
@@ -3181,11 +3181,11 @@
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.23571428571429</v>
+        <v>37.78</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|5|10|25|31</t>
+          <t>1|4|10|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>14</v>
-      </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L31" t="n">
         <v>25</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.28333333333333</v>
+        <v>37.06571428571429</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5|10|14|23|25</t>
+          <t>4|5|10|19|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.95</v>
+        <v>36.11333333333333</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1|6|10|21|29</t>
+          <t>5|7|10|25|32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.67727272727272</v>
+        <v>35.50727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>7|9|10|24|25</t>
+          <t>6|10|11|21|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="N34" t="n">
         <v>185</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|45</t>
+          <t>1|3|42|44|46|49|16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M35" t="n">
         <v>45</v>
       </c>
       <c r="N35" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6667</v>
+        <v>48.4667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>16|17|24|29|31|40|45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -3780,7 +3780,7 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6667</v>
+        <v>43.4667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3878,7 +3878,7 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1667</v>
+        <v>40.9667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -3925,34 +3925,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
+        <v>31</v>
+      </c>
+      <c r="L38" t="n">
+        <v>38</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>161</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>34</v>
-      </c>
-      <c r="L38" t="n">
-        <v>39</v>
-      </c>
-      <c r="M38" t="n">
-        <v>8</v>
-      </c>
-      <c r="N38" t="n">
-        <v>169</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>35</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6667</v>
+        <v>39.4667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14|16|17|34|39|49|8</t>
+          <t>9|16|24|31|38|43|4</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
+        <v>9</v>
+      </c>
+      <c r="I39" t="n">
         <v>16</v>
       </c>
-      <c r="I39" t="n">
-        <v>20</v>
-      </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L39" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M39" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="N39" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6667</v>
+        <v>38.4667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16|20|24|29|31|41|14</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -4124,22 +4124,22 @@
         <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.95241428571428</v>
+        <v>37.75241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>9|13|24|28|38|41|46</t>
+          <t>9|19|20|31|40|44|6</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M41" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N41" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4167</v>
+        <v>37.2167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1|16|24|29|35|44|9</t>
+          <t>5|19|24|30|31|44|18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L42" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M42" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,16 +4368,16 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.00003333333333</v>
+        <v>36.80003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>1|3|24|28|41|44|6</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
         <v>41</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N43" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,16 +4466,16 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6667</v>
+        <v>36.4667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>9|16|24|35|41|44|4</t>
+          <t>3|13|24|26|41|44|23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L44" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M44" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="N44" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.39397272727273</v>
+        <v>36.19397272727272</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>7|16|24|29|30|39|23</t>
+          <t>5|17|24|28|44|49|10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="N45" t="n">
         <v>185</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|45</t>
+          <t>1|3|42|44|46|49|16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4718,13 +4718,13 @@
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L46" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="N46" t="n">
         <v>153</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1667</v>
+        <v>35.9667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|6|24|34|37|49|4</t>
+          <t>3|6|24|29|42|49|28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4807,25 +4807,25 @@
         <v>12</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L47" t="n">
+        <v>35</v>
+      </c>
+      <c r="M47" t="n">
         <v>38</v>
       </c>
-      <c r="M47" t="n">
-        <v>35</v>
-      </c>
       <c r="N47" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.97439230769231</v>
+        <v>35.77439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|6|8|29|38|49|35</t>
+          <t>10|19|20|31|35|42|38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L48" t="n">
         <v>36</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N48" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.80955714285714</v>
+        <v>35.60955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|20|21|25|36|44|4</t>
+          <t>2|3|24|29|36|49|16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -5003,25 +5003,25 @@
         <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L49" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="N49" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,16 +5054,16 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6667</v>
+        <v>35.4667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>6|15|24|31|44|49|16</t>
+          <t>3|12|20|25|38|49|34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5104,19 +5104,19 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
         <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
         <v>161</v>
@@ -5152,16 +5152,16 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5417</v>
+        <v>35.3417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|12|20|32|45|49|42</t>
+          <t>3|9|20|38|42|49|5</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
+        <v>24</v>
+      </c>
+      <c r="K51" t="n">
+        <v>29</v>
+      </c>
+      <c r="L51" t="n">
+        <v>34</v>
+      </c>
+      <c r="M51" t="n">
         <v>20</v>
       </c>
-      <c r="K51" t="n">
-        <v>25</v>
-      </c>
-      <c r="L51" t="n">
-        <v>32</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7</v>
-      </c>
       <c r="N51" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.43140588235294</v>
+        <v>35.23140588235295</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|12|20|25|32|33|7</t>
+          <t>3|6|24|29|34|37|20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L52" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="N52" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5348,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.33336666666666</v>
+        <v>35.13336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|6|18|37|44|49|33</t>
+          <t>3|18|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L53" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M53" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N53" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.24564736842105</v>
+        <v>35.04564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|6|20|29|46|49|15</t>
+          <t>3|14|24|25|42|49|8</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5493,25 +5493,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L54" t="n">
         <v>44</v>
       </c>
       <c r="M54" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N54" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,16 +5544,16 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1667</v>
+        <v>34.9667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|12|17|38|44|45|30</t>
+          <t>6|17|20|31|44|45|18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M55" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="N55" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>34.89527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|14|15|36|38|45|49</t>
+          <t>3|18|21|37|40|44|13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:33</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,34 +1505,34 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.77</v>
+        <v>73.8</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8|11|13|15|52|56|48</t>
+          <t>2|4|44|49|51|56|22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
         <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="N13" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.77</v>
+        <v>47.8</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8|11|15|40|44|49|50</t>
+          <t>11|12|27|33|44|48|9</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -1693,34 +1693,34 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
+        <v>33</v>
+      </c>
+      <c r="L14" t="n">
+        <v>37</v>
+      </c>
+      <c r="M14" t="n">
+        <v>43</v>
+      </c>
+      <c r="N14" t="n">
+        <v>165</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
         <v>40</v>
-      </c>
-      <c r="L14" t="n">
-        <v>43</v>
-      </c>
-      <c r="M14" t="n">
-        <v>27</v>
-      </c>
-      <c r="N14" t="n">
-        <v>159</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>45</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,20 +1744,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.77</v>
+        <v>42.8</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|27</t>
+          <t>8|12|27|33|37|48|43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1790,22 +1790,22 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M15" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N15" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.27</v>
+        <v>40.3</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|7|21|32|39|46|37</t>
+          <t>4|8|15|40|43|49|27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16</v>
+      </c>
+      <c r="K16" t="n">
+        <v>33</v>
+      </c>
+      <c r="L16" t="n">
+        <v>36</v>
+      </c>
+      <c r="M16" t="n">
         <v>11</v>
       </c>
-      <c r="J16" t="n">
-        <v>27</v>
-      </c>
-      <c r="K16" t="n">
-        <v>39</v>
-      </c>
-      <c r="L16" t="n">
-        <v>40</v>
-      </c>
-      <c r="M16" t="n">
-        <v>34</v>
-      </c>
       <c r="N16" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.77</v>
+        <v>38.8</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|11|27|39|40|48|34</t>
+          <t>3|8|16|33|36|49|11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K17" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N17" t="n">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,16 +2026,16 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.77</v>
+        <v>37.8</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6|13|15|32|36|49|58</t>
+          <t>12|13|23|40|42|49|53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2072,22 +2072,22 @@
         <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M18" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.05571428571429</v>
+        <v>37.08571428571428</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8|12|15|35|38|47|52</t>
+          <t>8|16|27|31|32|49|6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -2169,19 +2169,19 @@
         <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="M19" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N19" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.52</v>
+        <v>36.55</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4|8|21|31|33|46|39</t>
+          <t>4|8|27|36|39|47|53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -2260,22 +2260,22 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L20" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M20" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="N20" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.10333333333333</v>
+        <v>36.13333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4|13|25|32|36|49|16</t>
+          <t>4|8|21|31|33|46|39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="N21" t="n">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.77</v>
+        <v>35.8</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3|11|15|30|40|48|41</t>
+          <t>1|22|29|32|42|49|48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2496,7 +2496,7 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.49727272727273</v>
+        <v>35.52727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.78</v>
+        <v>73.98</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,32 +2629,32 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" t="n">
         <v>10</v>
       </c>
-      <c r="J24" t="n">
-        <v>14</v>
-      </c>
       <c r="K24" t="n">
+        <v>22</v>
+      </c>
+      <c r="L24" t="n">
         <v>25</v>
-      </c>
-      <c r="L24" t="n">
-        <v>35</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2675,19 +2675,19 @@
         <v>0.5</v>
       </c>
       <c r="X24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>50.78</v>
+        <v>47.98</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4|10|14|25|35</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.78</v>
+        <v>43.48</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>6|9|10|25|27</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="n">
         <v>10</v>
       </c>
-      <c r="I26" t="n">
-        <v>12</v>
-      </c>
       <c r="J26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.28</v>
+        <v>42.98</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10|12|13|25|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
       </c>
       <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" t="n">
         <v>13</v>
       </c>
-      <c r="J27" t="n">
-        <v>15</v>
-      </c>
       <c r="K27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>39.53</v>
+        <v>38.98</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|13|15|23|36</t>
+          <t>6|10|13|21|25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,35 +2986,35 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
+        <v>23</v>
+      </c>
+      <c r="L28" t="n">
         <v>25</v>
-      </c>
-      <c r="L28" t="n">
-        <v>36</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.78</v>
+        <v>37.98</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4|13|15|25|36</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>38.78</v>
+        <v>37.26571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>2|7|12|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.78</v>
+        <v>36.73</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1|4|10|25|27</t>
+          <t>4|6|13|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,26 +3256,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>37.06571428571429</v>
+        <v>36.31333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|5|10|19|25</t>
+          <t>10|12|17|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3346,26 +3346,26 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
         <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L32" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>36.11333333333333</v>
+        <v>35.98</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5|7|10|25|32</t>
+          <t>5|6|10|23|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,32 +3439,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" t="n">
         <v>10</v>
       </c>
-      <c r="J33" t="n">
-        <v>11</v>
-      </c>
       <c r="K33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.50727272727273</v>
+        <v>35.70727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>6|10|11|21|25</t>
+          <t>4|7|10|25|32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N34" t="n">
         <v>185</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.4667</v>
+        <v>74.5333</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|16</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
         <v>45</v>
       </c>
       <c r="N35" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.4667</v>
+        <v>48.5333</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16|17|24|29|31|40|45</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N36" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.4667</v>
+        <v>43.5333</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13|17|24|31|38|44|10</t>
+          <t>5|20|24|30|41|45|13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
         <v>31</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N37" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>40.9667</v>
+        <v>41.0333</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>13|17|24|31|38|44|10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N38" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.4667</v>
+        <v>39.5333</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|16|24|31|38|43|4</t>
+          <t>14|16|17|34|39|49|7</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" t="n">
         <v>16</v>
-      </c>
-      <c r="J39" t="n">
-        <v>19</v>
       </c>
       <c r="K39" t="n">
         <v>31</v>
       </c>
       <c r="L39" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.4667</v>
+        <v>38.5333</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,10 +4121,10 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
         <v>20</v>
@@ -4133,10 +4133,10 @@
         <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="N40" t="n">
         <v>163</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.75241428571429</v>
+        <v>37.81901428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|44|6</t>
+          <t>7|16|20|31|44|45|43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L41" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M41" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.2167</v>
+        <v>37.2833</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>5|19|24|30|31|44|18</t>
+          <t>1|3|24|28|41|44|6</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4320,22 +4320,22 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.80003333333333</v>
+        <v>36.86663333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|3|24|28|41|44|6</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L43" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.4667</v>
+        <v>36.5333</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|13|24|26|41|44|23</t>
+          <t>1|7|24|28|38|45|6</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -4516,22 +4516,22 @@
         <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M44" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="N44" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.19397272727272</v>
+        <v>36.26057272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|17|24|28|44|49|10</t>
+          <t>5|7|24|38|43|48|33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
         <v>185</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.4667</v>
+        <v>74.5333</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|16</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4712,22 +4712,22 @@
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M46" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="N46" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4760,16 +4760,16 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>35.9667</v>
+        <v>36.0333</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|6|24|29|42|49|28</t>
+          <t>3|18|24|25|38|49|8</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4807,34 +4807,34 @@
         <v>12</v>
       </c>
       <c r="H47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L47" t="n">
+        <v>32</v>
+      </c>
+      <c r="M47" t="n">
+        <v>42</v>
+      </c>
+      <c r="N47" t="n">
+        <v>143</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="n">
         <v>35</v>
-      </c>
-      <c r="M47" t="n">
-        <v>38</v>
-      </c>
-      <c r="N47" t="n">
-        <v>157</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3</v>
-      </c>
-      <c r="P47" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>32</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.77439230769231</v>
+        <v>35.8409923076923</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10|19|20|31|35|42|38</t>
+          <t>3|21|24|25|32|38|42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
+        <v>42</v>
+      </c>
+      <c r="M48" t="n">
         <v>36</v>
       </c>
-      <c r="M48" t="n">
-        <v>16</v>
-      </c>
       <c r="N48" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,16 +4956,16 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.60955714285714</v>
+        <v>35.67615714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>2|3|24|29|36|49|16</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -5006,7 +5006,7 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
         <v>20</v>
@@ -5015,13 +5015,13 @@
         <v>25</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M49" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N49" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.4667</v>
+        <v>35.5333</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|20|25|38|49|34</t>
+          <t>3|18|20|25|44|45|24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
+        <v>37</v>
+      </c>
+      <c r="L50" t="n">
         <v>38</v>
       </c>
-      <c r="L50" t="n">
-        <v>42</v>
-      </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="N50" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.3417</v>
+        <v>35.4083</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|9|20|38|42|49|5</t>
+          <t>3|12|23|37|38|46|48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L51" t="n">
+        <v>38</v>
+      </c>
+      <c r="M51" t="n">
         <v>34</v>
       </c>
-      <c r="M51" t="n">
-        <v>20</v>
-      </c>
       <c r="N51" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.23140588235295</v>
+        <v>35.29800588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|24|29|34|37|20</t>
+          <t>3|11|18|32|38|45|34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L52" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M52" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.13336666666666</v>
+        <v>35.19996666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|18|20|32|45|49|42</t>
+          <t>3|20|21|25|36|42|4</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L53" t="n">
+        <v>45</v>
+      </c>
+      <c r="M53" t="n">
         <v>42</v>
       </c>
-      <c r="M53" t="n">
-        <v>8</v>
-      </c>
       <c r="N53" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5446,16 +5446,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.04564736842106</v>
+        <v>35.11224736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|14|24|25|42|49|8</t>
+          <t>3|12|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>34.9667</v>
+        <v>35.0333</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L55" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M55" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="N55" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.89527142857143</v>
+        <v>34.96187142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|18|21|37|40|44|13</t>
+          <t>11|19|20|26|38|45|34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2539,23 +2539,23 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="n">
-        <v>12</v>
-      </c>
       <c r="K23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
@@ -2564,7 +2564,7 @@
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.98</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6|10|12|33|35</t>
+          <t>5|7|10|34|36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,23 +2629,23 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.98</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>4|14|15|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2716,26 +2716,26 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>43.48</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>10|11|14|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,26 +2806,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>42.98</v>
+        <v>40.84</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
@@ -2905,17 +2905,17 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.98</v>
+        <v>40.34</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|13|21|25</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,35 +2986,35 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="n">
         <v>10</v>
       </c>
-      <c r="J28" t="n">
-        <v>14</v>
-      </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L28" t="n">
         <v>25</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>3</v>
-      </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.98</v>
+        <v>38.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3079,23 +3079,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.26571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2|7|12|25|27</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,23 +3169,23 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K30" t="n">
+        <v>21</v>
+      </c>
+      <c r="L30" t="n">
         <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.73</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|6|13|25|27</t>
+          <t>9|10|12|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,32 +3259,32 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
         <v>10</v>
       </c>
-      <c r="I31" t="n">
-        <v>12</v>
-      </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
+        <v>21</v>
+      </c>
+      <c r="L31" t="n">
         <v>25</v>
-      </c>
-      <c r="L31" t="n">
-        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.31333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10|12|17|25|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
         <v>23</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.98</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5|6|10|23|27</t>
+          <t>6|7|10|23|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,32 +3439,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
         <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.70727272727272</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|7|10|25|32</t>
+          <t>2|7|12|25|27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N34" t="n">
         <v>185</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
         <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M35" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="N35" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3686,16 +3686,16 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>5|13|24|38|41|48|9</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
         <v>10</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3882,16 +3882,16 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13|17|24|31|38|44|10</t>
+          <t>1|3|16|38|44|45|10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,34 +3925,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" t="n">
         <v>16</v>
       </c>
-      <c r="J38" t="n">
-        <v>17</v>
-      </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L38" t="n">
+        <v>44</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>157</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>39</v>
-      </c>
-      <c r="M38" t="n">
-        <v>7</v>
-      </c>
-      <c r="N38" t="n">
-        <v>169</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>35</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3980,16 +3980,16 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14|16|17|34|39|49|7</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
+        <v>27</v>
+      </c>
+      <c r="L39" t="n">
         <v>31</v>
       </c>
-      <c r="L39" t="n">
-        <v>44</v>
-      </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4078,16 +4078,16 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>16|19|22|27|31|44|35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -4121,34 +4121,34 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M40" t="n">
+        <v>6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>141</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
         <v>43</v>
-      </c>
-      <c r="N40" t="n">
-        <v>163</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3</v>
-      </c>
-      <c r="P40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>38</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4176,16 +4176,16 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>7|16|20|31|44|45|43</t>
+          <t>1|3|24|28|41|44|6</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -4222,22 +4222,22 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4274,16 +4274,16 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1|3|24|28|41|44|6</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4320,22 +4320,22 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L42" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>1|7|24|28|38|45|6</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
       </c>
       <c r="K43" t="n">
+        <v>26</v>
+      </c>
+      <c r="L43" t="n">
+        <v>44</v>
+      </c>
+      <c r="M43" t="n">
         <v>28</v>
       </c>
-      <c r="L43" t="n">
-        <v>38</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6</v>
-      </c>
       <c r="N43" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>1|7|24|28|38|45|6</t>
+          <t>9|13|24|26|44|45|28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
+        <v>31</v>
+      </c>
+      <c r="L44" t="n">
         <v>38</v>
       </c>
-      <c r="L44" t="n">
-        <v>43</v>
-      </c>
       <c r="M44" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N44" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4568,16 +4568,16 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|7|24|38|43|48|33</t>
+          <t>14|19|20|31|38|45|29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N45" t="n">
         <v>185</v>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4712,7 +4712,7 @@
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
@@ -4721,13 +4721,13 @@
         <v>25</v>
       </c>
       <c r="L46" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M46" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="N46" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4764,12 +4764,12 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|18|24|25|38|49|8</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L47" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N47" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4862,16 +4862,16 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|21|24|25|32|38|42</t>
+          <t>3|12|23|37|38|46|48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L48" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="M48" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="N48" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4960,16 +4960,16 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>9|11|20|27|36|42|44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5104,22 +5104,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N50" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5156,16 +5156,16 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|12|23|37|38|46|48</t>
+          <t>3|18|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
+        <v>25</v>
+      </c>
+      <c r="L51" t="n">
         <v>32</v>
-      </c>
-      <c r="L51" t="n">
-        <v>38</v>
       </c>
       <c r="M51" t="n">
         <v>34</v>
       </c>
       <c r="N51" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|11|18|32|38|45|34</t>
+          <t>3|12|20|25|32|45|34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
+        <v>11</v>
+      </c>
+      <c r="J52" t="n">
         <v>20</v>
       </c>
-      <c r="J52" t="n">
-        <v>21</v>
-      </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L52" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="N52" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5352,12 +5352,12 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|20|21|25|36|42|4</t>
+          <t>3|11|20|29|40|42|44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L53" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M53" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="N53" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5450,16 +5450,16 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|20|32|45|49|42</t>
+          <t>3|19|20|36|37|42|10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
         <v>31</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M54" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5548,16 +5548,16 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>6|17|20|31|44|45|18</t>
+          <t>6|20|24|31|37|49|4</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M55" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="N55" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5646,16 +5646,16 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11|19|20|26|38|45|34</t>
+          <t>3|18|24|27|35|44|45</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -633,10 +633,10 @@
         <v>0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>60.58</v>
+        <v>57.6</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -674,28 +674,28 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>7</v>
-      </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>52.58</v>
+        <v>53.1</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7|13|24|29|34|11</t>
+          <t>2|22|23|31|43|17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -817,19 +817,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>52.6</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>13|19|24|34|37|3</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -861,25 +861,25 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -912,16 +912,16 @@
         <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.58</v>
+        <v>50.6</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>8|15|24|29|43|7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -950,28 +950,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -1001,19 +1001,19 @@
         <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>50.08</v>
+        <v>49.35</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>1|13|18|34|37|5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1045,25 +1045,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.91333333333333</v>
+        <v>48.93333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9|14|22|39|43|11</t>
+          <t>3|15|20|29|38|13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1137,19 +1137,19 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.6</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7|13|25|34|42|11</t>
+          <t>2|20|25|31|43|11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1280,16 +1280,16 @@
         <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.86571428571428</v>
+        <v>48.6</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14|19|22|29|43|4</t>
+          <t>4|19|24|29|31|10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,28 +1318,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.33</v>
+        <v>46.88571428571429</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|22|24|27|29|16</t>
+          <t>9|19|24|34|41|18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1413,25 +1413,25 @@
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>45.32727272727273</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3|12|15|29|32|15</t>
+          <t>9|14|22|39|43|11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.91</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.91</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,10 +2719,10 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>7</v>
+      </c>
+      <c r="I25" t="n">
         <v>10</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11</v>
       </c>
       <c r="J25" t="n">
         <v>14</v>
@@ -2731,11 +2731,11 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.84</v>
+        <v>42.91</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10|11|14|25|35</t>
+          <t>7|10|14|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>9</v>
@@ -2821,11 +2821,11 @@
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2855,19 +2855,19 @@
         <v>0.5</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.84</v>
+        <v>40.41</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>4|9|10|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,26 +2896,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="J27" t="n">
-        <v>15</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.34</v>
+        <v>40.19571428571428</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.84</v>
+        <v>38.91</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>6|10|15|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3076,26 +3076,26 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
       <c r="I29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="n">
-        <v>14</v>
-      </c>
       <c r="K29" t="n">
+        <v>22</v>
+      </c>
+      <c r="L29" t="n">
         <v>25</v>
-      </c>
-      <c r="L29" t="n">
-        <v>31</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.12571428571429</v>
+        <v>37.91</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
@@ -3185,16 +3185,16 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.59</v>
+        <v>36.66</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9|10|12|21|25</t>
+          <t>4|10|12|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
@@ -3268,23 +3268,23 @@
         <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.17333333333333</v>
+        <v>36.24333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>5|10|14|25|31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
         <v>6</v>
       </c>
-      <c r="I32" t="n">
-        <v>7</v>
-      </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.84</v>
+        <v>35.91</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|7|10|23|25</t>
+          <t>4|6|13|25|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,32 +3439,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>35.63727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>2|7|12|25|27</t>
+          <t>4|6|10|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="N34" t="n">
         <v>185</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|42|44|46|49|29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
         <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.5333</v>
+        <v>48.6667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>5|13|24|38|41|48|9</t>
+          <t>2|5|9|38|44|45|6</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -3729,22 +3729,22 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N36" t="n">
         <v>165</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.5333</v>
+        <v>43.6667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|20|24|30|41|45|13</t>
+          <t>14|19|24|29|38|41|20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
+        <v>31</v>
+      </c>
+      <c r="L37" t="n">
         <v>38</v>
       </c>
-      <c r="L37" t="n">
-        <v>44</v>
-      </c>
       <c r="M37" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="N37" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.0333</v>
+        <v>41.1667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1|3|16|38|44|45|10</t>
+          <t>5|19|22|31|38|44|40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I38" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" t="n">
+        <v>30</v>
+      </c>
+      <c r="L38" t="n">
+        <v>32</v>
+      </c>
+      <c r="M38" t="n">
         <v>15</v>
       </c>
-      <c r="J38" t="n">
-        <v>16</v>
-      </c>
-      <c r="K38" t="n">
-        <v>31</v>
-      </c>
-      <c r="L38" t="n">
-        <v>44</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5</v>
-      </c>
       <c r="N38" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.5333</v>
+        <v>39.6667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>13|17|24|30|32|39|15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" t="n">
         <v>19</v>
       </c>
-      <c r="J39" t="n">
-        <v>22</v>
-      </c>
       <c r="K39" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L39" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="N39" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.5333</v>
+        <v>38.6667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16|19|22|27|31|44|35</t>
+          <t>2|15|19|40|44|45|17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -4121,10 +4121,10 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
@@ -4133,13 +4133,13 @@
         <v>28</v>
       </c>
       <c r="L40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.81901428571428</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>1|3|24|28|41|44|6</t>
+          <t>13|15|24|28|44|45|1</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,16 +4270,16 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.2833</v>
+        <v>37.4167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>17|20|24|28|31|45|8</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N42" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,20 +4368,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.86663333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|7|24|28|38|45|6</t>
+          <t>2|17|24|31|33|44|18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
+        <v>5</v>
+      </c>
+      <c r="I43" t="n">
         <v>9</v>
       </c>
-      <c r="I43" t="n">
-        <v>13</v>
-      </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L43" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M43" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="N43" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.5333</v>
+        <v>36.6667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>9|13|24|26|44|45|28</t>
+          <t>5|9|17|36|40|44|15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L44" t="n">
         <v>38</v>
       </c>
       <c r="M44" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N44" t="n">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,20 +4564,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.26057272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14|19|20|31|38|45|29</t>
+          <t>3|5|13|30|38|44|33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="N45" t="n">
         <v>185</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|42|44|46|49|29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L46" t="n">
         <v>42</v>
       </c>
       <c r="M46" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.0333</v>
+        <v>36.1667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>4|11|20|31|42|45|3</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -4813,19 +4813,19 @@
         <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M47" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="N47" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,20 +4858,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.8409923076923</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|12|23|37|38|46|48</t>
+          <t>3|12|15|25|36|38|10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
         <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L48" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="N48" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.67615714285714</v>
+        <v>35.80955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>9|11|20|27|36|42|44</t>
+          <t>11|19|20|31|38|44|8</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -5006,22 +5006,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
         <v>25</v>
       </c>
       <c r="L49" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M49" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="N49" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.5333</v>
+        <v>35.6667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|18|20|25|44|45|24</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -5101,22 +5101,22 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="N50" t="n">
         <v>167</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.4083</v>
+        <v>35.5417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|18|20|32|45|49|42</t>
+          <t>6|19|24|31|42|45|33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
         <v>25</v>
       </c>
       <c r="L51" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M51" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N51" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5250,16 +5250,16 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.29800588235294</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|12|20|25|32|45|34</t>
+          <t>3|18|24|25|34|45|20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J52" t="n">
         <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N52" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.19996666666667</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|11|20|29|40|42|44</t>
+          <t>3|12|20|25|38|49|34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L53" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M53" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="N53" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.11224736842105</v>
+        <v>35.24564736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|19|20|36|37|42|10</t>
+          <t>3|8|15|38|42|49|40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -5493,22 +5493,22 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
+        <v>18</v>
+      </c>
+      <c r="J54" t="n">
         <v>20</v>
       </c>
-      <c r="J54" t="n">
-        <v>24</v>
-      </c>
       <c r="K54" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L54" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="N54" t="n">
         <v>167</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,16 +5544,16 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.0333</v>
+        <v>35.1667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>6|20|24|31|37|49|4</t>
+          <t>3|18|20|32|45|49|42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L55" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M55" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="N55" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.96187142857143</v>
+        <v>35.09527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|18|24|27|35|44|45</t>
+          <t>3|12|20|25|32|45|34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
         <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.8</v>
+        <v>73.81</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|22</t>
+          <t>2|4|44|49|51|56|10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
         <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="N13" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,20 +1650,20 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.8</v>
+        <v>47.81</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11|12|27|33|44|48|9</t>
+          <t>5|8|15|40|44|49|28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1693,22 +1693,22 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L14" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
         <v>165</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -1744,16 +1744,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.8</v>
+        <v>42.81</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8|12|27|33|37|48|43</t>
+          <t>7|11|16|39|44|48|17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
         <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M15" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="N15" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,16 +1838,16 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.3</v>
+        <v>40.31</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|27</t>
+          <t>7|8|17|38|42|49|9</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="N16" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,16 +1932,16 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.8</v>
+        <v>38.81</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3|8|16|33|36|49|11</t>
+          <t>6|8|25|39|40|49|41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -1975,25 +1975,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L17" t="n">
         <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N17" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,16 +2026,16 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.8</v>
+        <v>37.81</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12|13|23|40|42|49|53</t>
+          <t>2|11|27|38|42|49|41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2069,25 +2069,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L18" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="N18" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.08571428571428</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8|16|27|31|32|49|6</t>
+          <t>1|7|20|32|39|46|42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -2163,25 +2163,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
         <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M19" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N19" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2190,7 +2190,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.55</v>
+        <v>36.56</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4|8|27|36|39|47|53</t>
+          <t>8|18|27|32|37|49|25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2257,25 +2257,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L20" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.13333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4|8|21|31|33|46|39</t>
+          <t>8|12|19|33|37|48|18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2351,22 +2351,22 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
         <v>175</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.8</v>
+        <v>35.81</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1|22|29|32|42|49|48</t>
+          <t>12|14|27|31|43|48|2</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>12</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29</v>
+      </c>
+      <c r="K22" t="n">
+        <v>36</v>
+      </c>
+      <c r="L22" t="n">
+        <v>39</v>
+      </c>
+      <c r="M22" t="n">
         <v>13</v>
       </c>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" t="n">
-        <v>24</v>
-      </c>
-      <c r="K22" t="n">
-        <v>32</v>
-      </c>
-      <c r="L22" t="n">
-        <v>41</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3</v>
-      </c>
       <c r="N22" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.52727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13|21|24|32|41|46|3</t>
+          <t>6|12|29|36|39|49|13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.91</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
         <v>14</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.91</v>
+        <v>47.85</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4|14|15|25|27</t>
+          <t>7|10|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,13 +2719,13 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.91</v>
+        <v>42.85</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>7|10|14|25|27</t>
+          <t>4|14|15|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
         <v>9</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.41</v>
+        <v>40.35</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|9|10|25|27</t>
+          <t>6|9|10|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.19571428571428</v>
+        <v>39.18333333333334</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>1|5|10|25|36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,23 +2989,23 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="n">
         <v>10</v>
       </c>
-      <c r="J28" t="n">
-        <v>15</v>
-      </c>
       <c r="K28" t="n">
+        <v>22</v>
+      </c>
+      <c r="L28" t="n">
         <v>25</v>
-      </c>
-      <c r="L28" t="n">
-        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.91</v>
+        <v>38.85</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|10|15|25|27</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3082,20 +3082,20 @@
         <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.91</v>
+        <v>37.85</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
         <v>4</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,7 +3218,7 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.66</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
@@ -3271,20 +3271,20 @@
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.125</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.24333333333333</v>
+        <v>36.6</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5|10|14|25|31</t>
+          <t>4|10|14|25|29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,23 +3349,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
         <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.91</v>
+        <v>35.85</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|6|13|25|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3445,26 +3445,26 @@
         <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.63727272727273</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|6|10|23|25</t>
+          <t>4|6|13|25|27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="N34" t="n">
         <v>185</v>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|29</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="N35" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3686,16 +3686,16 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>2|5|9|38|44|45|6</t>
+          <t>17|19|22|26|31|44|34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L36" t="n">
         <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3784,16 +3784,16 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14|19|24|29|38|41|20</t>
+          <t>1|7|24|28|38|45|6</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3882,16 +3882,16 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>5|19|22|31|38|44|40</t>
+          <t>2|5|9|38|44|45|6</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L38" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N38" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3980,16 +3980,16 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13|17|24|30|32|39|15</t>
+          <t>14|19|24|29|38|41|17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4023,34 +4023,34 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J39" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L39" t="n">
+        <v>45</v>
+      </c>
+      <c r="M39" t="n">
+        <v>24</v>
+      </c>
+      <c r="N39" t="n">
+        <v>163</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
         <v>44</v>
-      </c>
-      <c r="M39" t="n">
-        <v>17</v>
-      </c>
-      <c r="N39" t="n">
-        <v>165</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>43</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4078,16 +4078,16 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>2|15|19|40|44|45|17</t>
+          <t>5|14|16|34|45|49|24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I40" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N40" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4176,16 +4176,16 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13|15|24|28|44|45|1</t>
+          <t>17|19|24|26|34|39|8</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
         <v>17</v>
       </c>
-      <c r="I41" t="n">
-        <v>20</v>
-      </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K41" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L41" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4274,16 +4274,16 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17|20|24|28|31|45|8</t>
+          <t>2|17|23|26|41|44|7</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N42" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4372,16 +4372,16 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2|17|24|31|33|44|18</t>
+          <t>1|5|24|40|44|45|19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -4415,25 +4415,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
         <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M43" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N43" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4470,16 +4470,16 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|9|17|36|40|44|15</t>
+          <t>3|9|22|42|44|45|7</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -4516,22 +4516,22 @@
         <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
+        <v>38</v>
+      </c>
+      <c r="L44" t="n">
+        <v>43</v>
+      </c>
+      <c r="M44" t="n">
         <v>30</v>
       </c>
-      <c r="L44" t="n">
-        <v>38</v>
-      </c>
-      <c r="M44" t="n">
-        <v>33</v>
-      </c>
       <c r="N44" t="n">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4568,12 +4568,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>3|5|13|30|38|44|33</t>
+          <t>3|17|24|38|43|44|30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
         <v>185</v>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|29</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4709,25 +4709,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="N46" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4764,16 +4764,16 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>4|11|20|31|42|45|3</t>
+          <t>3|6|24|36|37|49|33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -4810,22 +4810,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
         <v>25</v>
       </c>
       <c r="L47" t="n">
+        <v>42</v>
+      </c>
+      <c r="M47" t="n">
         <v>36</v>
       </c>
-      <c r="M47" t="n">
-        <v>10</v>
-      </c>
       <c r="N47" t="n">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4862,16 +4862,16 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|12|15|25|36|38|10</t>
+          <t>3|6|24|25|42|49|36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -4905,25 +4905,25 @@
         <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
         <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N48" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4960,16 +4960,16 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11|19|20|31|38|44|8</t>
+          <t>3|18|20|25|44|45|24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -5003,25 +5003,25 @@
         <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L49" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M49" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>2|3|24|40|47|49|9</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -5101,22 +5101,22 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M50" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N50" t="n">
         <v>167</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5156,16 +5156,16 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>6|19|24|31|42|45|33</t>
+          <t>2|13|24|39|40|49|36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -5202,22 +5202,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L51" t="n">
         <v>34</v>
       </c>
       <c r="M51" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N51" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|18|24|25|34|45|20</t>
+          <t>3|15|24|32|34|45|41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -5300,22 +5300,22 @@
         <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L52" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5352,12 +5352,12 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|12|20|25|38|49|34</t>
+          <t>3|10|14|38|45|49|8</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L53" t="n">
         <v>42</v>
       </c>
       <c r="M53" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5450,16 +5450,16 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|40</t>
+          <t>3|11|20|31|42|46|4</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
+        <v>9</v>
+      </c>
+      <c r="J54" t="n">
         <v>18</v>
       </c>
-      <c r="J54" t="n">
-        <v>20</v>
-      </c>
       <c r="K54" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M54" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="N54" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|18|20|32|45|49|42</t>
+          <t>3|9|18|38|42|49|33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
         <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L55" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M55" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="N55" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5646,16 +5646,16 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|12|20|25|32|45|34</t>
+          <t>3|19|20|36|37|42|10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -2539,32 +2539,32 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
         <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="P23" t="n">
-        <v>3</v>
-      </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
@@ -2588,16 +2588,16 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5|7|10|34|36</t>
+          <t>1|6|10|33|35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
         <v>10</v>
-      </c>
-      <c r="J24" t="n">
-        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.85</v>
+        <v>47.89</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|10|14|25|27</t>
+          <t>4|5|10|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,13 +2719,13 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>25</v>
@@ -2735,16 +2735,16 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.85</v>
+        <v>42.89</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4|14|15|25|27</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
         <v>9</v>
@@ -2818,14 +2818,14 @@
         <v>10</v>
       </c>
       <c r="K26" t="n">
+        <v>22</v>
+      </c>
+      <c r="L26" t="n">
         <v>25</v>
-      </c>
-      <c r="L26" t="n">
-        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.35</v>
+        <v>40.39</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>6|9|10|25|27</t>
+          <t>5|9|10|22|25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2948,16 +2948,16 @@
         <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>39.18333333333334</v>
+        <v>40.17571428571429</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|5|10|25|36</t>
+          <t>1|9|10|25|36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2989,32 +2989,32 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>38.85</v>
+        <v>38.89</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>4|6|14|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3082,16 +3082,16 @@
         <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -3128,16 +3128,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.85</v>
+        <v>37.89</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>5|12|16|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
         <v>4</v>
@@ -3175,7 +3175,7 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
         <v>21</v>
@@ -3185,13 +3185,13 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>21</v>
@@ -3203,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>37.13571428571429</v>
+        <v>36.64</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|10|12|21|25</t>
+          <t>4|10|15|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3256,35 +3256,35 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
+        <v>21</v>
+      </c>
+      <c r="L31" t="n">
         <v>25</v>
-      </c>
-      <c r="L31" t="n">
-        <v>29</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.6</v>
+        <v>36.22333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|10|14|25|29</t>
+          <t>9|10|12|21|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3349,32 +3349,32 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
         <v>10</v>
-      </c>
-      <c r="J32" t="n">
-        <v>14</v>
       </c>
       <c r="K32" t="n">
         <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -3398,16 +3398,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.85</v>
+        <v>35.89</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|6|10|25|36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -3439,23 +3439,23 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L33" t="n">
         <v>27</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -3488,16 +3488,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.57727272727273</v>
+        <v>35.61727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|6|13|25|27</t>
+          <t>5|11|14|22|27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -3548,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>185</v>
@@ -3584,16 +3584,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -3631,25 +3631,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
         <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="N35" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -3682,20 +3682,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6667</v>
+        <v>48.4667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|22|26|31|44|34</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
@@ -3729,25 +3729,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N36" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -3780,20 +3780,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6667</v>
+        <v>43.4667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>1|7|24|28|38|45|6</t>
+          <t>7|17|24|32|40|41|15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -3827,25 +3827,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="N37" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -3854,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3878,20 +3878,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1667</v>
+        <v>40.9667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|5|9|38|44|45|6</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3925,25 +3925,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M38" t="n">
         <v>17</v>
       </c>
       <c r="N38" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -3976,20 +3976,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6667</v>
+        <v>39.4667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14|19|24|29|38|41|17</t>
+          <t>3|23|24|28|41|44|17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -4023,25 +4023,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L39" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N39" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4050,7 +4050,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -4074,20 +4074,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6667</v>
+        <v>38.4667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|14|16|34|45|49|24</t>
+          <t>16|19|20|31|37|44|27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -4121,25 +4121,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L40" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -4172,20 +4172,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.95241428571428</v>
+        <v>37.75241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17|19|24|26|34|39|8</t>
+          <t>2|5|9|38|44|45|6</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -4219,25 +4219,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L41" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N41" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -4246,7 +4246,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -4270,20 +4270,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4167</v>
+        <v>37.2167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2|17|23|26|41|44|7</t>
+          <t>14|19|20|31|38|45|32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -4317,25 +4317,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
         <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M42" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N42" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4368,16 +4368,16 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.00003333333333</v>
+        <v>36.80003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|5|24|40|44|45|19</t>
+          <t>6|14|19|40|41|45|8</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -4424,16 +4424,16 @@
         <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L43" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="N43" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4466,20 +4466,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6667</v>
+        <v>36.4667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3|9|22|42|44|45|7</t>
+          <t>3|9|22|30|38|41|49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -4513,25 +4513,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L44" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M44" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -4540,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4564,16 +4564,16 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.39397272727273</v>
+        <v>36.19397272727272</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>3|17|24|38|43|44|30</t>
+          <t>7|13|19|32|40|44|6</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -4626,7 +4626,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N45" t="n">
         <v>185</v>
@@ -4662,16 +4662,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -4712,19 +4712,19 @@
         <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M46" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N46" t="n">
         <v>155</v>
@@ -4736,7 +4736,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4760,20 +4760,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.1667</v>
+        <v>35.9667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|6|24|36|37|49|33</t>
+          <t>3|14|18|37|38|45|34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -4807,25 +4807,25 @@
         <v>12</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L47" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M47" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="N47" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -4834,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4858,16 +4858,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.97439230769231</v>
+        <v>35.77439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|6|24|25|42|49|36</t>
+          <t>11|20|22|29|32|49|47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -4908,22 +4908,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
         <v>25</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M48" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="N48" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4956,20 +4956,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.80955714285714</v>
+        <v>35.60955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|18|20|25|44|45|24</t>
+          <t>3|6|24|25|42|49|37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -5003,25 +5003,25 @@
         <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L49" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="M49" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="N49" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -5054,20 +5054,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6667</v>
+        <v>35.4667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>2|3|24|40|47|49|9</t>
+          <t>3|12|20|31|32|45|34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -5101,25 +5101,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="N50" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -5152,20 +5152,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5417</v>
+        <v>35.3417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2|13|24|39|40|49|36</t>
+          <t>1|20|21|29|42|44|6</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
@@ -5202,19 +5202,19 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" t="n">
+        <v>29</v>
+      </c>
+      <c r="L51" t="n">
+        <v>46</v>
+      </c>
+      <c r="M51" t="n">
         <v>15</v>
-      </c>
-      <c r="J51" t="n">
-        <v>24</v>
-      </c>
-      <c r="K51" t="n">
-        <v>32</v>
-      </c>
-      <c r="L51" t="n">
-        <v>34</v>
-      </c>
-      <c r="M51" t="n">
-        <v>41</v>
       </c>
       <c r="N51" t="n">
         <v>153</v>
@@ -5226,7 +5226,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -5250,20 +5250,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.43140588235294</v>
+        <v>35.23140588235295</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|15|24|32|34|45|41</t>
+          <t>3|6|20|29|46|49|15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -5297,25 +5297,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L52" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N52" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5348,20 +5348,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.33336666666666</v>
+        <v>35.13336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|10|14|38|45|49|8</t>
+          <t>1|4|20|33|42|45|29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -5398,22 +5398,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N53" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -5422,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5446,20 +5446,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.24564736842105</v>
+        <v>35.04564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|11|20|31|42|46|4</t>
+          <t>3|20|21|29|40|42|30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
@@ -5496,22 +5496,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L54" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M54" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N54" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5544,20 +5544,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1667</v>
+        <v>34.9667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|9|18|38|42|49|33</t>
+          <t>3|19|20|36|37|42|10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
@@ -5594,22 +5594,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L55" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M55" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N55" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5642,20 +5642,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>34.89527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|19|20|36|37|42|10</t>
+          <t>3|14|18|29|42|45|22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/all_games_ensemble_predictions.xlsx
@@ -585,25 +585,25 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -636,16 +636,16 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.6</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9|15|20|38|43|18</t>
+          <t>7|13|24|29|34|11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -674,28 +674,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U3" t="n">
         <v>0.5</v>
@@ -725,19 +725,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>53.1</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2|22|23|31|43|17</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -817,19 +817,19 @@
         <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>52.6</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13|19|24|34|37|3</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
         <v>29</v>
@@ -876,10 +876,10 @@
         <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -888,7 +888,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -909,19 +909,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.6</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8|15|24|29|43|7</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -956,22 +956,22 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -1004,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>49.35</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1045,25 +1045,25 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23</v>
+      </c>
+      <c r="K7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L7" t="n">
+        <v>41</v>
+      </c>
+      <c r="M7" t="n">
         <v>15</v>
       </c>
-      <c r="J7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" t="n">
-        <v>29</v>
-      </c>
-      <c r="L7" t="n">
-        <v>38</v>
-      </c>
-      <c r="M7" t="n">
-        <v>13</v>
-      </c>
       <c r="N7" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1072,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1096,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.93333333333333</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3|15|20|29|38|13</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1137,22 +1137,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1188,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.6</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2|20|25|31|43|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -1277,19 +1277,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>48.6</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4|19|24|29|31|10</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
@@ -1330,16 +1330,16 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1348,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.88571428571429</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|19|24|34|41|18</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -1410,28 +1410,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -1464,16 +1464,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.32727272727273</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|14|22|39|43|11</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -1517,10 +1517,10 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.81</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|10</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -1599,25 +1599,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1650,16 +1650,16 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.81</v>
+        <v>47.85</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5|8|15|40|44|49|28</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -1696,22 +1696,22 @@
         <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="N14" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1744,16 +1744,16 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.81</v>
+        <v>42.85</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|17</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -1787,25 +1787,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L15" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -1838,20 +1838,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.31</v>
+        <v>40.35</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7|8|17|38|42|49|9</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1881,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1908,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -1932,20 +1932,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.81</v>
+        <v>38.85</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6|8|25|39|40|49|41</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1975,22 +1975,22 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
         <v>11</v>
       </c>
       <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="n">
+        <v>40</v>
+      </c>
+      <c r="L17" t="n">
+        <v>44</v>
+      </c>
+      <c r="M17" t="n">
         <v>27</v>
-      </c>
-      <c r="K17" t="n">
-        <v>38</v>
-      </c>
-      <c r="L17" t="n">
-        <v>42</v>
-      </c>
-      <c r="M17" t="n">
-        <v>41</v>
       </c>
       <c r="N17" t="n">
         <v>169</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2026,20 +2026,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.81</v>
+        <v>37.85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2|11|27|38|42|49|41</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -2072,22 +2072,22 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -2096,7 +2096,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2120,20 +2120,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.09571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|7|20|32|39|46|42</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -2163,10 +2163,10 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
         <v>8</v>
-      </c>
-      <c r="I19" t="n">
-        <v>18</v>
       </c>
       <c r="J19" t="n">
         <v>27</v>
@@ -2175,13 +2175,13 @@
         <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -2214,20 +2214,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.56</v>
+        <v>36.6</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8|18|27|32|37|49|25</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -2260,22 +2260,22 @@
         <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -2284,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2308,20 +2308,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.14333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|12|19|33|37|48|18</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2351,25 +2351,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
         <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2402,20 +2402,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.81</v>
+        <v>35.85</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12|14|27|31|43|48|2</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2445,25 +2445,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -2472,7 +2472,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2496,20 +2496,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.53727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6|12|29|36|39|49|13</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2588,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.89</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2678,16 +2678,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.89</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4|5|10|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -2735,16 +2735,16 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2768,16 +2768,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.89</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2812,20 +2812,20 @@
         <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -2858,16 +2858,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.39</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|9|10|22|25</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
@@ -2911,7 +2911,7 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
@@ -2924,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0.5</v>
       </c>
       <c r="X27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>40.17571428571429</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1|9|10|25|36</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
         <v>14</v>
@@ -3005,16 +3005,16 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>3</v>
-      </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -30